--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA8528A-A0F0-44BB-8E85-3AE44CFC2348}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0BDD4A-FF86-4F3E-A05A-D0CC37C93C29}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="71" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="72" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="670">
   <si>
     <t>Codigo</t>
   </si>
@@ -2003,6 +2003,39 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7790250016182.png</t>
+  </si>
+  <si>
+    <t>7792658000763</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Nupcial</t>
+  </si>
+  <si>
+    <t>Bazar</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7792658000763.png</t>
+  </si>
+  <si>
+    <t>7792316001019</t>
+  </si>
+  <si>
+    <t>Sidra</t>
+  </si>
+  <si>
+    <t>etiqueta</t>
+  </si>
+  <si>
+    <t>La Victoria</t>
+  </si>
+  <si>
+    <t>Bebidas alcohólicas</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7792316001019.png</t>
   </si>
 </sst>
 </file>
@@ -2354,8 +2387,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E032640-34D0-4A58-80D0-EF8E3820E11D}">
-  <dimension ref="A1:R122"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95569BB3-265A-4516-B01E-9EB6B663FBBA}">
+  <dimension ref="A1:R124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -6236,57 +6269,57 @@
         <v>1</v>
       </c>
       <c r="Q69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="B70" t="s">
-        <v>584</v>
+        <v>659</v>
       </c>
       <c r="C70" t="s">
-        <v>585</v>
+        <v>660</v>
       </c>
       <c r="D70" t="s">
-        <v>541</v>
+        <v>17</v>
       </c>
       <c r="E70" t="s">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="F70" t="s">
-        <v>517</v>
+        <v>661</v>
       </c>
       <c r="G70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H70" t="s">
         <v>20</v>
       </c>
       <c r="I70" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J70" t="s">
-        <v>587</v>
+        <v>662</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
       </c>
       <c r="N70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="s">
-        <v>588</v>
+        <v>663</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -6300,49 +6333,49 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="B71" t="s">
-        <v>589</v>
+        <v>664</v>
       </c>
       <c r="C71" t="s">
-        <v>590</v>
+        <v>665</v>
       </c>
       <c r="D71" t="s">
-        <v>591</v>
+        <v>666</v>
       </c>
       <c r="E71" t="s">
-        <v>592</v>
+        <v>426</v>
       </c>
       <c r="F71" t="s">
-        <v>593</v>
+        <v>667</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>720</v>
       </c>
       <c r="H71" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I71" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="J71" t="s">
-        <v>594</v>
+        <v>668</v>
       </c>
       <c r="K71" t="s">
-        <v>595</v>
+        <v>23</v>
       </c>
       <c r="L71">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
       </c>
       <c r="N71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>596</v>
+        <v>669</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
@@ -6356,40 +6389,40 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B72" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="C72" t="s">
-        <v>72</v>
+        <v>585</v>
       </c>
       <c r="D72" t="s">
-        <v>598</v>
+        <v>541</v>
       </c>
       <c r="E72" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="F72" t="s">
-        <v>600</v>
+        <v>517</v>
       </c>
       <c r="G72">
-        <v>180</v>
+        <v>2</v>
       </c>
       <c r="H72" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I72" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="J72" t="s">
-        <v>76</v>
+        <v>587</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
@@ -6398,7 +6431,7 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
@@ -6412,22 +6445,22 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B73" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="C73" t="s">
-        <v>195</v>
+        <v>590</v>
       </c>
       <c r="D73" t="s">
-        <v>172</v>
+        <v>591</v>
       </c>
       <c r="E73" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="F73" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -6436,16 +6469,16 @@
         <v>20</v>
       </c>
       <c r="I73" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J73" t="s">
-        <v>243</v>
+        <v>594</v>
       </c>
       <c r="K73" t="s">
-        <v>23</v>
+        <v>595</v>
       </c>
       <c r="L73">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
@@ -6454,7 +6487,7 @@
         <v>0</v>
       </c>
       <c r="O73" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
@@ -6463,54 +6496,54 @@
         <v>1</v>
       </c>
       <c r="R73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B74" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="C74" t="s">
-        <v>607</v>
+        <v>72</v>
       </c>
       <c r="D74" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="E74" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="F74" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="H74" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I74" t="s">
-        <v>490</v>
+        <v>53</v>
       </c>
       <c r="J74" t="s">
-        <v>611</v>
+        <v>76</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
       </c>
       <c r="L74">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
       </c>
       <c r="N74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -6524,49 +6557,49 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B75" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="C75" t="s">
-        <v>614</v>
+        <v>195</v>
       </c>
       <c r="D75" t="s">
-        <v>615</v>
+        <v>172</v>
       </c>
       <c r="E75" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="F75" t="s">
-        <v>111</v>
+        <v>604</v>
       </c>
       <c r="G75">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H75" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I75" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J75" t="s">
-        <v>576</v>
+        <v>243</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
       </c>
       <c r="N75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -6575,54 +6608,54 @@
         <v>1</v>
       </c>
       <c r="R75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B76" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="C76" t="s">
-        <v>174</v>
+        <v>607</v>
       </c>
       <c r="D76" t="s">
-        <v>175</v>
+        <v>608</v>
       </c>
       <c r="E76" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="F76" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76" t="s">
         <v>20</v>
-      </c>
-      <c r="H76" t="s">
-        <v>42</v>
       </c>
       <c r="I76" t="s">
         <v>490</v>
       </c>
       <c r="J76" t="s">
-        <v>177</v>
+        <v>611</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
       </c>
       <c r="N76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O76" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -6636,40 +6669,40 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="B77" t="s">
-        <v>373</v>
+        <v>613</v>
       </c>
       <c r="C77" t="s">
-        <v>88</v>
+        <v>614</v>
       </c>
       <c r="D77" t="s">
-        <v>89</v>
+        <v>615</v>
       </c>
       <c r="E77" t="s">
-        <v>90</v>
+        <v>616</v>
       </c>
       <c r="F77" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="G77">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="H77" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I77" t="s">
-        <v>36</v>
+        <v>490</v>
       </c>
       <c r="J77" t="s">
-        <v>92</v>
+        <v>576</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
       </c>
       <c r="L77">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
@@ -6678,13 +6711,13 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>265</v>
+        <v>617</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
       </c>
       <c r="Q77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" t="b">
         <v>1</v>
@@ -6692,40 +6725,40 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="B78" t="s">
-        <v>374</v>
+        <v>618</v>
       </c>
       <c r="C78" t="s">
-        <v>62</v>
+        <v>174</v>
       </c>
       <c r="D78" t="s">
-        <v>93</v>
+        <v>175</v>
       </c>
       <c r="E78" t="s">
-        <v>94</v>
+        <v>619</v>
       </c>
       <c r="F78" t="s">
-        <v>95</v>
+        <v>620</v>
       </c>
       <c r="G78">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H78" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I78" t="s">
-        <v>60</v>
+        <v>490</v>
       </c>
       <c r="J78" t="s">
-        <v>66</v>
+        <v>177</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -6734,13 +6767,13 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>266</v>
+        <v>621</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
       </c>
       <c r="Q78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" t="b">
         <v>1</v>
@@ -6748,40 +6781,40 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B79" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C79" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="D79" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="E79" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="F79" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H79" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I79" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="J79" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -6790,13 +6823,13 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
       </c>
       <c r="Q79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R79" t="b">
         <v>1</v>
@@ -6804,49 +6837,49 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B80" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C80" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="D80" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E80" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F80" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G80">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="H80" t="s">
         <v>20</v>
       </c>
       <c r="I80" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J80" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
       </c>
       <c r="N80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6860,34 +6893,34 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B81" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C81" t="s">
-        <v>103</v>
+        <v>24</v>
       </c>
       <c r="D81" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="E81" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="F81" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="G81">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H81" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I81" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="J81" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
@@ -6902,13 +6935,13 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
       </c>
       <c r="Q81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R81" t="b">
         <v>1</v>
@@ -6916,34 +6949,34 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B82" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C82" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="D82" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E82" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F82" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="G82">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H82" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I82" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J82" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
@@ -6955,10 +6988,10 @@
         <v>0</v>
       </c>
       <c r="N82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O82" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -6972,40 +7005,40 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B83" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C83" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="D83" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E83" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="F83" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G83">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H83" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I83" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J83" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
       </c>
       <c r="L83">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
@@ -7014,13 +7047,13 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
       </c>
       <c r="Q83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="b">
         <v>1</v>
@@ -7028,34 +7061,34 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
+        <v>32</v>
+      </c>
+      <c r="B84" t="s">
+        <v>378</v>
+      </c>
+      <c r="C84" t="s">
+        <v>31</v>
+      </c>
+      <c r="D84" t="s">
+        <v>109</v>
+      </c>
+      <c r="E84" t="s">
+        <v>110</v>
+      </c>
+      <c r="F84" t="s">
         <v>34</v>
       </c>
-      <c r="B84" t="s">
-        <v>380</v>
-      </c>
-      <c r="C84" t="s">
-        <v>112</v>
-      </c>
-      <c r="D84" t="s">
-        <v>113</v>
-      </c>
-      <c r="E84" t="s">
-        <v>114</v>
-      </c>
-      <c r="F84" t="s">
-        <v>115</v>
-      </c>
       <c r="G84">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H84" t="s">
         <v>35</v>
       </c>
       <c r="I84" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="J84" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
@@ -7070,7 +7103,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -7084,40 +7117,40 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B85" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C85" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="D85" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="E85" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="F85" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="G85">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H85" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I85" t="s">
         <v>21</v>
       </c>
       <c r="J85" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
       </c>
       <c r="L85">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
@@ -7126,13 +7159,13 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
       </c>
       <c r="Q85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" t="b">
         <v>1</v>
@@ -7140,34 +7173,34 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
+        <v>34</v>
+      </c>
+      <c r="B86" t="s">
+        <v>380</v>
+      </c>
+      <c r="C86" t="s">
+        <v>112</v>
+      </c>
+      <c r="D86" t="s">
+        <v>113</v>
+      </c>
+      <c r="E86" t="s">
+        <v>114</v>
+      </c>
+      <c r="F86" t="s">
+        <v>115</v>
+      </c>
+      <c r="G86">
+        <v>300</v>
+      </c>
+      <c r="H86" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86" t="s">
         <v>36</v>
       </c>
-      <c r="B86" t="s">
-        <v>382</v>
-      </c>
-      <c r="C86" t="s">
-        <v>121</v>
-      </c>
-      <c r="D86" t="s">
-        <v>122</v>
-      </c>
-      <c r="E86" t="s">
-        <v>32</v>
-      </c>
-      <c r="F86" t="s">
-        <v>123</v>
-      </c>
-      <c r="G86">
-        <v>250</v>
-      </c>
-      <c r="H86" t="s">
-        <v>42</v>
-      </c>
-      <c r="I86" t="s">
-        <v>124</v>
-      </c>
       <c r="J86" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
@@ -7182,13 +7215,13 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
       </c>
       <c r="Q86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R86" t="b">
         <v>1</v>
@@ -7196,40 +7229,40 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B87" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C87" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D87" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E87" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F87" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="G87">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="H87" t="s">
         <v>42</v>
       </c>
       <c r="I87" t="s">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="J87" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
       </c>
       <c r="L87">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
@@ -7238,7 +7271,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -7252,40 +7285,40 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B88" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C88" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="D88" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="E88" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="F88" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="G88">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H88" t="s">
         <v>42</v>
       </c>
       <c r="I88" t="s">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="J88" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
@@ -7294,7 +7327,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -7308,40 +7341,40 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B89" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C89" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D89" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E89" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="F89" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G89">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="H89" t="s">
         <v>42</v>
       </c>
       <c r="I89" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="J89" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
@@ -7350,13 +7383,13 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
       </c>
       <c r="Q89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R89" t="b">
         <v>1</v>
@@ -7364,40 +7397,40 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B90" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C90" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D90" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E90" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="F90" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="H90" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I90" t="s">
         <v>21</v>
       </c>
       <c r="J90" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
       </c>
       <c r="L90">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -7406,7 +7439,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -7420,55 +7453,55 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B91" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C91" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D91" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E91" t="s">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="F91" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="G91">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="H91" t="s">
         <v>42</v>
       </c>
       <c r="I91" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="J91" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="M91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
       </c>
       <c r="Q91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" t="b">
         <v>1</v>
@@ -7476,55 +7509,55 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B92" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C92" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D92" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E92" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="F92" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="G92">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H92" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I92" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J92" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
       </c>
       <c r="L92">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
       </c>
       <c r="Q92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" t="b">
         <v>1</v>
@@ -7532,22 +7565,22 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B93" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C93" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D93" t="s">
         <v>139</v>
       </c>
       <c r="E93" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F93" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G93">
         <v>1000</v>
@@ -7559,7 +7592,7 @@
         <v>142</v>
       </c>
       <c r="J93" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
@@ -7571,10 +7604,10 @@
         <v>1</v>
       </c>
       <c r="N93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O93" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
@@ -7588,55 +7621,55 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B94" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C94" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D94" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E94" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F94" t="s">
-        <v>152</v>
+        <v>87</v>
       </c>
       <c r="G94">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H94" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I94" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J94" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
       </c>
       <c r="L94">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
       </c>
       <c r="Q94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R94" t="b">
         <v>1</v>
@@ -7644,49 +7677,49 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B95" t="s">
-        <v>645</v>
+        <v>389</v>
       </c>
       <c r="C95" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D95" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="E95" t="s">
-        <v>646</v>
+        <v>146</v>
       </c>
       <c r="F95" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="G95">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="H95" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I95" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="J95" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="K95" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="L95">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="M95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>647</v>
+        <v>281</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
@@ -7700,34 +7733,34 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B96" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C96" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D96" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="E96" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="F96" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="G96">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="H96" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I96" t="s">
-        <v>29</v>
+        <v>153</v>
       </c>
       <c r="J96" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
@@ -7742,7 +7775,7 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
@@ -7756,55 +7789,55 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B97" t="s">
-        <v>392</v>
+        <v>645</v>
       </c>
       <c r="C97" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="D97" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E97" t="s">
-        <v>167</v>
+        <v>646</v>
       </c>
       <c r="F97" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="G97">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H97" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I97" t="s">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="J97" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="K97" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="L97">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
       </c>
       <c r="N97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O97" t="s">
-        <v>284</v>
+        <v>647</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
       </c>
       <c r="Q97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" t="b">
         <v>1</v>
@@ -7812,34 +7845,34 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B98" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C98" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D98" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="E98" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F98" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="G98">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H98" t="s">
         <v>42</v>
       </c>
       <c r="I98" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J98" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="K98" t="s">
         <v>23</v>
@@ -7854,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
@@ -7868,34 +7901,34 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B99" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C99" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D99" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="E99" t="s">
-        <v>622</v>
+        <v>167</v>
       </c>
       <c r="F99" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G99">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H99" t="s">
         <v>42</v>
       </c>
       <c r="I99" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J99" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="K99" t="s">
         <v>23</v>
@@ -7910,7 +7943,7 @@
         <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
@@ -7924,37 +7957,37 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B100" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C100" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D100" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E100" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F100" t="s">
-        <v>181</v>
+        <v>70</v>
       </c>
       <c r="G100">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H100" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I100" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J100" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="K100" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="L100">
         <v>12</v>
@@ -7966,7 +7999,7 @@
         <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
@@ -7980,40 +8013,40 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B101" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C101" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D101" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="E101" t="s">
-        <v>186</v>
+        <v>622</v>
       </c>
       <c r="F101" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="G101">
-        <v>360</v>
+        <v>50</v>
       </c>
       <c r="H101" t="s">
-        <v>188</v>
+        <v>42</v>
       </c>
       <c r="I101" t="s">
-        <v>189</v>
+        <v>490</v>
       </c>
       <c r="J101" t="s">
-        <v>552</v>
+        <v>177</v>
       </c>
       <c r="K101" t="s">
         <v>23</v>
       </c>
       <c r="L101">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M101" t="b">
         <v>0</v>
@@ -8022,7 +8055,7 @@
         <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
@@ -8036,13 +8069,13 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B102" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C102" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D102" t="s">
         <v>179</v>
@@ -8054,7 +8087,7 @@
         <v>181</v>
       </c>
       <c r="G102">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H102" t="s">
         <v>20</v>
@@ -8066,10 +8099,10 @@
         <v>182</v>
       </c>
       <c r="K102" t="s">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="L102">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M102" t="b">
         <v>0</v>
@@ -8078,7 +8111,7 @@
         <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
@@ -8092,34 +8125,34 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C103" t="s">
-        <v>31</v>
+        <v>184</v>
       </c>
       <c r="D103" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="E103" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F103" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="G103">
-        <v>1.5</v>
+        <v>360</v>
       </c>
       <c r="H103" t="s">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="I103" t="s">
-        <v>36</v>
+        <v>189</v>
       </c>
       <c r="J103" t="s">
-        <v>37</v>
+        <v>552</v>
       </c>
       <c r="K103" t="s">
         <v>23</v>
@@ -8134,7 +8167,7 @@
         <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
@@ -8148,52 +8181,52 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B104" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C104" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D104" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="E104" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="F104" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="G104">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H104" t="s">
         <v>20</v>
       </c>
       <c r="I104" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J104" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="K104" t="s">
         <v>23</v>
       </c>
       <c r="L104">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="M104" t="b">
         <v>0</v>
       </c>
       <c r="N104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="P104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q104" t="b">
         <v>1</v>
@@ -8204,40 +8237,40 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B105" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C105" t="s">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="D105" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E105" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="F105" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G105">
-        <v>150</v>
+        <v>1.5</v>
       </c>
       <c r="H105" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I105" t="s">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="J105" t="s">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="K105" t="s">
         <v>23</v>
       </c>
       <c r="L105">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M105" t="b">
         <v>0</v>
@@ -8246,13 +8279,13 @@
         <v>1</v>
       </c>
       <c r="O105" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
       </c>
       <c r="Q105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105" t="b">
         <v>1</v>
@@ -8260,55 +8293,55 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B106" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C106" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D106" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="E106" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F106" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="G106">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="H106" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I106" t="s">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="J106" t="s">
-        <v>66</v>
+        <v>199</v>
       </c>
       <c r="K106" t="s">
         <v>23</v>
       </c>
       <c r="L106">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M106" t="b">
         <v>0</v>
       </c>
       <c r="N106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O106" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="P106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R106" t="b">
         <v>1</v>
@@ -8316,40 +8349,40 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B107" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C107" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="D107" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="E107" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="F107" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G107">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H107" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I107" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="J107" t="s">
-        <v>66</v>
+        <v>190</v>
       </c>
       <c r="K107" t="s">
         <v>23</v>
       </c>
       <c r="L107">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M107" t="b">
         <v>0</v>
@@ -8358,7 +8391,7 @@
         <v>1</v>
       </c>
       <c r="O107" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
@@ -8372,10 +8405,10 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B108" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C108" t="s">
         <v>203</v>
@@ -8384,7 +8417,7 @@
         <v>204</v>
       </c>
       <c r="E108" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="F108" t="s">
         <v>206</v>
@@ -8405,7 +8438,7 @@
         <v>23</v>
       </c>
       <c r="L108">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M108" t="b">
         <v>0</v>
@@ -8414,7 +8447,7 @@
         <v>1</v>
       </c>
       <c r="O108" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="P108" t="b">
         <v>1</v>
@@ -8428,40 +8461,40 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B109" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C109" t="s">
-        <v>145</v>
+        <v>208</v>
       </c>
       <c r="D109" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E109" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F109" t="s">
-        <v>56</v>
+        <v>206</v>
       </c>
       <c r="G109">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H109" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I109" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="J109" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K109" t="s">
         <v>23</v>
       </c>
       <c r="L109">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M109" t="b">
         <v>0</v>
@@ -8470,13 +8503,13 @@
         <v>1</v>
       </c>
       <c r="O109" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="P109" t="b">
         <v>1</v>
       </c>
       <c r="Q109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R109" t="b">
         <v>1</v>
@@ -8484,34 +8517,34 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B110" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C110" t="s">
-        <v>24</v>
+        <v>203</v>
       </c>
       <c r="D110" t="s">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="E110" t="s">
-        <v>55</v>
+        <v>211</v>
       </c>
       <c r="F110" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="G110">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="H110" t="s">
         <v>42</v>
       </c>
       <c r="I110" t="s">
-        <v>60</v>
+        <v>207</v>
       </c>
       <c r="J110" t="s">
-        <v>553</v>
+        <v>66</v>
       </c>
       <c r="K110" t="s">
         <v>23</v>
@@ -8526,13 +8559,13 @@
         <v>1</v>
       </c>
       <c r="O110" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P110" t="b">
         <v>1</v>
       </c>
       <c r="Q110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R110" t="b">
         <v>1</v>
@@ -8540,49 +8573,49 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B111" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C111" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="D111" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E111" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="F111" t="s">
-        <v>218</v>
+        <v>56</v>
       </c>
       <c r="G111">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H111" t="s">
         <v>20</v>
       </c>
       <c r="I111" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="J111" t="s">
-        <v>215</v>
+        <v>148</v>
       </c>
       <c r="K111" t="s">
         <v>23</v>
       </c>
       <c r="L111">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M111" t="b">
         <v>0</v>
       </c>
       <c r="N111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P111" t="b">
         <v>1</v>
@@ -8596,55 +8629,55 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B112" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C112" t="s">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="D112" t="s">
-        <v>219</v>
+        <v>81</v>
       </c>
       <c r="E112" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="F112" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="G112">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H112" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I112" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J112" t="s">
-        <v>215</v>
+        <v>553</v>
       </c>
       <c r="K112" t="s">
         <v>23</v>
       </c>
       <c r="L112">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M112" t="b">
         <v>0</v>
       </c>
       <c r="N112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P112" t="b">
         <v>1</v>
       </c>
       <c r="Q112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R112" t="b">
         <v>1</v>
@@ -8652,55 +8685,55 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B113" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C113" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D113" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="E113" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F113" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="G113">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H113" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I113" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J113" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K113" t="s">
         <v>23</v>
       </c>
       <c r="L113">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M113" t="b">
         <v>0</v>
       </c>
       <c r="N113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O113" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P113" t="b">
         <v>1</v>
       </c>
       <c r="Q113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" t="b">
         <v>1</v>
@@ -8708,49 +8741,49 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B114" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C114" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D114" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="E114" t="s">
-        <v>32</v>
+        <v>217</v>
       </c>
       <c r="F114" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G114">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="H114" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I114" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="J114" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="K114" t="s">
         <v>23</v>
       </c>
       <c r="L114">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M114" t="b">
         <v>0</v>
       </c>
       <c r="N114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O114" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="P114" t="b">
         <v>1</v>
@@ -8764,40 +8797,40 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B115" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C115" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D115" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="E115" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="F115" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="G115">
-        <v>237</v>
+        <v>60</v>
       </c>
       <c r="H115" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I115" t="s">
-        <v>124</v>
+        <v>53</v>
       </c>
       <c r="J115" t="s">
-        <v>125</v>
+        <v>222</v>
       </c>
       <c r="K115" t="s">
         <v>23</v>
       </c>
       <c r="L115">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M115" t="b">
         <v>0</v>
@@ -8806,13 +8839,13 @@
         <v>1</v>
       </c>
       <c r="O115" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="P115" t="b">
         <v>1</v>
       </c>
       <c r="Q115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R115" t="b">
         <v>1</v>
@@ -8820,40 +8853,40 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B116" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C116" t="s">
-        <v>44</v>
+        <v>223</v>
       </c>
       <c r="D116" t="s">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="E116" t="s">
-        <v>227</v>
+        <v>32</v>
       </c>
       <c r="F116" t="s">
-        <v>47</v>
+        <v>224</v>
       </c>
       <c r="G116">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="H116" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I116" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J116" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="K116" t="s">
         <v>23</v>
       </c>
       <c r="L116">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M116" t="b">
         <v>0</v>
@@ -8862,13 +8895,13 @@
         <v>1</v>
       </c>
       <c r="O116" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="P116" t="b">
         <v>1</v>
       </c>
       <c r="Q116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R116" t="b">
         <v>1</v>
@@ -8876,40 +8909,40 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B117" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C117" t="s">
-        <v>31</v>
+        <v>225</v>
       </c>
       <c r="D117" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="E117" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F117" t="s">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="G117">
-        <v>1.5</v>
+        <v>237</v>
       </c>
       <c r="H117" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I117" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="J117" t="s">
-        <v>37</v>
+        <v>125</v>
       </c>
       <c r="K117" t="s">
         <v>23</v>
       </c>
       <c r="L117">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M117" t="b">
         <v>0</v>
@@ -8918,13 +8951,13 @@
         <v>1</v>
       </c>
       <c r="O117" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="P117" t="b">
         <v>1</v>
       </c>
       <c r="Q117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R117" t="b">
         <v>1</v>
@@ -8932,40 +8965,40 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B118" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C118" t="s">
-        <v>184</v>
+        <v>44</v>
       </c>
       <c r="D118" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="E118" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F118" t="s">
-        <v>202</v>
+        <v>47</v>
       </c>
       <c r="G118">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="H118" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I118" t="s">
-        <v>189</v>
+        <v>60</v>
       </c>
       <c r="J118" t="s">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="K118" t="s">
         <v>23</v>
       </c>
       <c r="L118">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M118" t="b">
         <v>0</v>
@@ -8974,13 +9007,13 @@
         <v>1</v>
       </c>
       <c r="O118" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="P118" t="b">
         <v>1</v>
       </c>
       <c r="Q118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R118" t="b">
         <v>1</v>
@@ -8988,34 +9021,34 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B119" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C119" t="s">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="D119" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E119" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F119" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G119">
-        <v>150</v>
+        <v>1.5</v>
       </c>
       <c r="H119" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I119" t="s">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="J119" t="s">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="K119" t="s">
         <v>23</v>
@@ -9030,7 +9063,7 @@
         <v>1</v>
       </c>
       <c r="O119" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="P119" t="b">
         <v>1</v>
@@ -9044,10 +9077,10 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B120" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C120" t="s">
         <v>184</v>
@@ -9056,7 +9089,7 @@
         <v>200</v>
       </c>
       <c r="E120" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F120" t="s">
         <v>202</v>
@@ -9086,7 +9119,7 @@
         <v>1</v>
       </c>
       <c r="O120" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="P120" t="b">
         <v>1</v>
@@ -9100,41 +9133,41 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B121" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C121" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="D121" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="E121" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F121" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="G121">
+        <v>150</v>
+      </c>
+      <c r="H121" t="s">
+        <v>35</v>
+      </c>
+      <c r="I121" t="s">
+        <v>189</v>
+      </c>
+      <c r="J121" t="s">
+        <v>190</v>
+      </c>
+      <c r="K121" t="s">
+        <v>23</v>
+      </c>
+      <c r="L121">
         <v>6</v>
       </c>
-      <c r="H121" t="s">
-        <v>20</v>
-      </c>
-      <c r="I121" t="s">
-        <v>237</v>
-      </c>
-      <c r="J121" t="s">
-        <v>233</v>
-      </c>
-      <c r="K121" t="s">
-        <v>23</v>
-      </c>
-      <c r="L121">
-        <v>1</v>
-      </c>
       <c r="M121" t="b">
         <v>0</v>
       </c>
@@ -9142,13 +9175,13 @@
         <v>1</v>
       </c>
       <c r="O121" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="P121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R121" t="b">
         <v>1</v>
@@ -9156,57 +9189,169 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
+        <v>70</v>
+      </c>
+      <c r="B122" t="s">
+        <v>415</v>
+      </c>
+      <c r="C122" t="s">
+        <v>184</v>
+      </c>
+      <c r="D122" t="s">
+        <v>200</v>
+      </c>
+      <c r="E122" t="s">
+        <v>232</v>
+      </c>
+      <c r="F122" t="s">
+        <v>202</v>
+      </c>
+      <c r="G122">
+        <v>250</v>
+      </c>
+      <c r="H122" t="s">
+        <v>35</v>
+      </c>
+      <c r="I122" t="s">
+        <v>189</v>
+      </c>
+      <c r="J122" t="s">
+        <v>190</v>
+      </c>
+      <c r="K122" t="s">
+        <v>23</v>
+      </c>
+      <c r="L122">
+        <v>6</v>
+      </c>
+      <c r="M122" t="b">
+        <v>0</v>
+      </c>
+      <c r="N122" t="b">
+        <v>1</v>
+      </c>
+      <c r="O122" t="s">
+        <v>307</v>
+      </c>
+      <c r="P122" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q122" t="b">
+        <v>0</v>
+      </c>
+      <c r="R122" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>71</v>
+      </c>
+      <c r="B123" t="s">
+        <v>416</v>
+      </c>
+      <c r="C123" t="s">
+        <v>233</v>
+      </c>
+      <c r="D123" t="s">
+        <v>234</v>
+      </c>
+      <c r="E123" t="s">
+        <v>235</v>
+      </c>
+      <c r="F123" t="s">
+        <v>236</v>
+      </c>
+      <c r="G123">
+        <v>6</v>
+      </c>
+      <c r="H123" t="s">
+        <v>20</v>
+      </c>
+      <c r="I123" t="s">
+        <v>237</v>
+      </c>
+      <c r="J123" t="s">
+        <v>233</v>
+      </c>
+      <c r="K123" t="s">
+        <v>23</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
+      </c>
+      <c r="M123" t="b">
+        <v>0</v>
+      </c>
+      <c r="N123" t="b">
+        <v>1</v>
+      </c>
+      <c r="O123" t="s">
+        <v>308</v>
+      </c>
+      <c r="P123" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="b">
+        <v>1</v>
+      </c>
+      <c r="R123" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
         <v>72</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B124" t="s">
         <v>417</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C124" t="s">
         <v>195</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D124" t="s">
         <v>196</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E124" t="s">
         <v>197</v>
       </c>
-      <c r="F122" t="s">
+      <c r="F124" t="s">
         <v>238</v>
       </c>
-      <c r="G122">
+      <c r="G124">
         <v>4</v>
       </c>
-      <c r="H122" t="s">
+      <c r="H124" t="s">
         <v>20</v>
       </c>
-      <c r="I122" t="s">
+      <c r="I124" t="s">
         <v>21</v>
       </c>
-      <c r="J122" t="s">
+      <c r="J124" t="s">
         <v>199</v>
       </c>
-      <c r="K122" t="s">
-        <v>23</v>
-      </c>
-      <c r="L122">
+      <c r="K124" t="s">
+        <v>23</v>
+      </c>
+      <c r="L124">
         <v>10</v>
       </c>
-      <c r="M122" t="b">
-        <v>0</v>
-      </c>
-      <c r="N122" t="b">
-        <v>0</v>
-      </c>
-      <c r="O122" t="s">
+      <c r="M124" t="b">
+        <v>0</v>
+      </c>
+      <c r="N124" t="b">
+        <v>0</v>
+      </c>
+      <c r="O124" t="s">
         <v>309</v>
       </c>
-      <c r="P122" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q122" t="b">
-        <v>1</v>
-      </c>
-      <c r="R122" t="b">
+      <c r="P124" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q124" t="b">
+        <v>1</v>
+      </c>
+      <c r="R124" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0BDD4A-FF86-4F3E-A05A-D0CC37C93C29}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDFF8B5-48CA-4367-BEE1-B20F7058E0B6}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="72" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="73" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="673">
   <si>
     <t>Codigo</t>
   </si>
@@ -2036,6 +2036,15 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7792316001019.png</t>
+  </si>
+  <si>
+    <t>7798174970016</t>
+  </si>
+  <si>
+    <t>Azucel</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7798174970016.png</t>
   </si>
 </sst>
 </file>
@@ -2387,8 +2396,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95569BB3-265A-4516-B01E-9EB6B663FBBA}">
-  <dimension ref="A1:R124"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6835F66E-7A5E-426E-A87E-9AB71E9F7D26}">
+  <dimension ref="A1:R125"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -6389,40 +6398,40 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B72" t="s">
-        <v>584</v>
+        <v>670</v>
       </c>
       <c r="C72" t="s">
-        <v>585</v>
+        <v>44</v>
       </c>
       <c r="D72" t="s">
-        <v>541</v>
+        <v>77</v>
       </c>
       <c r="E72" t="s">
-        <v>586</v>
+        <v>78</v>
       </c>
       <c r="F72" t="s">
-        <v>517</v>
+        <v>671</v>
       </c>
       <c r="G72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H72" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I72" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J72" t="s">
-        <v>587</v>
+        <v>44</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
       </c>
       <c r="L72">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
@@ -6431,7 +6440,7 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>588</v>
+        <v>672</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
@@ -6445,37 +6454,37 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B73" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C73" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="D73" t="s">
-        <v>591</v>
+        <v>541</v>
       </c>
       <c r="E73" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="F73" t="s">
-        <v>593</v>
+        <v>517</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H73" t="s">
         <v>20</v>
       </c>
       <c r="I73" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="J73" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="K73" t="s">
-        <v>595</v>
+        <v>23</v>
       </c>
       <c r="L73">
         <v>12</v>
@@ -6484,10 +6493,10 @@
         <v>0</v>
       </c>
       <c r="N73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
@@ -6501,49 +6510,49 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B74" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="C74" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="D74" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="E74" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="F74" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="G74">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H74" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I74" t="s">
         <v>53</v>
       </c>
       <c r="J74" t="s">
-        <v>76</v>
+        <v>594</v>
       </c>
       <c r="K74" t="s">
-        <v>23</v>
+        <v>595</v>
       </c>
       <c r="L74">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
       </c>
       <c r="N74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -6557,49 +6566,49 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B75" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="C75" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="D75" t="s">
-        <v>172</v>
+        <v>598</v>
       </c>
       <c r="E75" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="F75" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="H75" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I75" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J75" t="s">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
       </c>
       <c r="N75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -6608,27 +6617,27 @@
         <v>1</v>
       </c>
       <c r="R75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B76" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C76" t="s">
-        <v>607</v>
+        <v>195</v>
       </c>
       <c r="D76" t="s">
-        <v>608</v>
+        <v>172</v>
       </c>
       <c r="E76" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="F76" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -6637,16 +6646,16 @@
         <v>20</v>
       </c>
       <c r="I76" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J76" t="s">
-        <v>611</v>
+        <v>243</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
@@ -6655,7 +6664,7 @@
         <v>0</v>
       </c>
       <c r="O76" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -6664,39 +6673,39 @@
         <v>1</v>
       </c>
       <c r="R76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B77" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="C77" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="D77" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="E77" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="F77" t="s">
-        <v>111</v>
+        <v>610</v>
       </c>
       <c r="G77">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I77" t="s">
         <v>490</v>
       </c>
       <c r="J77" t="s">
-        <v>576</v>
+        <v>611</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
@@ -6708,10 +6717,10 @@
         <v>0</v>
       </c>
       <c r="N77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6725,25 +6734,25 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B78" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C78" t="s">
-        <v>174</v>
+        <v>614</v>
       </c>
       <c r="D78" t="s">
-        <v>175</v>
+        <v>615</v>
       </c>
       <c r="E78" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="F78" t="s">
-        <v>620</v>
+        <v>111</v>
       </c>
       <c r="G78">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H78" t="s">
         <v>42</v>
@@ -6752,13 +6761,13 @@
         <v>490</v>
       </c>
       <c r="J78" t="s">
-        <v>177</v>
+        <v>576</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -6767,7 +6776,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6781,40 +6790,40 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="B79" t="s">
-        <v>373</v>
+        <v>618</v>
       </c>
       <c r="C79" t="s">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="D79" t="s">
-        <v>89</v>
+        <v>175</v>
       </c>
       <c r="E79" t="s">
-        <v>90</v>
+        <v>619</v>
       </c>
       <c r="F79" t="s">
-        <v>91</v>
+        <v>620</v>
       </c>
       <c r="G79">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="H79" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I79" t="s">
-        <v>36</v>
+        <v>490</v>
       </c>
       <c r="J79" t="s">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -6823,13 +6832,13 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>265</v>
+        <v>621</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
       </c>
       <c r="Q79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" t="b">
         <v>1</v>
@@ -6837,40 +6846,40 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C80" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D80" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E80" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F80" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G80">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H80" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I80" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J80" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
@@ -6879,7 +6888,7 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6893,41 +6902,41 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B81" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C81" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D81" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E81" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F81" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H81" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I81" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J81" t="s">
+        <v>66</v>
+      </c>
+      <c r="K81" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81">
         <v>30</v>
       </c>
-      <c r="K81" t="s">
-        <v>23</v>
-      </c>
-      <c r="L81">
-        <v>12</v>
-      </c>
       <c r="M81" t="b">
         <v>0</v>
       </c>
@@ -6935,13 +6944,13 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
       </c>
       <c r="Q81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" t="b">
         <v>1</v>
@@ -6949,55 +6958,55 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
+        <v>29</v>
+      </c>
+      <c r="B82" t="s">
+        <v>375</v>
+      </c>
+      <c r="C82" t="s">
+        <v>24</v>
+      </c>
+      <c r="D82" t="s">
+        <v>54</v>
+      </c>
+      <c r="E82" t="s">
+        <v>55</v>
+      </c>
+      <c r="F82" t="s">
+        <v>61</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+      <c r="H82" t="s">
+        <v>28</v>
+      </c>
+      <c r="I82" t="s">
+        <v>96</v>
+      </c>
+      <c r="J82" t="s">
         <v>30</v>
       </c>
-      <c r="B82" t="s">
-        <v>376</v>
-      </c>
-      <c r="C82" t="s">
-        <v>97</v>
-      </c>
-      <c r="D82" t="s">
-        <v>98</v>
-      </c>
-      <c r="E82" t="s">
-        <v>99</v>
-      </c>
-      <c r="F82" t="s">
-        <v>100</v>
-      </c>
-      <c r="G82">
-        <v>100</v>
-      </c>
-      <c r="H82" t="s">
-        <v>20</v>
-      </c>
-      <c r="I82" t="s">
-        <v>101</v>
-      </c>
-      <c r="J82" t="s">
-        <v>102</v>
-      </c>
       <c r="K82" t="s">
         <v>23</v>
       </c>
       <c r="L82">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
       </c>
       <c r="N82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
       </c>
       <c r="Q82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" t="b">
         <v>1</v>
@@ -7005,49 +7014,49 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B83" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C83" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D83" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E83" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F83" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G83">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H83" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I83" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J83" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
       </c>
       <c r="L83">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
       </c>
       <c r="N83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O83" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -7061,22 +7070,22 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B84" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C84" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D84" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E84" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F84" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G84">
         <v>500</v>
@@ -7088,13 +7097,13 @@
         <v>107</v>
       </c>
       <c r="J84" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
       </c>
       <c r="L84">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
@@ -7103,7 +7112,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -7117,40 +7126,40 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B85" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C85" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D85" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E85" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F85" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H85" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I85" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J85" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
       </c>
       <c r="L85">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
@@ -7159,13 +7168,13 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
       </c>
       <c r="Q85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" t="b">
         <v>1</v>
@@ -7173,40 +7182,40 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B86" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C86" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D86" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E86" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F86" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G86">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H86" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I86" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J86" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
       </c>
       <c r="L86">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
@@ -7215,13 +7224,13 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
       </c>
       <c r="Q86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" t="b">
         <v>1</v>
@@ -7229,40 +7238,40 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
+        <v>34</v>
+      </c>
+      <c r="B87" t="s">
+        <v>380</v>
+      </c>
+      <c r="C87" t="s">
+        <v>112</v>
+      </c>
+      <c r="D87" t="s">
+        <v>113</v>
+      </c>
+      <c r="E87" t="s">
+        <v>114</v>
+      </c>
+      <c r="F87" t="s">
+        <v>115</v>
+      </c>
+      <c r="G87">
+        <v>300</v>
+      </c>
+      <c r="H87" t="s">
         <v>35</v>
       </c>
-      <c r="B87" t="s">
-        <v>381</v>
-      </c>
-      <c r="C87" t="s">
-        <v>117</v>
-      </c>
-      <c r="D87" t="s">
-        <v>118</v>
-      </c>
-      <c r="E87" t="s">
-        <v>119</v>
-      </c>
-      <c r="F87" t="s">
-        <v>120</v>
-      </c>
-      <c r="G87">
-        <v>500</v>
-      </c>
-      <c r="H87" t="s">
-        <v>42</v>
-      </c>
       <c r="I87" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J87" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
       </c>
       <c r="L87">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
@@ -7271,7 +7280,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -7285,40 +7294,40 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B88" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C88" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D88" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E88" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F88" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G88">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H88" t="s">
         <v>42</v>
       </c>
       <c r="I88" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J88" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
@@ -7327,13 +7336,13 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
       </c>
       <c r="Q88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R88" t="b">
         <v>1</v>
@@ -7341,40 +7350,40 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B89" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C89" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D89" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E89" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F89" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G89">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H89" t="s">
         <v>42</v>
       </c>
       <c r="I89" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J89" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
@@ -7383,13 +7392,13 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
       </c>
       <c r="Q89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" t="b">
         <v>1</v>
@@ -7397,34 +7406,34 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B90" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C90" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D90" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E90" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F90" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G90">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H90" t="s">
         <v>42</v>
       </c>
       <c r="I90" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J90" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
@@ -7439,13 +7448,13 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
       </c>
       <c r="Q90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="b">
         <v>1</v>
@@ -7453,40 +7462,40 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B91" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C91" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D91" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E91" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F91" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G91">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H91" t="s">
         <v>42</v>
       </c>
       <c r="I91" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J91" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -7495,7 +7504,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -7509,40 +7518,40 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B92" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C92" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D92" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E92" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F92" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H92" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I92" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J92" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
       </c>
       <c r="L92">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -7551,7 +7560,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -7565,55 +7574,55 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B93" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C93" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D93" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E93" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F93" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G93">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H93" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I93" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J93" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
       </c>
       <c r="L93">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
       </c>
       <c r="Q93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
@@ -7621,10 +7630,10 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B94" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C94" t="s">
         <v>138</v>
@@ -7633,10 +7642,10 @@
         <v>139</v>
       </c>
       <c r="E94" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F94" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G94">
         <v>1000</v>
@@ -7660,10 +7669,10 @@
         <v>1</v>
       </c>
       <c r="N94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O94" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -7677,22 +7686,22 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B95" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C95" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D95" t="s">
         <v>139</v>
       </c>
       <c r="E95" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F95" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G95">
         <v>1000</v>
@@ -7704,7 +7713,7 @@
         <v>142</v>
       </c>
       <c r="J95" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
@@ -7719,7 +7728,7 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
@@ -7733,55 +7742,55 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B96" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C96" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D96" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E96" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F96" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G96">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H96" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I96" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J96" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
       </c>
       <c r="L96">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
       </c>
       <c r="Q96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" t="b">
         <v>1</v>
@@ -7789,55 +7798,55 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B97" t="s">
-        <v>645</v>
+        <v>390</v>
       </c>
       <c r="C97" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D97" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E97" t="s">
-        <v>646</v>
+        <v>151</v>
       </c>
       <c r="F97" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G97">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H97" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I97" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="J97" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="K97" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="L97">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
       </c>
       <c r="N97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>647</v>
+        <v>282</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
       </c>
       <c r="Q97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" t="b">
         <v>1</v>
@@ -7845,55 +7854,55 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B98" t="s">
-        <v>391</v>
+        <v>645</v>
       </c>
       <c r="C98" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D98" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E98" t="s">
-        <v>163</v>
+        <v>646</v>
       </c>
       <c r="F98" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G98">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H98" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I98" t="s">
-        <v>29</v>
+        <v>158</v>
       </c>
       <c r="J98" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K98" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="L98">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M98" t="b">
         <v>0</v>
       </c>
       <c r="N98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O98" t="s">
-        <v>283</v>
+        <v>647</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
       </c>
       <c r="Q98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="b">
         <v>1</v>
@@ -7901,34 +7910,34 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B99" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C99" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D99" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E99" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F99" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G99">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H99" t="s">
         <v>42</v>
       </c>
       <c r="I99" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J99" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="K99" t="s">
         <v>23</v>
@@ -7943,7 +7952,7 @@
         <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
@@ -7957,22 +7966,22 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B100" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C100" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D100" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E100" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F100" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="G100">
         <v>500</v>
@@ -7984,7 +7993,7 @@
         <v>21</v>
       </c>
       <c r="J100" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K100" t="s">
         <v>23</v>
@@ -7999,7 +8008,7 @@
         <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
@@ -8013,34 +8022,34 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B101" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C101" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D101" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E101" t="s">
-        <v>622</v>
+        <v>172</v>
       </c>
       <c r="F101" t="s">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="G101">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H101" t="s">
         <v>42</v>
       </c>
       <c r="I101" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J101" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="K101" t="s">
         <v>23</v>
@@ -8055,7 +8064,7 @@
         <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
@@ -8069,37 +8078,37 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
+        <v>49</v>
+      </c>
+      <c r="B102" t="s">
+        <v>394</v>
+      </c>
+      <c r="C102" t="s">
+        <v>174</v>
+      </c>
+      <c r="D102" t="s">
+        <v>175</v>
+      </c>
+      <c r="E102" t="s">
+        <v>622</v>
+      </c>
+      <c r="F102" t="s">
+        <v>176</v>
+      </c>
+      <c r="G102">
         <v>50</v>
       </c>
-      <c r="B102" t="s">
-        <v>395</v>
-      </c>
-      <c r="C102" t="s">
-        <v>178</v>
-      </c>
-      <c r="D102" t="s">
-        <v>179</v>
-      </c>
-      <c r="E102" t="s">
-        <v>180</v>
-      </c>
-      <c r="F102" t="s">
-        <v>181</v>
-      </c>
-      <c r="G102">
-        <v>12</v>
-      </c>
       <c r="H102" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I102" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="J102" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="K102" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="L102">
         <v>12</v>
@@ -8111,7 +8120,7 @@
         <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
@@ -8125,40 +8134,40 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B103" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C103" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D103" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E103" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F103" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G103">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H103" t="s">
-        <v>188</v>
+        <v>20</v>
       </c>
       <c r="I103" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="J103" t="s">
-        <v>552</v>
+        <v>182</v>
       </c>
       <c r="K103" t="s">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="L103">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M103" t="b">
         <v>0</v>
@@ -8167,7 +8176,7 @@
         <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
@@ -8181,40 +8190,40 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C104" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D104" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E104" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F104" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="G104">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H104" t="s">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="I104" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
       <c r="J104" t="s">
-        <v>182</v>
+        <v>552</v>
       </c>
       <c r="K104" t="s">
         <v>23</v>
       </c>
       <c r="L104">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M104" t="b">
         <v>0</v>
@@ -8223,7 +8232,7 @@
         <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
@@ -8237,40 +8246,40 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
+        <v>52</v>
+      </c>
+      <c r="B105" t="s">
+        <v>397</v>
+      </c>
+      <c r="C105" t="s">
+        <v>191</v>
+      </c>
+      <c r="D105" t="s">
+        <v>179</v>
+      </c>
+      <c r="E105" t="s">
+        <v>180</v>
+      </c>
+      <c r="F105" t="s">
+        <v>181</v>
+      </c>
+      <c r="G105">
+        <v>24</v>
+      </c>
+      <c r="H105" t="s">
+        <v>20</v>
+      </c>
+      <c r="I105" t="s">
         <v>53</v>
       </c>
-      <c r="B105" t="s">
-        <v>398</v>
-      </c>
-      <c r="C105" t="s">
-        <v>31</v>
-      </c>
-      <c r="D105" t="s">
-        <v>192</v>
-      </c>
-      <c r="E105" t="s">
-        <v>193</v>
-      </c>
-      <c r="F105" t="s">
-        <v>194</v>
-      </c>
-      <c r="G105">
-        <v>1.5</v>
-      </c>
-      <c r="H105" t="s">
-        <v>28</v>
-      </c>
-      <c r="I105" t="s">
-        <v>36</v>
-      </c>
       <c r="J105" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="K105" t="s">
         <v>23</v>
       </c>
       <c r="L105">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M105" t="b">
         <v>0</v>
@@ -8279,7 +8288,7 @@
         <v>1</v>
       </c>
       <c r="O105" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
@@ -8293,52 +8302,52 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B106" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C106" t="s">
-        <v>195</v>
+        <v>31</v>
       </c>
       <c r="D106" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E106" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F106" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G106">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H106" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I106" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J106" t="s">
-        <v>199</v>
+        <v>37</v>
       </c>
       <c r="K106" t="s">
         <v>23</v>
       </c>
       <c r="L106">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M106" t="b">
         <v>0</v>
       </c>
       <c r="N106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O106" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q106" t="b">
         <v>1</v>
@@ -8349,55 +8358,55 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B107" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C107" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="D107" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E107" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F107" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G107">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H107" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I107" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="J107" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="K107" t="s">
         <v>23</v>
       </c>
       <c r="L107">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M107" t="b">
         <v>0</v>
       </c>
       <c r="N107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O107" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" t="b">
         <v>1</v>
@@ -8405,40 +8414,40 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B108" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C108" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="D108" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E108" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F108" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G108">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H108" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I108" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="J108" t="s">
-        <v>66</v>
+        <v>190</v>
       </c>
       <c r="K108" t="s">
         <v>23</v>
       </c>
       <c r="L108">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M108" t="b">
         <v>0</v>
@@ -8447,7 +8456,7 @@
         <v>1</v>
       </c>
       <c r="O108" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P108" t="b">
         <v>1</v>
@@ -8461,19 +8470,19 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B109" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C109" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D109" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E109" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F109" t="s">
         <v>206</v>
@@ -8503,7 +8512,7 @@
         <v>1</v>
       </c>
       <c r="O109" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P109" t="b">
         <v>1</v>
@@ -8517,19 +8526,19 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B110" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C110" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D110" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E110" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F110" t="s">
         <v>206</v>
@@ -8550,7 +8559,7 @@
         <v>23</v>
       </c>
       <c r="L110">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M110" t="b">
         <v>0</v>
@@ -8559,7 +8568,7 @@
         <v>1</v>
       </c>
       <c r="O110" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P110" t="b">
         <v>1</v>
@@ -8573,34 +8582,34 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B111" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C111" t="s">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="D111" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E111" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F111" t="s">
-        <v>56</v>
+        <v>206</v>
       </c>
       <c r="G111">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H111" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I111" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="J111" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K111" t="s">
         <v>23</v>
@@ -8615,13 +8624,13 @@
         <v>1</v>
       </c>
       <c r="O111" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P111" t="b">
         <v>1</v>
       </c>
       <c r="Q111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R111" t="b">
         <v>1</v>
@@ -8629,34 +8638,34 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B112" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C112" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D112" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="E112" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="F112" t="s">
-        <v>214</v>
+        <v>56</v>
       </c>
       <c r="G112">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H112" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I112" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J112" t="s">
-        <v>553</v>
+        <v>148</v>
       </c>
       <c r="K112" t="s">
         <v>23</v>
@@ -8671,7 +8680,7 @@
         <v>1</v>
       </c>
       <c r="O112" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P112" t="b">
         <v>1</v>
@@ -8685,49 +8694,49 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B113" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C113" t="s">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="D113" t="s">
-        <v>216</v>
+        <v>81</v>
       </c>
       <c r="E113" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="F113" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G113">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H113" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I113" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J113" t="s">
-        <v>215</v>
+        <v>553</v>
       </c>
       <c r="K113" t="s">
         <v>23</v>
       </c>
       <c r="L113">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M113" t="b">
         <v>0</v>
       </c>
       <c r="N113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O113" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P113" t="b">
         <v>1</v>
@@ -8741,22 +8750,22 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B114" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C114" t="s">
         <v>215</v>
       </c>
       <c r="D114" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E114" t="s">
         <v>217</v>
       </c>
       <c r="F114" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G114">
         <v>20</v>
@@ -8783,13 +8792,13 @@
         <v>0</v>
       </c>
       <c r="O114" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P114" t="b">
         <v>1</v>
       </c>
       <c r="Q114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R114" t="b">
         <v>1</v>
@@ -8797,49 +8806,49 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B115" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C115" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D115" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="E115" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F115" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="G115">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H115" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I115" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J115" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K115" t="s">
         <v>23</v>
       </c>
       <c r="L115">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M115" t="b">
         <v>0</v>
       </c>
       <c r="N115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O115" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P115" t="b">
         <v>1</v>
@@ -8853,34 +8862,34 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B116" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C116" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D116" t="s">
         <v>200</v>
       </c>
       <c r="E116" t="s">
-        <v>32</v>
+        <v>201</v>
       </c>
       <c r="F116" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="G116">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H116" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I116" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J116" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="K116" t="s">
         <v>23</v>
@@ -8895,7 +8904,7 @@
         <v>1</v>
       </c>
       <c r="O116" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P116" t="b">
         <v>1</v>
@@ -8909,40 +8918,40 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B117" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C117" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D117" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="E117" t="s">
-        <v>227</v>
+        <v>32</v>
       </c>
       <c r="F117" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G117">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H117" t="s">
         <v>42</v>
       </c>
       <c r="I117" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J117" t="s">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="K117" t="s">
         <v>23</v>
       </c>
       <c r="L117">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M117" t="b">
         <v>0</v>
@@ -8951,13 +8960,13 @@
         <v>1</v>
       </c>
       <c r="O117" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P117" t="b">
         <v>1</v>
       </c>
       <c r="Q117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R117" t="b">
         <v>1</v>
@@ -8965,40 +8974,40 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B118" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C118" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
       <c r="D118" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E118" t="s">
         <v>227</v>
       </c>
       <c r="F118" t="s">
-        <v>47</v>
+        <v>228</v>
       </c>
       <c r="G118">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H118" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I118" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J118" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K118" t="s">
         <v>23</v>
       </c>
       <c r="L118">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M118" t="b">
         <v>0</v>
@@ -9007,7 +9016,7 @@
         <v>1</v>
       </c>
       <c r="O118" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P118" t="b">
         <v>1</v>
@@ -9021,40 +9030,40 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B119" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C119" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D119" t="s">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="E119" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F119" t="s">
-        <v>194</v>
+        <v>47</v>
       </c>
       <c r="G119">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H119" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I119" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J119" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K119" t="s">
         <v>23</v>
       </c>
       <c r="L119">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M119" t="b">
         <v>0</v>
@@ -9063,13 +9072,13 @@
         <v>1</v>
       </c>
       <c r="O119" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P119" t="b">
         <v>1</v>
       </c>
       <c r="Q119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R119" t="b">
         <v>1</v>
@@ -9077,34 +9086,34 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B120" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C120" t="s">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="D120" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E120" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F120" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G120">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H120" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I120" t="s">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="J120" t="s">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="K120" t="s">
         <v>23</v>
@@ -9119,7 +9128,7 @@
         <v>1</v>
       </c>
       <c r="O120" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P120" t="b">
         <v>1</v>
@@ -9133,10 +9142,10 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B121" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C121" t="s">
         <v>184</v>
@@ -9145,13 +9154,13 @@
         <v>200</v>
       </c>
       <c r="E121" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F121" t="s">
         <v>202</v>
       </c>
       <c r="G121">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H121" t="s">
         <v>35</v>
@@ -9175,7 +9184,7 @@
         <v>1</v>
       </c>
       <c r="O121" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P121" t="b">
         <v>1</v>
@@ -9189,10 +9198,10 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B122" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C122" t="s">
         <v>184</v>
@@ -9207,7 +9216,7 @@
         <v>202</v>
       </c>
       <c r="G122">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H122" t="s">
         <v>35</v>
@@ -9231,7 +9240,7 @@
         <v>1</v>
       </c>
       <c r="O122" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P122" t="b">
         <v>1</v>
@@ -9245,41 +9254,41 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B123" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C123" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="D123" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="E123" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F123" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="G123">
+        <v>250</v>
+      </c>
+      <c r="H123" t="s">
+        <v>35</v>
+      </c>
+      <c r="I123" t="s">
+        <v>189</v>
+      </c>
+      <c r="J123" t="s">
+        <v>190</v>
+      </c>
+      <c r="K123" t="s">
+        <v>23</v>
+      </c>
+      <c r="L123">
         <v>6</v>
       </c>
-      <c r="H123" t="s">
-        <v>20</v>
-      </c>
-      <c r="I123" t="s">
-        <v>237</v>
-      </c>
-      <c r="J123" t="s">
-        <v>233</v>
-      </c>
-      <c r="K123" t="s">
-        <v>23</v>
-      </c>
-      <c r="L123">
-        <v>1</v>
-      </c>
       <c r="M123" t="b">
         <v>0</v>
       </c>
@@ -9287,13 +9296,13 @@
         <v>1</v>
       </c>
       <c r="O123" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R123" t="b">
         <v>1</v>
@@ -9301,57 +9310,113 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B124" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C124" t="s">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="D124" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="E124" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="F124" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G124">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H124" t="s">
         <v>20</v>
       </c>
       <c r="I124" t="s">
+        <v>237</v>
+      </c>
+      <c r="J124" t="s">
+        <v>233</v>
+      </c>
+      <c r="K124" t="s">
+        <v>23</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+      <c r="M124" t="b">
+        <v>0</v>
+      </c>
+      <c r="N124" t="b">
+        <v>1</v>
+      </c>
+      <c r="O124" t="s">
+        <v>308</v>
+      </c>
+      <c r="P124" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="b">
+        <v>1</v>
+      </c>
+      <c r="R124" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>72</v>
+      </c>
+      <c r="B125" t="s">
+        <v>417</v>
+      </c>
+      <c r="C125" t="s">
+        <v>195</v>
+      </c>
+      <c r="D125" t="s">
+        <v>196</v>
+      </c>
+      <c r="E125" t="s">
+        <v>197</v>
+      </c>
+      <c r="F125" t="s">
+        <v>238</v>
+      </c>
+      <c r="G125">
+        <v>4</v>
+      </c>
+      <c r="H125" t="s">
+        <v>20</v>
+      </c>
+      <c r="I125" t="s">
         <v>21</v>
       </c>
-      <c r="J124" t="s">
+      <c r="J125" t="s">
         <v>199</v>
       </c>
-      <c r="K124" t="s">
-        <v>23</v>
-      </c>
-      <c r="L124">
+      <c r="K125" t="s">
+        <v>23</v>
+      </c>
+      <c r="L125">
         <v>10</v>
       </c>
-      <c r="M124" t="b">
-        <v>0</v>
-      </c>
-      <c r="N124" t="b">
-        <v>0</v>
-      </c>
-      <c r="O124" t="s">
+      <c r="M125" t="b">
+        <v>0</v>
+      </c>
+      <c r="N125" t="b">
+        <v>0</v>
+      </c>
+      <c r="O125" t="s">
         <v>309</v>
       </c>
-      <c r="P124" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q124" t="b">
-        <v>1</v>
-      </c>
-      <c r="R124" t="b">
+      <c r="P125" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q125" t="b">
+        <v>1</v>
+      </c>
+      <c r="R125" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDFF8B5-48CA-4367-BEE1-B20F7058E0B6}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C037E1-6DD7-4290-9103-8949135E5CF9}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="73" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="74" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="677">
   <si>
     <t>Codigo</t>
   </si>
@@ -2045,6 +2045,18 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7798174970016.png</t>
+  </si>
+  <si>
+    <t>7790520995285</t>
+  </si>
+  <si>
+    <t>de ambientes</t>
+  </si>
+  <si>
+    <t>Lysoform</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7790520995285.png</t>
   </si>
 </sst>
 </file>
@@ -2396,8 +2408,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6835F66E-7A5E-426E-A87E-9AB71E9F7D26}">
-  <dimension ref="A1:R125"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D760988-B621-47C2-9476-8EE2B22FA18B}">
+  <dimension ref="A1:R126"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -6454,40 +6466,40 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="B73" t="s">
-        <v>584</v>
+        <v>673</v>
       </c>
       <c r="C73" t="s">
-        <v>585</v>
+        <v>184</v>
       </c>
       <c r="D73" t="s">
-        <v>541</v>
+        <v>674</v>
       </c>
       <c r="E73" t="s">
-        <v>586</v>
+        <v>32</v>
       </c>
       <c r="F73" t="s">
-        <v>517</v>
+        <v>675</v>
       </c>
       <c r="G73">
-        <v>2</v>
+        <v>360</v>
       </c>
       <c r="H73" t="s">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="I73" t="s">
-        <v>490</v>
+        <v>189</v>
       </c>
       <c r="J73" t="s">
-        <v>587</v>
+        <v>552</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
       </c>
       <c r="L73">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
@@ -6496,7 +6508,7 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>588</v>
+        <v>676</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
@@ -6510,37 +6522,37 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B74" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C74" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="D74" t="s">
-        <v>591</v>
+        <v>541</v>
       </c>
       <c r="E74" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="F74" t="s">
-        <v>593</v>
+        <v>517</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H74" t="s">
         <v>20</v>
       </c>
       <c r="I74" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="J74" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="K74" t="s">
-        <v>595</v>
+        <v>23</v>
       </c>
       <c r="L74">
         <v>12</v>
@@ -6549,10 +6561,10 @@
         <v>0</v>
       </c>
       <c r="N74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -6566,49 +6578,49 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B75" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="C75" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="D75" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="E75" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="F75" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="G75">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H75" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I75" t="s">
         <v>53</v>
       </c>
       <c r="J75" t="s">
-        <v>76</v>
+        <v>594</v>
       </c>
       <c r="K75" t="s">
-        <v>23</v>
+        <v>595</v>
       </c>
       <c r="L75">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
       </c>
       <c r="N75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -6622,49 +6634,49 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B76" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="C76" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="D76" t="s">
-        <v>172</v>
+        <v>598</v>
       </c>
       <c r="E76" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="F76" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="H76" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I76" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J76" t="s">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
       </c>
       <c r="N76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -6673,27 +6685,27 @@
         <v>1</v>
       </c>
       <c r="R76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B77" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C77" t="s">
-        <v>607</v>
+        <v>195</v>
       </c>
       <c r="D77" t="s">
-        <v>608</v>
+        <v>172</v>
       </c>
       <c r="E77" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="F77" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -6702,16 +6714,16 @@
         <v>20</v>
       </c>
       <c r="I77" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J77" t="s">
-        <v>611</v>
+        <v>243</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
       </c>
       <c r="L77">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
@@ -6720,7 +6732,7 @@
         <v>0</v>
       </c>
       <c r="O77" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6729,39 +6741,39 @@
         <v>1</v>
       </c>
       <c r="R77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B78" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="C78" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="D78" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="E78" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="F78" t="s">
-        <v>111</v>
+        <v>610</v>
       </c>
       <c r="G78">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H78" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I78" t="s">
         <v>490</v>
       </c>
       <c r="J78" t="s">
-        <v>576</v>
+        <v>611</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
@@ -6773,10 +6785,10 @@
         <v>0</v>
       </c>
       <c r="N78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O78" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6790,25 +6802,25 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B79" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C79" t="s">
-        <v>174</v>
+        <v>614</v>
       </c>
       <c r="D79" t="s">
-        <v>175</v>
+        <v>615</v>
       </c>
       <c r="E79" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="F79" t="s">
-        <v>620</v>
+        <v>111</v>
       </c>
       <c r="G79">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H79" t="s">
         <v>42</v>
@@ -6817,13 +6829,13 @@
         <v>490</v>
       </c>
       <c r="J79" t="s">
-        <v>177</v>
+        <v>576</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -6832,7 +6844,7 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6846,40 +6858,40 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="B80" t="s">
-        <v>373</v>
+        <v>618</v>
       </c>
       <c r="C80" t="s">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="D80" t="s">
-        <v>89</v>
+        <v>175</v>
       </c>
       <c r="E80" t="s">
-        <v>90</v>
+        <v>619</v>
       </c>
       <c r="F80" t="s">
-        <v>91</v>
+        <v>620</v>
       </c>
       <c r="G80">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="H80" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I80" t="s">
-        <v>36</v>
+        <v>490</v>
       </c>
       <c r="J80" t="s">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
@@ -6888,13 +6900,13 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>265</v>
+        <v>621</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
       </c>
       <c r="Q80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" t="b">
         <v>1</v>
@@ -6902,40 +6914,40 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B81" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C81" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D81" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E81" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F81" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G81">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H81" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I81" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J81" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
@@ -6944,7 +6956,7 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6958,41 +6970,41 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B82" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C82" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D82" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E82" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F82" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H82" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I82" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J82" t="s">
+        <v>66</v>
+      </c>
+      <c r="K82" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82">
         <v>30</v>
       </c>
-      <c r="K82" t="s">
-        <v>23</v>
-      </c>
-      <c r="L82">
-        <v>12</v>
-      </c>
       <c r="M82" t="b">
         <v>0</v>
       </c>
@@ -7000,13 +7012,13 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
       </c>
       <c r="Q82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" t="b">
         <v>1</v>
@@ -7014,55 +7026,55 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
+        <v>29</v>
+      </c>
+      <c r="B83" t="s">
+        <v>375</v>
+      </c>
+      <c r="C83" t="s">
+        <v>24</v>
+      </c>
+      <c r="D83" t="s">
+        <v>54</v>
+      </c>
+      <c r="E83" t="s">
+        <v>55</v>
+      </c>
+      <c r="F83" t="s">
+        <v>61</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+      <c r="H83" t="s">
+        <v>28</v>
+      </c>
+      <c r="I83" t="s">
+        <v>96</v>
+      </c>
+      <c r="J83" t="s">
         <v>30</v>
       </c>
-      <c r="B83" t="s">
-        <v>376</v>
-      </c>
-      <c r="C83" t="s">
-        <v>97</v>
-      </c>
-      <c r="D83" t="s">
-        <v>98</v>
-      </c>
-      <c r="E83" t="s">
-        <v>99</v>
-      </c>
-      <c r="F83" t="s">
-        <v>100</v>
-      </c>
-      <c r="G83">
-        <v>100</v>
-      </c>
-      <c r="H83" t="s">
-        <v>20</v>
-      </c>
-      <c r="I83" t="s">
-        <v>101</v>
-      </c>
-      <c r="J83" t="s">
-        <v>102</v>
-      </c>
       <c r="K83" t="s">
         <v>23</v>
       </c>
       <c r="L83">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
       </c>
       <c r="N83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
       </c>
       <c r="Q83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" t="b">
         <v>1</v>
@@ -7070,49 +7082,49 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B84" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C84" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D84" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E84" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F84" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G84">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H84" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I84" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J84" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
       </c>
       <c r="L84">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
       </c>
       <c r="N84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -7126,22 +7138,22 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B85" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C85" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D85" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E85" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F85" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G85">
         <v>500</v>
@@ -7153,13 +7165,13 @@
         <v>107</v>
       </c>
       <c r="J85" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
       </c>
       <c r="L85">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
@@ -7168,7 +7180,7 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -7182,40 +7194,40 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B86" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C86" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D86" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E86" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F86" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G86">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H86" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I86" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J86" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
       </c>
       <c r="L86">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
@@ -7224,13 +7236,13 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
       </c>
       <c r="Q86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R86" t="b">
         <v>1</v>
@@ -7238,40 +7250,40 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B87" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C87" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D87" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E87" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F87" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G87">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H87" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I87" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J87" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
       </c>
       <c r="L87">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
@@ -7280,13 +7292,13 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
       </c>
       <c r="Q87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87" t="b">
         <v>1</v>
@@ -7294,40 +7306,40 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
+        <v>34</v>
+      </c>
+      <c r="B88" t="s">
+        <v>380</v>
+      </c>
+      <c r="C88" t="s">
+        <v>112</v>
+      </c>
+      <c r="D88" t="s">
+        <v>113</v>
+      </c>
+      <c r="E88" t="s">
+        <v>114</v>
+      </c>
+      <c r="F88" t="s">
+        <v>115</v>
+      </c>
+      <c r="G88">
+        <v>300</v>
+      </c>
+      <c r="H88" t="s">
         <v>35</v>
       </c>
-      <c r="B88" t="s">
-        <v>381</v>
-      </c>
-      <c r="C88" t="s">
-        <v>117</v>
-      </c>
-      <c r="D88" t="s">
-        <v>118</v>
-      </c>
-      <c r="E88" t="s">
-        <v>119</v>
-      </c>
-      <c r="F88" t="s">
-        <v>120</v>
-      </c>
-      <c r="G88">
-        <v>500</v>
-      </c>
-      <c r="H88" t="s">
-        <v>42</v>
-      </c>
       <c r="I88" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J88" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
@@ -7336,7 +7348,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -7350,40 +7362,40 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B89" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C89" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D89" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E89" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F89" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G89">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H89" t="s">
         <v>42</v>
       </c>
       <c r="I89" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J89" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
@@ -7392,13 +7404,13 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
       </c>
       <c r="Q89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R89" t="b">
         <v>1</v>
@@ -7406,40 +7418,40 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B90" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C90" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D90" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E90" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F90" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G90">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H90" t="s">
         <v>42</v>
       </c>
       <c r="I90" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J90" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
       </c>
       <c r="L90">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -7448,13 +7460,13 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
       </c>
       <c r="Q90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" t="b">
         <v>1</v>
@@ -7462,34 +7474,34 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B91" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C91" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D91" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E91" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F91" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G91">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H91" t="s">
         <v>42</v>
       </c>
       <c r="I91" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J91" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
@@ -7504,13 +7516,13 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
       </c>
       <c r="Q91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R91" t="b">
         <v>1</v>
@@ -7518,40 +7530,40 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B92" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C92" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D92" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E92" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F92" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G92">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H92" t="s">
         <v>42</v>
       </c>
       <c r="I92" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J92" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
       </c>
       <c r="L92">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -7560,7 +7572,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -7574,40 +7586,40 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B93" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C93" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D93" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E93" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F93" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G93">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H93" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I93" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J93" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
       </c>
       <c r="L93">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -7616,7 +7628,7 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
@@ -7630,55 +7642,55 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B94" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C94" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D94" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E94" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F94" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G94">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H94" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I94" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J94" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
       </c>
       <c r="L94">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
       </c>
       <c r="Q94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94" t="b">
         <v>1</v>
@@ -7686,10 +7698,10 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B95" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C95" t="s">
         <v>138</v>
@@ -7698,10 +7710,10 @@
         <v>139</v>
       </c>
       <c r="E95" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F95" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G95">
         <v>1000</v>
@@ -7725,10 +7737,10 @@
         <v>1</v>
       </c>
       <c r="N95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O95" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
@@ -7742,22 +7754,22 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B96" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C96" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D96" t="s">
         <v>139</v>
       </c>
       <c r="E96" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F96" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G96">
         <v>1000</v>
@@ -7769,7 +7781,7 @@
         <v>142</v>
       </c>
       <c r="J96" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
@@ -7784,7 +7796,7 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
@@ -7798,55 +7810,55 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B97" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C97" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D97" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E97" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F97" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G97">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H97" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I97" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J97" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K97" t="s">
         <v>23</v>
       </c>
       <c r="L97">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
       </c>
       <c r="Q97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" t="b">
         <v>1</v>
@@ -7854,55 +7866,55 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B98" t="s">
-        <v>645</v>
+        <v>390</v>
       </c>
       <c r="C98" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D98" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E98" t="s">
-        <v>646</v>
+        <v>151</v>
       </c>
       <c r="F98" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G98">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H98" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I98" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="J98" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="K98" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="L98">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M98" t="b">
         <v>0</v>
       </c>
       <c r="N98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>647</v>
+        <v>282</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
       </c>
       <c r="Q98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" t="b">
         <v>1</v>
@@ -7910,55 +7922,55 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B99" t="s">
-        <v>391</v>
+        <v>645</v>
       </c>
       <c r="C99" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D99" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E99" t="s">
-        <v>163</v>
+        <v>646</v>
       </c>
       <c r="F99" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G99">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H99" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I99" t="s">
-        <v>29</v>
+        <v>158</v>
       </c>
       <c r="J99" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K99" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="L99">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M99" t="b">
         <v>0</v>
       </c>
       <c r="N99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O99" t="s">
-        <v>283</v>
+        <v>647</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
       </c>
       <c r="Q99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R99" t="b">
         <v>1</v>
@@ -7966,34 +7978,34 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B100" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C100" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D100" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E100" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F100" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G100">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H100" t="s">
         <v>42</v>
       </c>
       <c r="I100" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J100" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="K100" t="s">
         <v>23</v>
@@ -8008,7 +8020,7 @@
         <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
@@ -8022,22 +8034,22 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B101" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C101" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D101" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E101" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F101" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="G101">
         <v>500</v>
@@ -8049,7 +8061,7 @@
         <v>21</v>
       </c>
       <c r="J101" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K101" t="s">
         <v>23</v>
@@ -8064,7 +8076,7 @@
         <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
@@ -8078,34 +8090,34 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B102" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C102" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D102" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E102" t="s">
-        <v>622</v>
+        <v>172</v>
       </c>
       <c r="F102" t="s">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="G102">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H102" t="s">
         <v>42</v>
       </c>
       <c r="I102" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J102" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="K102" t="s">
         <v>23</v>
@@ -8120,7 +8132,7 @@
         <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
@@ -8134,37 +8146,37 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
+        <v>49</v>
+      </c>
+      <c r="B103" t="s">
+        <v>394</v>
+      </c>
+      <c r="C103" t="s">
+        <v>174</v>
+      </c>
+      <c r="D103" t="s">
+        <v>175</v>
+      </c>
+      <c r="E103" t="s">
+        <v>622</v>
+      </c>
+      <c r="F103" t="s">
+        <v>176</v>
+      </c>
+      <c r="G103">
         <v>50</v>
       </c>
-      <c r="B103" t="s">
-        <v>395</v>
-      </c>
-      <c r="C103" t="s">
-        <v>178</v>
-      </c>
-      <c r="D103" t="s">
-        <v>179</v>
-      </c>
-      <c r="E103" t="s">
-        <v>180</v>
-      </c>
-      <c r="F103" t="s">
-        <v>181</v>
-      </c>
-      <c r="G103">
-        <v>12</v>
-      </c>
       <c r="H103" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I103" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="J103" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="K103" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="L103">
         <v>12</v>
@@ -8176,7 +8188,7 @@
         <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
@@ -8190,40 +8202,40 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B104" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C104" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D104" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E104" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F104" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G104">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H104" t="s">
-        <v>188</v>
+        <v>20</v>
       </c>
       <c r="I104" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="J104" t="s">
-        <v>552</v>
+        <v>182</v>
       </c>
       <c r="K104" t="s">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="L104">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M104" t="b">
         <v>0</v>
@@ -8232,7 +8244,7 @@
         <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
@@ -8246,40 +8258,40 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B105" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C105" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D105" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E105" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F105" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="G105">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H105" t="s">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="I105" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
       <c r="J105" t="s">
-        <v>182</v>
+        <v>552</v>
       </c>
       <c r="K105" t="s">
         <v>23</v>
       </c>
       <c r="L105">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M105" t="b">
         <v>0</v>
@@ -8288,7 +8300,7 @@
         <v>1</v>
       </c>
       <c r="O105" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
@@ -8302,40 +8314,40 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
+        <v>52</v>
+      </c>
+      <c r="B106" t="s">
+        <v>397</v>
+      </c>
+      <c r="C106" t="s">
+        <v>191</v>
+      </c>
+      <c r="D106" t="s">
+        <v>179</v>
+      </c>
+      <c r="E106" t="s">
+        <v>180</v>
+      </c>
+      <c r="F106" t="s">
+        <v>181</v>
+      </c>
+      <c r="G106">
+        <v>24</v>
+      </c>
+      <c r="H106" t="s">
+        <v>20</v>
+      </c>
+      <c r="I106" t="s">
         <v>53</v>
       </c>
-      <c r="B106" t="s">
-        <v>398</v>
-      </c>
-      <c r="C106" t="s">
-        <v>31</v>
-      </c>
-      <c r="D106" t="s">
-        <v>192</v>
-      </c>
-      <c r="E106" t="s">
-        <v>193</v>
-      </c>
-      <c r="F106" t="s">
-        <v>194</v>
-      </c>
-      <c r="G106">
-        <v>1.5</v>
-      </c>
-      <c r="H106" t="s">
-        <v>28</v>
-      </c>
-      <c r="I106" t="s">
-        <v>36</v>
-      </c>
       <c r="J106" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="K106" t="s">
         <v>23</v>
       </c>
       <c r="L106">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M106" t="b">
         <v>0</v>
@@ -8344,7 +8356,7 @@
         <v>1</v>
       </c>
       <c r="O106" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
@@ -8358,52 +8370,52 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B107" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C107" t="s">
-        <v>195</v>
+        <v>31</v>
       </c>
       <c r="D107" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E107" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F107" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G107">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H107" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I107" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J107" t="s">
-        <v>199</v>
+        <v>37</v>
       </c>
       <c r="K107" t="s">
         <v>23</v>
       </c>
       <c r="L107">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M107" t="b">
         <v>0</v>
       </c>
       <c r="N107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O107" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q107" t="b">
         <v>1</v>
@@ -8414,55 +8426,55 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B108" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C108" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="D108" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E108" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F108" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G108">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H108" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I108" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="J108" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="K108" t="s">
         <v>23</v>
       </c>
       <c r="L108">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M108" t="b">
         <v>0</v>
       </c>
       <c r="N108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O108" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R108" t="b">
         <v>1</v>
@@ -8470,40 +8482,40 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B109" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C109" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="D109" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E109" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F109" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G109">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H109" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I109" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="J109" t="s">
-        <v>66</v>
+        <v>190</v>
       </c>
       <c r="K109" t="s">
         <v>23</v>
       </c>
       <c r="L109">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M109" t="b">
         <v>0</v>
@@ -8512,7 +8524,7 @@
         <v>1</v>
       </c>
       <c r="O109" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P109" t="b">
         <v>1</v>
@@ -8526,19 +8538,19 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B110" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C110" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D110" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E110" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F110" t="s">
         <v>206</v>
@@ -8568,7 +8580,7 @@
         <v>1</v>
       </c>
       <c r="O110" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P110" t="b">
         <v>1</v>
@@ -8582,19 +8594,19 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B111" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C111" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D111" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E111" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F111" t="s">
         <v>206</v>
@@ -8615,7 +8627,7 @@
         <v>23</v>
       </c>
       <c r="L111">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M111" t="b">
         <v>0</v>
@@ -8624,7 +8636,7 @@
         <v>1</v>
       </c>
       <c r="O111" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P111" t="b">
         <v>1</v>
@@ -8638,34 +8650,34 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B112" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C112" t="s">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="D112" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E112" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F112" t="s">
-        <v>56</v>
+        <v>206</v>
       </c>
       <c r="G112">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H112" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I112" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="J112" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K112" t="s">
         <v>23</v>
@@ -8680,13 +8692,13 @@
         <v>1</v>
       </c>
       <c r="O112" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P112" t="b">
         <v>1</v>
       </c>
       <c r="Q112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R112" t="b">
         <v>1</v>
@@ -8694,34 +8706,34 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B113" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C113" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D113" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="E113" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="F113" t="s">
-        <v>214</v>
+        <v>56</v>
       </c>
       <c r="G113">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H113" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I113" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J113" t="s">
-        <v>553</v>
+        <v>148</v>
       </c>
       <c r="K113" t="s">
         <v>23</v>
@@ -8736,7 +8748,7 @@
         <v>1</v>
       </c>
       <c r="O113" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P113" t="b">
         <v>1</v>
@@ -8750,49 +8762,49 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B114" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C114" t="s">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="D114" t="s">
-        <v>216</v>
+        <v>81</v>
       </c>
       <c r="E114" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="F114" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G114">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H114" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I114" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J114" t="s">
-        <v>215</v>
+        <v>553</v>
       </c>
       <c r="K114" t="s">
         <v>23</v>
       </c>
       <c r="L114">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M114" t="b">
         <v>0</v>
       </c>
       <c r="N114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O114" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P114" t="b">
         <v>1</v>
@@ -8806,22 +8818,22 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B115" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C115" t="s">
         <v>215</v>
       </c>
       <c r="D115" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E115" t="s">
         <v>217</v>
       </c>
       <c r="F115" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G115">
         <v>20</v>
@@ -8848,13 +8860,13 @@
         <v>0</v>
       </c>
       <c r="O115" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P115" t="b">
         <v>1</v>
       </c>
       <c r="Q115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R115" t="b">
         <v>1</v>
@@ -8862,49 +8874,49 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B116" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C116" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D116" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="E116" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F116" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="G116">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H116" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I116" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J116" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K116" t="s">
         <v>23</v>
       </c>
       <c r="L116">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M116" t="b">
         <v>0</v>
       </c>
       <c r="N116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O116" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P116" t="b">
         <v>1</v>
@@ -8918,34 +8930,34 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B117" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C117" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D117" t="s">
         <v>200</v>
       </c>
       <c r="E117" t="s">
-        <v>32</v>
+        <v>201</v>
       </c>
       <c r="F117" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="G117">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H117" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I117" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J117" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="K117" t="s">
         <v>23</v>
@@ -8960,7 +8972,7 @@
         <v>1</v>
       </c>
       <c r="O117" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P117" t="b">
         <v>1</v>
@@ -8974,40 +8986,40 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B118" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C118" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D118" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="E118" t="s">
-        <v>227</v>
+        <v>32</v>
       </c>
       <c r="F118" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G118">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H118" t="s">
         <v>42</v>
       </c>
       <c r="I118" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J118" t="s">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="K118" t="s">
         <v>23</v>
       </c>
       <c r="L118">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M118" t="b">
         <v>0</v>
@@ -9016,13 +9028,13 @@
         <v>1</v>
       </c>
       <c r="O118" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P118" t="b">
         <v>1</v>
       </c>
       <c r="Q118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R118" t="b">
         <v>1</v>
@@ -9030,40 +9042,40 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B119" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C119" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
       <c r="D119" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E119" t="s">
         <v>227</v>
       </c>
       <c r="F119" t="s">
-        <v>47</v>
+        <v>228</v>
       </c>
       <c r="G119">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H119" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I119" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J119" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K119" t="s">
         <v>23</v>
       </c>
       <c r="L119">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M119" t="b">
         <v>0</v>
@@ -9072,7 +9084,7 @@
         <v>1</v>
       </c>
       <c r="O119" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P119" t="b">
         <v>1</v>
@@ -9086,40 +9098,40 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B120" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C120" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D120" t="s">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="E120" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F120" t="s">
-        <v>194</v>
+        <v>47</v>
       </c>
       <c r="G120">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H120" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I120" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J120" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K120" t="s">
         <v>23</v>
       </c>
       <c r="L120">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M120" t="b">
         <v>0</v>
@@ -9128,13 +9140,13 @@
         <v>1</v>
       </c>
       <c r="O120" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P120" t="b">
         <v>1</v>
       </c>
       <c r="Q120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R120" t="b">
         <v>1</v>
@@ -9142,34 +9154,34 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B121" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C121" t="s">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="D121" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E121" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F121" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G121">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H121" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I121" t="s">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="J121" t="s">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="K121" t="s">
         <v>23</v>
@@ -9184,7 +9196,7 @@
         <v>1</v>
       </c>
       <c r="O121" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P121" t="b">
         <v>1</v>
@@ -9198,10 +9210,10 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B122" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C122" t="s">
         <v>184</v>
@@ -9210,13 +9222,13 @@
         <v>200</v>
       </c>
       <c r="E122" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F122" t="s">
         <v>202</v>
       </c>
       <c r="G122">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H122" t="s">
         <v>35</v>
@@ -9240,7 +9252,7 @@
         <v>1</v>
       </c>
       <c r="O122" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P122" t="b">
         <v>1</v>
@@ -9254,10 +9266,10 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B123" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C123" t="s">
         <v>184</v>
@@ -9272,7 +9284,7 @@
         <v>202</v>
       </c>
       <c r="G123">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H123" t="s">
         <v>35</v>
@@ -9296,7 +9308,7 @@
         <v>1</v>
       </c>
       <c r="O123" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P123" t="b">
         <v>1</v>
@@ -9310,41 +9322,41 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B124" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C124" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="D124" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="E124" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F124" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="G124">
+        <v>250</v>
+      </c>
+      <c r="H124" t="s">
+        <v>35</v>
+      </c>
+      <c r="I124" t="s">
+        <v>189</v>
+      </c>
+      <c r="J124" t="s">
+        <v>190</v>
+      </c>
+      <c r="K124" t="s">
+        <v>23</v>
+      </c>
+      <c r="L124">
         <v>6</v>
       </c>
-      <c r="H124" t="s">
-        <v>20</v>
-      </c>
-      <c r="I124" t="s">
-        <v>237</v>
-      </c>
-      <c r="J124" t="s">
-        <v>233</v>
-      </c>
-      <c r="K124" t="s">
-        <v>23</v>
-      </c>
-      <c r="L124">
-        <v>1</v>
-      </c>
       <c r="M124" t="b">
         <v>0</v>
       </c>
@@ -9352,13 +9364,13 @@
         <v>1</v>
       </c>
       <c r="O124" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R124" t="b">
         <v>1</v>
@@ -9366,57 +9378,113 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B125" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C125" t="s">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="D125" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="E125" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="F125" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G125">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H125" t="s">
         <v>20</v>
       </c>
       <c r="I125" t="s">
+        <v>237</v>
+      </c>
+      <c r="J125" t="s">
+        <v>233</v>
+      </c>
+      <c r="K125" t="s">
+        <v>23</v>
+      </c>
+      <c r="L125">
+        <v>1</v>
+      </c>
+      <c r="M125" t="b">
+        <v>0</v>
+      </c>
+      <c r="N125" t="b">
+        <v>1</v>
+      </c>
+      <c r="O125" t="s">
+        <v>308</v>
+      </c>
+      <c r="P125" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="b">
+        <v>1</v>
+      </c>
+      <c r="R125" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>72</v>
+      </c>
+      <c r="B126" t="s">
+        <v>417</v>
+      </c>
+      <c r="C126" t="s">
+        <v>195</v>
+      </c>
+      <c r="D126" t="s">
+        <v>196</v>
+      </c>
+      <c r="E126" t="s">
+        <v>197</v>
+      </c>
+      <c r="F126" t="s">
+        <v>238</v>
+      </c>
+      <c r="G126">
+        <v>4</v>
+      </c>
+      <c r="H126" t="s">
+        <v>20</v>
+      </c>
+      <c r="I126" t="s">
         <v>21</v>
       </c>
-      <c r="J125" t="s">
+      <c r="J126" t="s">
         <v>199</v>
       </c>
-      <c r="K125" t="s">
-        <v>23</v>
-      </c>
-      <c r="L125">
+      <c r="K126" t="s">
+        <v>23</v>
+      </c>
+      <c r="L126">
         <v>10</v>
       </c>
-      <c r="M125" t="b">
-        <v>0</v>
-      </c>
-      <c r="N125" t="b">
-        <v>0</v>
-      </c>
-      <c r="O125" t="s">
+      <c r="M126" t="b">
+        <v>0</v>
+      </c>
+      <c r="N126" t="b">
+        <v>0</v>
+      </c>
+      <c r="O126" t="s">
         <v>309</v>
       </c>
-      <c r="P125" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q125" t="b">
-        <v>1</v>
-      </c>
-      <c r="R125" t="b">
+      <c r="P126" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q126" t="b">
+        <v>1</v>
+      </c>
+      <c r="R126" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C037E1-6DD7-4290-9103-8949135E5CF9}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CAC644B-5892-44A7-A1C6-7888D2A37001}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="74" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="75" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="680">
   <si>
     <t>Codigo</t>
   </si>
@@ -2057,6 +2057,15 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7790520995285.png</t>
+  </si>
+  <si>
+    <t>7790250024194</t>
+  </si>
+  <si>
+    <t>Elite</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7790250024194.png</t>
   </si>
 </sst>
 </file>
@@ -2408,8 +2417,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D760988-B621-47C2-9476-8EE2B22FA18B}">
-  <dimension ref="A1:R126"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B47EB8FD-D8F0-4DBE-9604-FF699FB6A975}">
+  <dimension ref="A1:R127"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -6522,49 +6531,49 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="B74" t="s">
-        <v>584</v>
+        <v>677</v>
       </c>
       <c r="C74" t="s">
-        <v>585</v>
+        <v>195</v>
       </c>
       <c r="D74" t="s">
-        <v>541</v>
+        <v>196</v>
       </c>
       <c r="E74" t="s">
-        <v>586</v>
+        <v>172</v>
       </c>
       <c r="F74" t="s">
-        <v>517</v>
+        <v>678</v>
       </c>
       <c r="G74">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H74" t="s">
         <v>20</v>
       </c>
       <c r="I74" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J74" t="s">
-        <v>587</v>
+        <v>243</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
       </c>
       <c r="L74">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
       </c>
       <c r="N74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" t="s">
-        <v>588</v>
+        <v>679</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -6578,37 +6587,37 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B75" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C75" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="D75" t="s">
-        <v>591</v>
+        <v>541</v>
       </c>
       <c r="E75" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="F75" t="s">
-        <v>593</v>
+        <v>517</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75" t="s">
         <v>20</v>
       </c>
       <c r="I75" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="J75" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="K75" t="s">
-        <v>595</v>
+        <v>23</v>
       </c>
       <c r="L75">
         <v>12</v>
@@ -6617,10 +6626,10 @@
         <v>0</v>
       </c>
       <c r="N75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -6634,49 +6643,49 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B76" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="C76" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="D76" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="E76" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="F76" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="G76">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I76" t="s">
         <v>53</v>
       </c>
       <c r="J76" t="s">
-        <v>76</v>
+        <v>594</v>
       </c>
       <c r="K76" t="s">
-        <v>23</v>
+        <v>595</v>
       </c>
       <c r="L76">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
       </c>
       <c r="N76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O76" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -6690,49 +6699,49 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B77" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="C77" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="D77" t="s">
-        <v>172</v>
+        <v>598</v>
       </c>
       <c r="E77" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="F77" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="H77" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I77" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J77" t="s">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
       </c>
       <c r="L77">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
       </c>
       <c r="N77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6741,27 +6750,27 @@
         <v>1</v>
       </c>
       <c r="R77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B78" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C78" t="s">
-        <v>607</v>
+        <v>195</v>
       </c>
       <c r="D78" t="s">
-        <v>608</v>
+        <v>172</v>
       </c>
       <c r="E78" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="F78" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -6770,16 +6779,16 @@
         <v>20</v>
       </c>
       <c r="I78" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J78" t="s">
-        <v>611</v>
+        <v>243</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -6788,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="O78" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6797,39 +6806,39 @@
         <v>1</v>
       </c>
       <c r="R78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B79" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="C79" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="D79" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="E79" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="F79" t="s">
-        <v>111</v>
+        <v>610</v>
       </c>
       <c r="G79">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H79" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I79" t="s">
         <v>490</v>
       </c>
       <c r="J79" t="s">
-        <v>576</v>
+        <v>611</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
@@ -6841,10 +6850,10 @@
         <v>0</v>
       </c>
       <c r="N79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O79" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6858,25 +6867,25 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B80" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C80" t="s">
-        <v>174</v>
+        <v>614</v>
       </c>
       <c r="D80" t="s">
-        <v>175</v>
+        <v>615</v>
       </c>
       <c r="E80" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="F80" t="s">
-        <v>620</v>
+        <v>111</v>
       </c>
       <c r="G80">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H80" t="s">
         <v>42</v>
@@ -6885,13 +6894,13 @@
         <v>490</v>
       </c>
       <c r="J80" t="s">
-        <v>177</v>
+        <v>576</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
@@ -6900,7 +6909,7 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6914,40 +6923,40 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="B81" t="s">
-        <v>373</v>
+        <v>618</v>
       </c>
       <c r="C81" t="s">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="D81" t="s">
-        <v>89</v>
+        <v>175</v>
       </c>
       <c r="E81" t="s">
-        <v>90</v>
+        <v>619</v>
       </c>
       <c r="F81" t="s">
-        <v>91</v>
+        <v>620</v>
       </c>
       <c r="G81">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="H81" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I81" t="s">
-        <v>36</v>
+        <v>490</v>
       </c>
       <c r="J81" t="s">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
@@ -6956,13 +6965,13 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>265</v>
+        <v>621</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
       </c>
       <c r="Q81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R81" t="b">
         <v>1</v>
@@ -6970,40 +6979,40 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C82" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D82" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E82" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F82" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G82">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H82" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I82" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J82" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
       </c>
       <c r="L82">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
@@ -7012,7 +7021,7 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -7026,41 +7035,41 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B83" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C83" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D83" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E83" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F83" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G83">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H83" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I83" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J83" t="s">
+        <v>66</v>
+      </c>
+      <c r="K83" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83">
         <v>30</v>
       </c>
-      <c r="K83" t="s">
-        <v>23</v>
-      </c>
-      <c r="L83">
-        <v>12</v>
-      </c>
       <c r="M83" t="b">
         <v>0</v>
       </c>
@@ -7068,13 +7077,13 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
       </c>
       <c r="Q83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="b">
         <v>1</v>
@@ -7082,55 +7091,55 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
+        <v>29</v>
+      </c>
+      <c r="B84" t="s">
+        <v>375</v>
+      </c>
+      <c r="C84" t="s">
+        <v>24</v>
+      </c>
+      <c r="D84" t="s">
+        <v>54</v>
+      </c>
+      <c r="E84" t="s">
+        <v>55</v>
+      </c>
+      <c r="F84" t="s">
+        <v>61</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+      <c r="H84" t="s">
+        <v>28</v>
+      </c>
+      <c r="I84" t="s">
+        <v>96</v>
+      </c>
+      <c r="J84" t="s">
         <v>30</v>
       </c>
-      <c r="B84" t="s">
-        <v>376</v>
-      </c>
-      <c r="C84" t="s">
-        <v>97</v>
-      </c>
-      <c r="D84" t="s">
-        <v>98</v>
-      </c>
-      <c r="E84" t="s">
-        <v>99</v>
-      </c>
-      <c r="F84" t="s">
-        <v>100</v>
-      </c>
-      <c r="G84">
-        <v>100</v>
-      </c>
-      <c r="H84" t="s">
-        <v>20</v>
-      </c>
-      <c r="I84" t="s">
-        <v>101</v>
-      </c>
-      <c r="J84" t="s">
-        <v>102</v>
-      </c>
       <c r="K84" t="s">
         <v>23</v>
       </c>
       <c r="L84">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
       </c>
       <c r="N84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
       </c>
       <c r="Q84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" t="b">
         <v>1</v>
@@ -7138,49 +7147,49 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B85" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C85" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D85" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E85" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F85" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G85">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H85" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I85" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J85" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
       </c>
       <c r="L85">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
       </c>
       <c r="N85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -7194,22 +7203,22 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B86" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C86" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D86" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E86" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F86" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G86">
         <v>500</v>
@@ -7221,13 +7230,13 @@
         <v>107</v>
       </c>
       <c r="J86" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
       </c>
       <c r="L86">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
@@ -7236,7 +7245,7 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -7250,40 +7259,40 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B87" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C87" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D87" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E87" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F87" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G87">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H87" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I87" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J87" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
       </c>
       <c r="L87">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
@@ -7292,13 +7301,13 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
       </c>
       <c r="Q87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" t="b">
         <v>1</v>
@@ -7306,40 +7315,40 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B88" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C88" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D88" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E88" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F88" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G88">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H88" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I88" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J88" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
@@ -7348,13 +7357,13 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
       </c>
       <c r="Q88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" t="b">
         <v>1</v>
@@ -7362,40 +7371,40 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
+        <v>34</v>
+      </c>
+      <c r="B89" t="s">
+        <v>380</v>
+      </c>
+      <c r="C89" t="s">
+        <v>112</v>
+      </c>
+      <c r="D89" t="s">
+        <v>113</v>
+      </c>
+      <c r="E89" t="s">
+        <v>114</v>
+      </c>
+      <c r="F89" t="s">
+        <v>115</v>
+      </c>
+      <c r="G89">
+        <v>300</v>
+      </c>
+      <c r="H89" t="s">
         <v>35</v>
       </c>
-      <c r="B89" t="s">
-        <v>381</v>
-      </c>
-      <c r="C89" t="s">
-        <v>117</v>
-      </c>
-      <c r="D89" t="s">
-        <v>118</v>
-      </c>
-      <c r="E89" t="s">
-        <v>119</v>
-      </c>
-      <c r="F89" t="s">
-        <v>120</v>
-      </c>
-      <c r="G89">
-        <v>500</v>
-      </c>
-      <c r="H89" t="s">
-        <v>42</v>
-      </c>
       <c r="I89" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J89" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
@@ -7404,7 +7413,7 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -7418,40 +7427,40 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B90" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C90" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D90" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E90" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F90" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G90">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H90" t="s">
         <v>42</v>
       </c>
       <c r="I90" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J90" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
       </c>
       <c r="L90">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -7460,13 +7469,13 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
       </c>
       <c r="Q90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="b">
         <v>1</v>
@@ -7474,40 +7483,40 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B91" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C91" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D91" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E91" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F91" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G91">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H91" t="s">
         <v>42</v>
       </c>
       <c r="I91" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J91" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -7516,13 +7525,13 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
       </c>
       <c r="Q91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" t="b">
         <v>1</v>
@@ -7530,34 +7539,34 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B92" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C92" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D92" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E92" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F92" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G92">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H92" t="s">
         <v>42</v>
       </c>
       <c r="I92" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J92" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
@@ -7572,13 +7581,13 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
       </c>
       <c r="Q92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="b">
         <v>1</v>
@@ -7586,40 +7595,40 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B93" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C93" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D93" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E93" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F93" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G93">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H93" t="s">
         <v>42</v>
       </c>
       <c r="I93" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J93" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
       </c>
       <c r="L93">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -7628,7 +7637,7 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
@@ -7642,40 +7651,40 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B94" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C94" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D94" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E94" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F94" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G94">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H94" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I94" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J94" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
       </c>
       <c r="L94">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -7684,7 +7693,7 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -7698,55 +7707,55 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B95" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C95" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D95" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E95" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F95" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G95">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H95" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I95" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J95" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
       </c>
       <c r="L95">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
       </c>
       <c r="Q95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R95" t="b">
         <v>1</v>
@@ -7754,10 +7763,10 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B96" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C96" t="s">
         <v>138</v>
@@ -7766,10 +7775,10 @@
         <v>139</v>
       </c>
       <c r="E96" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F96" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G96">
         <v>1000</v>
@@ -7793,10 +7802,10 @@
         <v>1</v>
       </c>
       <c r="N96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O96" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
@@ -7810,22 +7819,22 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B97" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C97" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D97" t="s">
         <v>139</v>
       </c>
       <c r="E97" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F97" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G97">
         <v>1000</v>
@@ -7837,7 +7846,7 @@
         <v>142</v>
       </c>
       <c r="J97" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K97" t="s">
         <v>23</v>
@@ -7852,7 +7861,7 @@
         <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
@@ -7866,55 +7875,55 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B98" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C98" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D98" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E98" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F98" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G98">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H98" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I98" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J98" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K98" t="s">
         <v>23</v>
       </c>
       <c r="L98">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
       </c>
       <c r="Q98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="b">
         <v>1</v>
@@ -7922,55 +7931,55 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B99" t="s">
-        <v>645</v>
+        <v>390</v>
       </c>
       <c r="C99" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D99" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E99" t="s">
-        <v>646</v>
+        <v>151</v>
       </c>
       <c r="F99" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G99">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H99" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I99" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="J99" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="K99" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="L99">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M99" t="b">
         <v>0</v>
       </c>
       <c r="N99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>647</v>
+        <v>282</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
       </c>
       <c r="Q99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R99" t="b">
         <v>1</v>
@@ -7978,55 +7987,55 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B100" t="s">
-        <v>391</v>
+        <v>645</v>
       </c>
       <c r="C100" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D100" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E100" t="s">
-        <v>163</v>
+        <v>646</v>
       </c>
       <c r="F100" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G100">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H100" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I100" t="s">
-        <v>29</v>
+        <v>158</v>
       </c>
       <c r="J100" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K100" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="L100">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M100" t="b">
         <v>0</v>
       </c>
       <c r="N100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O100" t="s">
-        <v>283</v>
+        <v>647</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
       </c>
       <c r="Q100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R100" t="b">
         <v>1</v>
@@ -8034,34 +8043,34 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B101" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C101" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D101" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E101" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F101" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G101">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H101" t="s">
         <v>42</v>
       </c>
       <c r="I101" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J101" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="K101" t="s">
         <v>23</v>
@@ -8076,7 +8085,7 @@
         <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
@@ -8090,22 +8099,22 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B102" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C102" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D102" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E102" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F102" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="G102">
         <v>500</v>
@@ -8117,7 +8126,7 @@
         <v>21</v>
       </c>
       <c r="J102" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K102" t="s">
         <v>23</v>
@@ -8132,7 +8141,7 @@
         <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
@@ -8146,34 +8155,34 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B103" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C103" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D103" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E103" t="s">
-        <v>622</v>
+        <v>172</v>
       </c>
       <c r="F103" t="s">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="G103">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H103" t="s">
         <v>42</v>
       </c>
       <c r="I103" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J103" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="K103" t="s">
         <v>23</v>
@@ -8188,7 +8197,7 @@
         <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
@@ -8202,37 +8211,37 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
+        <v>49</v>
+      </c>
+      <c r="B104" t="s">
+        <v>394</v>
+      </c>
+      <c r="C104" t="s">
+        <v>174</v>
+      </c>
+      <c r="D104" t="s">
+        <v>175</v>
+      </c>
+      <c r="E104" t="s">
+        <v>622</v>
+      </c>
+      <c r="F104" t="s">
+        <v>176</v>
+      </c>
+      <c r="G104">
         <v>50</v>
       </c>
-      <c r="B104" t="s">
-        <v>395</v>
-      </c>
-      <c r="C104" t="s">
-        <v>178</v>
-      </c>
-      <c r="D104" t="s">
-        <v>179</v>
-      </c>
-      <c r="E104" t="s">
-        <v>180</v>
-      </c>
-      <c r="F104" t="s">
-        <v>181</v>
-      </c>
-      <c r="G104">
-        <v>12</v>
-      </c>
       <c r="H104" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I104" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="J104" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="K104" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="L104">
         <v>12</v>
@@ -8244,7 +8253,7 @@
         <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
@@ -8258,40 +8267,40 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B105" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C105" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D105" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E105" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F105" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G105">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H105" t="s">
-        <v>188</v>
+        <v>20</v>
       </c>
       <c r="I105" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="J105" t="s">
-        <v>552</v>
+        <v>182</v>
       </c>
       <c r="K105" t="s">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="L105">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M105" t="b">
         <v>0</v>
@@ -8300,7 +8309,7 @@
         <v>1</v>
       </c>
       <c r="O105" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
@@ -8314,40 +8323,40 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B106" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C106" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D106" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E106" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F106" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="G106">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H106" t="s">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="I106" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
       <c r="J106" t="s">
-        <v>182</v>
+        <v>552</v>
       </c>
       <c r="K106" t="s">
         <v>23</v>
       </c>
       <c r="L106">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M106" t="b">
         <v>0</v>
@@ -8356,7 +8365,7 @@
         <v>1</v>
       </c>
       <c r="O106" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
@@ -8370,40 +8379,40 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
+        <v>52</v>
+      </c>
+      <c r="B107" t="s">
+        <v>397</v>
+      </c>
+      <c r="C107" t="s">
+        <v>191</v>
+      </c>
+      <c r="D107" t="s">
+        <v>179</v>
+      </c>
+      <c r="E107" t="s">
+        <v>180</v>
+      </c>
+      <c r="F107" t="s">
+        <v>181</v>
+      </c>
+      <c r="G107">
+        <v>24</v>
+      </c>
+      <c r="H107" t="s">
+        <v>20</v>
+      </c>
+      <c r="I107" t="s">
         <v>53</v>
       </c>
-      <c r="B107" t="s">
-        <v>398</v>
-      </c>
-      <c r="C107" t="s">
-        <v>31</v>
-      </c>
-      <c r="D107" t="s">
-        <v>192</v>
-      </c>
-      <c r="E107" t="s">
-        <v>193</v>
-      </c>
-      <c r="F107" t="s">
-        <v>194</v>
-      </c>
-      <c r="G107">
-        <v>1.5</v>
-      </c>
-      <c r="H107" t="s">
-        <v>28</v>
-      </c>
-      <c r="I107" t="s">
-        <v>36</v>
-      </c>
       <c r="J107" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="K107" t="s">
         <v>23</v>
       </c>
       <c r="L107">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M107" t="b">
         <v>0</v>
@@ -8412,7 +8421,7 @@
         <v>1</v>
       </c>
       <c r="O107" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
@@ -8426,52 +8435,52 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B108" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C108" t="s">
-        <v>195</v>
+        <v>31</v>
       </c>
       <c r="D108" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E108" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F108" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G108">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H108" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I108" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J108" t="s">
-        <v>199</v>
+        <v>37</v>
       </c>
       <c r="K108" t="s">
         <v>23</v>
       </c>
       <c r="L108">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M108" t="b">
         <v>0</v>
       </c>
       <c r="N108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O108" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q108" t="b">
         <v>1</v>
@@ -8482,55 +8491,55 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B109" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C109" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="D109" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E109" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F109" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G109">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H109" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I109" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="J109" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="K109" t="s">
         <v>23</v>
       </c>
       <c r="L109">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M109" t="b">
         <v>0</v>
       </c>
       <c r="N109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O109" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R109" t="b">
         <v>1</v>
@@ -8538,40 +8547,40 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B110" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C110" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="D110" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E110" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F110" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G110">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H110" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I110" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="J110" t="s">
-        <v>66</v>
+        <v>190</v>
       </c>
       <c r="K110" t="s">
         <v>23</v>
       </c>
       <c r="L110">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M110" t="b">
         <v>0</v>
@@ -8580,7 +8589,7 @@
         <v>1</v>
       </c>
       <c r="O110" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P110" t="b">
         <v>1</v>
@@ -8594,19 +8603,19 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B111" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C111" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D111" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E111" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F111" t="s">
         <v>206</v>
@@ -8636,7 +8645,7 @@
         <v>1</v>
       </c>
       <c r="O111" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P111" t="b">
         <v>1</v>
@@ -8650,19 +8659,19 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B112" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C112" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D112" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E112" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F112" t="s">
         <v>206</v>
@@ -8683,7 +8692,7 @@
         <v>23</v>
       </c>
       <c r="L112">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M112" t="b">
         <v>0</v>
@@ -8692,7 +8701,7 @@
         <v>1</v>
       </c>
       <c r="O112" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P112" t="b">
         <v>1</v>
@@ -8706,34 +8715,34 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B113" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C113" t="s">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="D113" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E113" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F113" t="s">
-        <v>56</v>
+        <v>206</v>
       </c>
       <c r="G113">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H113" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I113" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="J113" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K113" t="s">
         <v>23</v>
@@ -8748,13 +8757,13 @@
         <v>1</v>
       </c>
       <c r="O113" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P113" t="b">
         <v>1</v>
       </c>
       <c r="Q113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R113" t="b">
         <v>1</v>
@@ -8762,34 +8771,34 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B114" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C114" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D114" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="E114" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="F114" t="s">
-        <v>214</v>
+        <v>56</v>
       </c>
       <c r="G114">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H114" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I114" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J114" t="s">
-        <v>553</v>
+        <v>148</v>
       </c>
       <c r="K114" t="s">
         <v>23</v>
@@ -8804,7 +8813,7 @@
         <v>1</v>
       </c>
       <c r="O114" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P114" t="b">
         <v>1</v>
@@ -8818,49 +8827,49 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B115" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C115" t="s">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="D115" t="s">
-        <v>216</v>
+        <v>81</v>
       </c>
       <c r="E115" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="F115" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G115">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H115" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I115" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J115" t="s">
-        <v>215</v>
+        <v>553</v>
       </c>
       <c r="K115" t="s">
         <v>23</v>
       </c>
       <c r="L115">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M115" t="b">
         <v>0</v>
       </c>
       <c r="N115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O115" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P115" t="b">
         <v>1</v>
@@ -8874,22 +8883,22 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B116" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C116" t="s">
         <v>215</v>
       </c>
       <c r="D116" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E116" t="s">
         <v>217</v>
       </c>
       <c r="F116" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G116">
         <v>20</v>
@@ -8916,13 +8925,13 @@
         <v>0</v>
       </c>
       <c r="O116" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P116" t="b">
         <v>1</v>
       </c>
       <c r="Q116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R116" t="b">
         <v>1</v>
@@ -8930,49 +8939,49 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B117" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C117" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D117" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="E117" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F117" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="G117">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H117" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I117" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J117" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K117" t="s">
         <v>23</v>
       </c>
       <c r="L117">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M117" t="b">
         <v>0</v>
       </c>
       <c r="N117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O117" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P117" t="b">
         <v>1</v>
@@ -8986,34 +8995,34 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B118" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C118" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D118" t="s">
         <v>200</v>
       </c>
       <c r="E118" t="s">
-        <v>32</v>
+        <v>201</v>
       </c>
       <c r="F118" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="G118">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H118" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I118" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J118" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="K118" t="s">
         <v>23</v>
@@ -9028,7 +9037,7 @@
         <v>1</v>
       </c>
       <c r="O118" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P118" t="b">
         <v>1</v>
@@ -9042,40 +9051,40 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B119" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C119" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D119" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="E119" t="s">
-        <v>227</v>
+        <v>32</v>
       </c>
       <c r="F119" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G119">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H119" t="s">
         <v>42</v>
       </c>
       <c r="I119" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J119" t="s">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="K119" t="s">
         <v>23</v>
       </c>
       <c r="L119">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M119" t="b">
         <v>0</v>
@@ -9084,13 +9093,13 @@
         <v>1</v>
       </c>
       <c r="O119" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P119" t="b">
         <v>1</v>
       </c>
       <c r="Q119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R119" t="b">
         <v>1</v>
@@ -9098,40 +9107,40 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B120" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C120" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
       <c r="D120" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E120" t="s">
         <v>227</v>
       </c>
       <c r="F120" t="s">
-        <v>47</v>
+        <v>228</v>
       </c>
       <c r="G120">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H120" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I120" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J120" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K120" t="s">
         <v>23</v>
       </c>
       <c r="L120">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M120" t="b">
         <v>0</v>
@@ -9140,7 +9149,7 @@
         <v>1</v>
       </c>
       <c r="O120" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P120" t="b">
         <v>1</v>
@@ -9154,40 +9163,40 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B121" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C121" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D121" t="s">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="E121" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F121" t="s">
-        <v>194</v>
+        <v>47</v>
       </c>
       <c r="G121">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H121" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I121" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J121" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K121" t="s">
         <v>23</v>
       </c>
       <c r="L121">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M121" t="b">
         <v>0</v>
@@ -9196,13 +9205,13 @@
         <v>1</v>
       </c>
       <c r="O121" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P121" t="b">
         <v>1</v>
       </c>
       <c r="Q121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R121" t="b">
         <v>1</v>
@@ -9210,34 +9219,34 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B122" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C122" t="s">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="D122" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E122" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F122" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G122">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H122" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I122" t="s">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="J122" t="s">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="K122" t="s">
         <v>23</v>
@@ -9252,7 +9261,7 @@
         <v>1</v>
       </c>
       <c r="O122" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P122" t="b">
         <v>1</v>
@@ -9266,10 +9275,10 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B123" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C123" t="s">
         <v>184</v>
@@ -9278,13 +9287,13 @@
         <v>200</v>
       </c>
       <c r="E123" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F123" t="s">
         <v>202</v>
       </c>
       <c r="G123">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H123" t="s">
         <v>35</v>
@@ -9308,7 +9317,7 @@
         <v>1</v>
       </c>
       <c r="O123" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P123" t="b">
         <v>1</v>
@@ -9322,10 +9331,10 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B124" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C124" t="s">
         <v>184</v>
@@ -9340,7 +9349,7 @@
         <v>202</v>
       </c>
       <c r="G124">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H124" t="s">
         <v>35</v>
@@ -9364,7 +9373,7 @@
         <v>1</v>
       </c>
       <c r="O124" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P124" t="b">
         <v>1</v>
@@ -9378,41 +9387,41 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B125" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C125" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="D125" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="E125" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F125" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="G125">
+        <v>250</v>
+      </c>
+      <c r="H125" t="s">
+        <v>35</v>
+      </c>
+      <c r="I125" t="s">
+        <v>189</v>
+      </c>
+      <c r="J125" t="s">
+        <v>190</v>
+      </c>
+      <c r="K125" t="s">
+        <v>23</v>
+      </c>
+      <c r="L125">
         <v>6</v>
       </c>
-      <c r="H125" t="s">
-        <v>20</v>
-      </c>
-      <c r="I125" t="s">
-        <v>237</v>
-      </c>
-      <c r="J125" t="s">
-        <v>233</v>
-      </c>
-      <c r="K125" t="s">
-        <v>23</v>
-      </c>
-      <c r="L125">
-        <v>1</v>
-      </c>
       <c r="M125" t="b">
         <v>0</v>
       </c>
@@ -9420,13 +9429,13 @@
         <v>1</v>
       </c>
       <c r="O125" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R125" t="b">
         <v>1</v>
@@ -9434,57 +9443,113 @@
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B126" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C126" t="s">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="D126" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="E126" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="F126" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G126">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H126" t="s">
         <v>20</v>
       </c>
       <c r="I126" t="s">
+        <v>237</v>
+      </c>
+      <c r="J126" t="s">
+        <v>233</v>
+      </c>
+      <c r="K126" t="s">
+        <v>23</v>
+      </c>
+      <c r="L126">
+        <v>1</v>
+      </c>
+      <c r="M126" t="b">
+        <v>0</v>
+      </c>
+      <c r="N126" t="b">
+        <v>1</v>
+      </c>
+      <c r="O126" t="s">
+        <v>308</v>
+      </c>
+      <c r="P126" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="b">
+        <v>1</v>
+      </c>
+      <c r="R126" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>72</v>
+      </c>
+      <c r="B127" t="s">
+        <v>417</v>
+      </c>
+      <c r="C127" t="s">
+        <v>195</v>
+      </c>
+      <c r="D127" t="s">
+        <v>196</v>
+      </c>
+      <c r="E127" t="s">
+        <v>197</v>
+      </c>
+      <c r="F127" t="s">
+        <v>238</v>
+      </c>
+      <c r="G127">
+        <v>4</v>
+      </c>
+      <c r="H127" t="s">
+        <v>20</v>
+      </c>
+      <c r="I127" t="s">
         <v>21</v>
       </c>
-      <c r="J126" t="s">
+      <c r="J127" t="s">
         <v>199</v>
       </c>
-      <c r="K126" t="s">
-        <v>23</v>
-      </c>
-      <c r="L126">
+      <c r="K127" t="s">
+        <v>23</v>
+      </c>
+      <c r="L127">
         <v>10</v>
       </c>
-      <c r="M126" t="b">
-        <v>0</v>
-      </c>
-      <c r="N126" t="b">
-        <v>0</v>
-      </c>
-      <c r="O126" t="s">
+      <c r="M127" t="b">
+        <v>0</v>
+      </c>
+      <c r="N127" t="b">
+        <v>0</v>
+      </c>
+      <c r="O127" t="s">
         <v>309</v>
       </c>
-      <c r="P126" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q126" t="b">
-        <v>1</v>
-      </c>
-      <c r="R126" t="b">
+      <c r="P127" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q127" t="b">
+        <v>1</v>
+      </c>
+      <c r="R127" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CAC644B-5892-44A7-A1C6-7888D2A37001}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D01CD1-EAD9-4E2B-8A74-75EACB493791}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="75" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="76" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="683">
   <si>
     <t>Codigo</t>
   </si>
@@ -2066,6 +2066,15 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7790250024194.png</t>
+  </si>
+  <si>
+    <t>7791866001197</t>
+  </si>
+  <si>
+    <t>Natura</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7791866001197.png</t>
   </si>
 </sst>
 </file>
@@ -2417,8 +2426,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B47EB8FD-D8F0-4DBE-9604-FF699FB6A975}">
-  <dimension ref="A1:R127"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABADBA17-6C44-418D-9C36-1A9520D58FD3}">
+  <dimension ref="A1:R128"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -6587,93 +6596,93 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="B75" t="s">
-        <v>584</v>
+        <v>680</v>
       </c>
       <c r="C75" t="s">
-        <v>585</v>
+        <v>225</v>
       </c>
       <c r="D75" t="s">
-        <v>541</v>
+        <v>226</v>
       </c>
       <c r="E75" t="s">
-        <v>586</v>
+        <v>227</v>
       </c>
       <c r="F75" t="s">
-        <v>517</v>
+        <v>681</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>118</v>
       </c>
       <c r="H75" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I75" t="s">
-        <v>490</v>
+        <v>96</v>
       </c>
       <c r="J75" t="s">
-        <v>587</v>
+        <v>125</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
       </c>
       <c r="N75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="s">
-        <v>588</v>
+        <v>682</v>
       </c>
       <c r="P75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="b">
         <v>1</v>
       </c>
       <c r="R75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B76" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C76" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="D76" t="s">
-        <v>591</v>
+        <v>541</v>
       </c>
       <c r="E76" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="F76" t="s">
-        <v>593</v>
+        <v>517</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76" t="s">
         <v>20</v>
       </c>
       <c r="I76" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="J76" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="K76" t="s">
-        <v>595</v>
+        <v>23</v>
       </c>
       <c r="L76">
         <v>12</v>
@@ -6682,10 +6691,10 @@
         <v>0</v>
       </c>
       <c r="N76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -6699,49 +6708,49 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B77" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="C77" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="D77" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="E77" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="F77" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="G77">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I77" t="s">
         <v>53</v>
       </c>
       <c r="J77" t="s">
-        <v>76</v>
+        <v>594</v>
       </c>
       <c r="K77" t="s">
-        <v>23</v>
+        <v>595</v>
       </c>
       <c r="L77">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
       </c>
       <c r="N77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6755,49 +6764,49 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B78" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="C78" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="D78" t="s">
-        <v>172</v>
+        <v>598</v>
       </c>
       <c r="E78" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="F78" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="H78" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I78" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J78" t="s">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
       </c>
       <c r="N78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6806,27 +6815,27 @@
         <v>1</v>
       </c>
       <c r="R78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B79" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C79" t="s">
-        <v>607</v>
+        <v>195</v>
       </c>
       <c r="D79" t="s">
-        <v>608</v>
+        <v>172</v>
       </c>
       <c r="E79" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="F79" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -6835,16 +6844,16 @@
         <v>20</v>
       </c>
       <c r="I79" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J79" t="s">
-        <v>611</v>
+        <v>243</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -6853,7 +6862,7 @@
         <v>0</v>
       </c>
       <c r="O79" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6862,39 +6871,39 @@
         <v>1</v>
       </c>
       <c r="R79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B80" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="C80" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="D80" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="E80" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="F80" t="s">
-        <v>111</v>
+        <v>610</v>
       </c>
       <c r="G80">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H80" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I80" t="s">
         <v>490</v>
       </c>
       <c r="J80" t="s">
-        <v>576</v>
+        <v>611</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
@@ -6906,10 +6915,10 @@
         <v>0</v>
       </c>
       <c r="N80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6923,25 +6932,25 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B81" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C81" t="s">
-        <v>174</v>
+        <v>614</v>
       </c>
       <c r="D81" t="s">
-        <v>175</v>
+        <v>615</v>
       </c>
       <c r="E81" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="F81" t="s">
-        <v>620</v>
+        <v>111</v>
       </c>
       <c r="G81">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H81" t="s">
         <v>42</v>
@@ -6950,13 +6959,13 @@
         <v>490</v>
       </c>
       <c r="J81" t="s">
-        <v>177</v>
+        <v>576</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
@@ -6965,7 +6974,7 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6979,40 +6988,40 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="B82" t="s">
-        <v>373</v>
+        <v>618</v>
       </c>
       <c r="C82" t="s">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="D82" t="s">
-        <v>89</v>
+        <v>175</v>
       </c>
       <c r="E82" t="s">
-        <v>90</v>
+        <v>619</v>
       </c>
       <c r="F82" t="s">
-        <v>91</v>
+        <v>620</v>
       </c>
       <c r="G82">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="H82" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I82" t="s">
-        <v>36</v>
+        <v>490</v>
       </c>
       <c r="J82" t="s">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
       </c>
       <c r="L82">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
@@ -7021,13 +7030,13 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>265</v>
+        <v>621</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
       </c>
       <c r="Q82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" t="b">
         <v>1</v>
@@ -7035,40 +7044,40 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C83" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D83" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E83" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F83" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G83">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H83" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I83" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J83" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
       </c>
       <c r="L83">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
@@ -7077,7 +7086,7 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -7091,41 +7100,41 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B84" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C84" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D84" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E84" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F84" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H84" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I84" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J84" t="s">
+        <v>66</v>
+      </c>
+      <c r="K84" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84">
         <v>30</v>
       </c>
-      <c r="K84" t="s">
-        <v>23</v>
-      </c>
-      <c r="L84">
-        <v>12</v>
-      </c>
       <c r="M84" t="b">
         <v>0</v>
       </c>
@@ -7133,13 +7142,13 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
       </c>
       <c r="Q84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84" t="b">
         <v>1</v>
@@ -7147,55 +7156,55 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
+        <v>29</v>
+      </c>
+      <c r="B85" t="s">
+        <v>375</v>
+      </c>
+      <c r="C85" t="s">
+        <v>24</v>
+      </c>
+      <c r="D85" t="s">
+        <v>54</v>
+      </c>
+      <c r="E85" t="s">
+        <v>55</v>
+      </c>
+      <c r="F85" t="s">
+        <v>61</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+      <c r="H85" t="s">
+        <v>28</v>
+      </c>
+      <c r="I85" t="s">
+        <v>96</v>
+      </c>
+      <c r="J85" t="s">
         <v>30</v>
       </c>
-      <c r="B85" t="s">
-        <v>376</v>
-      </c>
-      <c r="C85" t="s">
-        <v>97</v>
-      </c>
-      <c r="D85" t="s">
-        <v>98</v>
-      </c>
-      <c r="E85" t="s">
-        <v>99</v>
-      </c>
-      <c r="F85" t="s">
-        <v>100</v>
-      </c>
-      <c r="G85">
-        <v>100</v>
-      </c>
-      <c r="H85" t="s">
-        <v>20</v>
-      </c>
-      <c r="I85" t="s">
-        <v>101</v>
-      </c>
-      <c r="J85" t="s">
-        <v>102</v>
-      </c>
       <c r="K85" t="s">
         <v>23</v>
       </c>
       <c r="L85">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
       </c>
       <c r="N85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
       </c>
       <c r="Q85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" t="b">
         <v>1</v>
@@ -7203,49 +7212,49 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B86" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C86" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D86" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E86" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F86" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G86">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H86" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I86" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J86" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
       </c>
       <c r="L86">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
       </c>
       <c r="N86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O86" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -7259,22 +7268,22 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B87" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C87" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D87" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E87" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F87" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G87">
         <v>500</v>
@@ -7286,13 +7295,13 @@
         <v>107</v>
       </c>
       <c r="J87" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
       </c>
       <c r="L87">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
@@ -7301,7 +7310,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -7315,40 +7324,40 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B88" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C88" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D88" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E88" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F88" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G88">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H88" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I88" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J88" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
@@ -7357,13 +7366,13 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
       </c>
       <c r="Q88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R88" t="b">
         <v>1</v>
@@ -7371,40 +7380,40 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B89" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C89" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D89" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E89" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F89" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G89">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H89" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I89" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J89" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
@@ -7413,13 +7422,13 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
       </c>
       <c r="Q89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" t="b">
         <v>1</v>
@@ -7427,40 +7436,40 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
+        <v>34</v>
+      </c>
+      <c r="B90" t="s">
+        <v>380</v>
+      </c>
+      <c r="C90" t="s">
+        <v>112</v>
+      </c>
+      <c r="D90" t="s">
+        <v>113</v>
+      </c>
+      <c r="E90" t="s">
+        <v>114</v>
+      </c>
+      <c r="F90" t="s">
+        <v>115</v>
+      </c>
+      <c r="G90">
+        <v>300</v>
+      </c>
+      <c r="H90" t="s">
         <v>35</v>
       </c>
-      <c r="B90" t="s">
-        <v>381</v>
-      </c>
-      <c r="C90" t="s">
-        <v>117</v>
-      </c>
-      <c r="D90" t="s">
-        <v>118</v>
-      </c>
-      <c r="E90" t="s">
-        <v>119</v>
-      </c>
-      <c r="F90" t="s">
-        <v>120</v>
-      </c>
-      <c r="G90">
-        <v>500</v>
-      </c>
-      <c r="H90" t="s">
-        <v>42</v>
-      </c>
       <c r="I90" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J90" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
       </c>
       <c r="L90">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -7469,7 +7478,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -7483,40 +7492,40 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B91" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C91" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D91" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E91" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F91" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G91">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H91" t="s">
         <v>42</v>
       </c>
       <c r="I91" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J91" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -7525,13 +7534,13 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
       </c>
       <c r="Q91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R91" t="b">
         <v>1</v>
@@ -7539,40 +7548,40 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B92" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C92" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D92" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E92" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F92" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G92">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H92" t="s">
         <v>42</v>
       </c>
       <c r="I92" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J92" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
       </c>
       <c r="L92">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -7581,13 +7590,13 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
       </c>
       <c r="Q92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" t="b">
         <v>1</v>
@@ -7595,34 +7604,34 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B93" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C93" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D93" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E93" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F93" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G93">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H93" t="s">
         <v>42</v>
       </c>
       <c r="I93" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J93" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
@@ -7637,13 +7646,13 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
       </c>
       <c r="Q93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
@@ -7651,40 +7660,40 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B94" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C94" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D94" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E94" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F94" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G94">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H94" t="s">
         <v>42</v>
       </c>
       <c r="I94" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J94" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
       </c>
       <c r="L94">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -7693,7 +7702,7 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -7707,40 +7716,40 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B95" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C95" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D95" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E95" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F95" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G95">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H95" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I95" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J95" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
       </c>
       <c r="L95">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
@@ -7749,7 +7758,7 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
@@ -7763,55 +7772,55 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B96" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C96" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D96" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E96" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F96" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G96">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H96" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I96" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J96" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
       </c>
       <c r="L96">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
       </c>
       <c r="Q96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" t="b">
         <v>1</v>
@@ -7819,10 +7828,10 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B97" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C97" t="s">
         <v>138</v>
@@ -7831,10 +7840,10 @@
         <v>139</v>
       </c>
       <c r="E97" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F97" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G97">
         <v>1000</v>
@@ -7858,10 +7867,10 @@
         <v>1</v>
       </c>
       <c r="N97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O97" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
@@ -7875,22 +7884,22 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B98" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C98" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D98" t="s">
         <v>139</v>
       </c>
       <c r="E98" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F98" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G98">
         <v>1000</v>
@@ -7902,7 +7911,7 @@
         <v>142</v>
       </c>
       <c r="J98" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K98" t="s">
         <v>23</v>
@@ -7917,7 +7926,7 @@
         <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
@@ -7931,55 +7940,55 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B99" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C99" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D99" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E99" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F99" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G99">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H99" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I99" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J99" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K99" t="s">
         <v>23</v>
       </c>
       <c r="L99">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
       </c>
       <c r="Q99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R99" t="b">
         <v>1</v>
@@ -7987,55 +7996,55 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B100" t="s">
-        <v>645</v>
+        <v>390</v>
       </c>
       <c r="C100" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D100" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E100" t="s">
-        <v>646</v>
+        <v>151</v>
       </c>
       <c r="F100" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H100" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I100" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="J100" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="K100" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="L100">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M100" t="b">
         <v>0</v>
       </c>
       <c r="N100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>647</v>
+        <v>282</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
       </c>
       <c r="Q100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R100" t="b">
         <v>1</v>
@@ -8043,55 +8052,55 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B101" t="s">
-        <v>391</v>
+        <v>645</v>
       </c>
       <c r="C101" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D101" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E101" t="s">
-        <v>163</v>
+        <v>646</v>
       </c>
       <c r="F101" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G101">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H101" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I101" t="s">
-        <v>29</v>
+        <v>158</v>
       </c>
       <c r="J101" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K101" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="L101">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M101" t="b">
         <v>0</v>
       </c>
       <c r="N101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O101" t="s">
-        <v>283</v>
+        <v>647</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
       </c>
       <c r="Q101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R101" t="b">
         <v>1</v>
@@ -8099,34 +8108,34 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B102" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C102" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D102" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E102" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F102" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G102">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H102" t="s">
         <v>42</v>
       </c>
       <c r="I102" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J102" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="K102" t="s">
         <v>23</v>
@@ -8141,7 +8150,7 @@
         <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
@@ -8155,22 +8164,22 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B103" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C103" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D103" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E103" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F103" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="G103">
         <v>500</v>
@@ -8182,7 +8191,7 @@
         <v>21</v>
       </c>
       <c r="J103" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K103" t="s">
         <v>23</v>
@@ -8197,7 +8206,7 @@
         <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
@@ -8211,34 +8220,34 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B104" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C104" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D104" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E104" t="s">
-        <v>622</v>
+        <v>172</v>
       </c>
       <c r="F104" t="s">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="G104">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H104" t="s">
         <v>42</v>
       </c>
       <c r="I104" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J104" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="K104" t="s">
         <v>23</v>
@@ -8253,7 +8262,7 @@
         <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
@@ -8267,37 +8276,37 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
+        <v>49</v>
+      </c>
+      <c r="B105" t="s">
+        <v>394</v>
+      </c>
+      <c r="C105" t="s">
+        <v>174</v>
+      </c>
+      <c r="D105" t="s">
+        <v>175</v>
+      </c>
+      <c r="E105" t="s">
+        <v>622</v>
+      </c>
+      <c r="F105" t="s">
+        <v>176</v>
+      </c>
+      <c r="G105">
         <v>50</v>
       </c>
-      <c r="B105" t="s">
-        <v>395</v>
-      </c>
-      <c r="C105" t="s">
-        <v>178</v>
-      </c>
-      <c r="D105" t="s">
-        <v>179</v>
-      </c>
-      <c r="E105" t="s">
-        <v>180</v>
-      </c>
-      <c r="F105" t="s">
-        <v>181</v>
-      </c>
-      <c r="G105">
-        <v>12</v>
-      </c>
       <c r="H105" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I105" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="J105" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="K105" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="L105">
         <v>12</v>
@@ -8309,7 +8318,7 @@
         <v>1</v>
       </c>
       <c r="O105" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
@@ -8323,40 +8332,40 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B106" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C106" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D106" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E106" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F106" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G106">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H106" t="s">
-        <v>188</v>
+        <v>20</v>
       </c>
       <c r="I106" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="J106" t="s">
-        <v>552</v>
+        <v>182</v>
       </c>
       <c r="K106" t="s">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="L106">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M106" t="b">
         <v>0</v>
@@ -8365,7 +8374,7 @@
         <v>1</v>
       </c>
       <c r="O106" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
@@ -8379,40 +8388,40 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B107" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C107" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D107" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E107" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F107" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="G107">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H107" t="s">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="I107" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
       <c r="J107" t="s">
-        <v>182</v>
+        <v>552</v>
       </c>
       <c r="K107" t="s">
         <v>23</v>
       </c>
       <c r="L107">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M107" t="b">
         <v>0</v>
@@ -8421,7 +8430,7 @@
         <v>1</v>
       </c>
       <c r="O107" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
@@ -8435,40 +8444,40 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
+        <v>52</v>
+      </c>
+      <c r="B108" t="s">
+        <v>397</v>
+      </c>
+      <c r="C108" t="s">
+        <v>191</v>
+      </c>
+      <c r="D108" t="s">
+        <v>179</v>
+      </c>
+      <c r="E108" t="s">
+        <v>180</v>
+      </c>
+      <c r="F108" t="s">
+        <v>181</v>
+      </c>
+      <c r="G108">
+        <v>24</v>
+      </c>
+      <c r="H108" t="s">
+        <v>20</v>
+      </c>
+      <c r="I108" t="s">
         <v>53</v>
       </c>
-      <c r="B108" t="s">
-        <v>398</v>
-      </c>
-      <c r="C108" t="s">
-        <v>31</v>
-      </c>
-      <c r="D108" t="s">
-        <v>192</v>
-      </c>
-      <c r="E108" t="s">
-        <v>193</v>
-      </c>
-      <c r="F108" t="s">
-        <v>194</v>
-      </c>
-      <c r="G108">
-        <v>1.5</v>
-      </c>
-      <c r="H108" t="s">
-        <v>28</v>
-      </c>
-      <c r="I108" t="s">
-        <v>36</v>
-      </c>
       <c r="J108" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="K108" t="s">
         <v>23</v>
       </c>
       <c r="L108">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M108" t="b">
         <v>0</v>
@@ -8477,7 +8486,7 @@
         <v>1</v>
       </c>
       <c r="O108" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P108" t="b">
         <v>1</v>
@@ -8491,52 +8500,52 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C109" t="s">
-        <v>195</v>
+        <v>31</v>
       </c>
       <c r="D109" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E109" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F109" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G109">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H109" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I109" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J109" t="s">
-        <v>199</v>
+        <v>37</v>
       </c>
       <c r="K109" t="s">
         <v>23</v>
       </c>
       <c r="L109">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M109" t="b">
         <v>0</v>
       </c>
       <c r="N109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O109" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q109" t="b">
         <v>1</v>
@@ -8547,55 +8556,55 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B110" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C110" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="D110" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E110" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F110" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G110">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H110" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I110" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="J110" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="K110" t="s">
         <v>23</v>
       </c>
       <c r="L110">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M110" t="b">
         <v>0</v>
       </c>
       <c r="N110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O110" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R110" t="b">
         <v>1</v>
@@ -8603,40 +8612,40 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B111" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C111" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="D111" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E111" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F111" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G111">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H111" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I111" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="J111" t="s">
-        <v>66</v>
+        <v>190</v>
       </c>
       <c r="K111" t="s">
         <v>23</v>
       </c>
       <c r="L111">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M111" t="b">
         <v>0</v>
@@ -8645,7 +8654,7 @@
         <v>1</v>
       </c>
       <c r="O111" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P111" t="b">
         <v>1</v>
@@ -8659,19 +8668,19 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B112" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C112" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D112" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E112" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F112" t="s">
         <v>206</v>
@@ -8701,7 +8710,7 @@
         <v>1</v>
       </c>
       <c r="O112" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P112" t="b">
         <v>1</v>
@@ -8715,19 +8724,19 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B113" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C113" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D113" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E113" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F113" t="s">
         <v>206</v>
@@ -8748,7 +8757,7 @@
         <v>23</v>
       </c>
       <c r="L113">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M113" t="b">
         <v>0</v>
@@ -8757,7 +8766,7 @@
         <v>1</v>
       </c>
       <c r="O113" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P113" t="b">
         <v>1</v>
@@ -8771,34 +8780,34 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B114" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C114" t="s">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="D114" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E114" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F114" t="s">
-        <v>56</v>
+        <v>206</v>
       </c>
       <c r="G114">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H114" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I114" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="J114" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K114" t="s">
         <v>23</v>
@@ -8813,13 +8822,13 @@
         <v>1</v>
       </c>
       <c r="O114" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P114" t="b">
         <v>1</v>
       </c>
       <c r="Q114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R114" t="b">
         <v>1</v>
@@ -8827,34 +8836,34 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B115" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C115" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D115" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="E115" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="F115" t="s">
-        <v>214</v>
+        <v>56</v>
       </c>
       <c r="G115">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H115" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I115" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J115" t="s">
-        <v>553</v>
+        <v>148</v>
       </c>
       <c r="K115" t="s">
         <v>23</v>
@@ -8869,7 +8878,7 @@
         <v>1</v>
       </c>
       <c r="O115" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P115" t="b">
         <v>1</v>
@@ -8883,49 +8892,49 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B116" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C116" t="s">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="D116" t="s">
-        <v>216</v>
+        <v>81</v>
       </c>
       <c r="E116" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="F116" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G116">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H116" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I116" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J116" t="s">
-        <v>215</v>
+        <v>553</v>
       </c>
       <c r="K116" t="s">
         <v>23</v>
       </c>
       <c r="L116">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M116" t="b">
         <v>0</v>
       </c>
       <c r="N116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O116" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P116" t="b">
         <v>1</v>
@@ -8939,22 +8948,22 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B117" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C117" t="s">
         <v>215</v>
       </c>
       <c r="D117" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E117" t="s">
         <v>217</v>
       </c>
       <c r="F117" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G117">
         <v>20</v>
@@ -8981,13 +8990,13 @@
         <v>0</v>
       </c>
       <c r="O117" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P117" t="b">
         <v>1</v>
       </c>
       <c r="Q117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R117" t="b">
         <v>1</v>
@@ -8995,49 +9004,49 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B118" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C118" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D118" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="E118" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F118" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="G118">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H118" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I118" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J118" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K118" t="s">
         <v>23</v>
       </c>
       <c r="L118">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M118" t="b">
         <v>0</v>
       </c>
       <c r="N118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O118" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P118" t="b">
         <v>1</v>
@@ -9051,34 +9060,34 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B119" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C119" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D119" t="s">
         <v>200</v>
       </c>
       <c r="E119" t="s">
-        <v>32</v>
+        <v>201</v>
       </c>
       <c r="F119" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="G119">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H119" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I119" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J119" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="K119" t="s">
         <v>23</v>
@@ -9093,7 +9102,7 @@
         <v>1</v>
       </c>
       <c r="O119" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P119" t="b">
         <v>1</v>
@@ -9107,40 +9116,40 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B120" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C120" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D120" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="E120" t="s">
-        <v>227</v>
+        <v>32</v>
       </c>
       <c r="F120" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G120">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H120" t="s">
         <v>42</v>
       </c>
       <c r="I120" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J120" t="s">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="K120" t="s">
         <v>23</v>
       </c>
       <c r="L120">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M120" t="b">
         <v>0</v>
@@ -9149,13 +9158,13 @@
         <v>1</v>
       </c>
       <c r="O120" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P120" t="b">
         <v>1</v>
       </c>
       <c r="Q120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R120" t="b">
         <v>1</v>
@@ -9163,40 +9172,40 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B121" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C121" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
       <c r="D121" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E121" t="s">
         <v>227</v>
       </c>
       <c r="F121" t="s">
-        <v>47</v>
+        <v>228</v>
       </c>
       <c r="G121">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H121" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I121" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J121" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K121" t="s">
         <v>23</v>
       </c>
       <c r="L121">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M121" t="b">
         <v>0</v>
@@ -9205,7 +9214,7 @@
         <v>1</v>
       </c>
       <c r="O121" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P121" t="b">
         <v>1</v>
@@ -9219,40 +9228,40 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B122" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C122" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D122" t="s">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="E122" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F122" t="s">
-        <v>194</v>
+        <v>47</v>
       </c>
       <c r="G122">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H122" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I122" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J122" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K122" t="s">
         <v>23</v>
       </c>
       <c r="L122">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M122" t="b">
         <v>0</v>
@@ -9261,13 +9270,13 @@
         <v>1</v>
       </c>
       <c r="O122" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P122" t="b">
         <v>1</v>
       </c>
       <c r="Q122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R122" t="b">
         <v>1</v>
@@ -9275,34 +9284,34 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B123" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C123" t="s">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="D123" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E123" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F123" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G123">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H123" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I123" t="s">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="J123" t="s">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="K123" t="s">
         <v>23</v>
@@ -9317,7 +9326,7 @@
         <v>1</v>
       </c>
       <c r="O123" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P123" t="b">
         <v>1</v>
@@ -9331,10 +9340,10 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B124" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C124" t="s">
         <v>184</v>
@@ -9343,13 +9352,13 @@
         <v>200</v>
       </c>
       <c r="E124" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F124" t="s">
         <v>202</v>
       </c>
       <c r="G124">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H124" t="s">
         <v>35</v>
@@ -9373,7 +9382,7 @@
         <v>1</v>
       </c>
       <c r="O124" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P124" t="b">
         <v>1</v>
@@ -9387,10 +9396,10 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B125" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C125" t="s">
         <v>184</v>
@@ -9405,7 +9414,7 @@
         <v>202</v>
       </c>
       <c r="G125">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H125" t="s">
         <v>35</v>
@@ -9429,7 +9438,7 @@
         <v>1</v>
       </c>
       <c r="O125" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P125" t="b">
         <v>1</v>
@@ -9443,41 +9452,41 @@
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B126" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C126" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="D126" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="E126" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F126" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="G126">
+        <v>250</v>
+      </c>
+      <c r="H126" t="s">
+        <v>35</v>
+      </c>
+      <c r="I126" t="s">
+        <v>189</v>
+      </c>
+      <c r="J126" t="s">
+        <v>190</v>
+      </c>
+      <c r="K126" t="s">
+        <v>23</v>
+      </c>
+      <c r="L126">
         <v>6</v>
       </c>
-      <c r="H126" t="s">
-        <v>20</v>
-      </c>
-      <c r="I126" t="s">
-        <v>237</v>
-      </c>
-      <c r="J126" t="s">
-        <v>233</v>
-      </c>
-      <c r="K126" t="s">
-        <v>23</v>
-      </c>
-      <c r="L126">
-        <v>1</v>
-      </c>
       <c r="M126" t="b">
         <v>0</v>
       </c>
@@ -9485,13 +9494,13 @@
         <v>1</v>
       </c>
       <c r="O126" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R126" t="b">
         <v>1</v>
@@ -9499,57 +9508,113 @@
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B127" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C127" t="s">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="D127" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="E127" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="F127" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G127">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H127" t="s">
         <v>20</v>
       </c>
       <c r="I127" t="s">
+        <v>237</v>
+      </c>
+      <c r="J127" t="s">
+        <v>233</v>
+      </c>
+      <c r="K127" t="s">
+        <v>23</v>
+      </c>
+      <c r="L127">
+        <v>1</v>
+      </c>
+      <c r="M127" t="b">
+        <v>0</v>
+      </c>
+      <c r="N127" t="b">
+        <v>1</v>
+      </c>
+      <c r="O127" t="s">
+        <v>308</v>
+      </c>
+      <c r="P127" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="b">
+        <v>1</v>
+      </c>
+      <c r="R127" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>72</v>
+      </c>
+      <c r="B128" t="s">
+        <v>417</v>
+      </c>
+      <c r="C128" t="s">
+        <v>195</v>
+      </c>
+      <c r="D128" t="s">
+        <v>196</v>
+      </c>
+      <c r="E128" t="s">
+        <v>197</v>
+      </c>
+      <c r="F128" t="s">
+        <v>238</v>
+      </c>
+      <c r="G128">
+        <v>4</v>
+      </c>
+      <c r="H128" t="s">
+        <v>20</v>
+      </c>
+      <c r="I128" t="s">
         <v>21</v>
       </c>
-      <c r="J127" t="s">
+      <c r="J128" t="s">
         <v>199</v>
       </c>
-      <c r="K127" t="s">
-        <v>23</v>
-      </c>
-      <c r="L127">
+      <c r="K128" t="s">
+        <v>23</v>
+      </c>
+      <c r="L128">
         <v>10</v>
       </c>
-      <c r="M127" t="b">
-        <v>0</v>
-      </c>
-      <c r="N127" t="b">
-        <v>0</v>
-      </c>
-      <c r="O127" t="s">
+      <c r="M128" t="b">
+        <v>0</v>
+      </c>
+      <c r="N128" t="b">
+        <v>0</v>
+      </c>
+      <c r="O128" t="s">
         <v>309</v>
       </c>
-      <c r="P127" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q127" t="b">
-        <v>1</v>
-      </c>
-      <c r="R127" t="b">
+      <c r="P128" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q128" t="b">
+        <v>1</v>
+      </c>
+      <c r="R128" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D01CD1-EAD9-4E2B-8A74-75EACB493791}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF20BF0-25D1-42AA-883A-2044FFE73076}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="76" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="77" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="690">
   <si>
     <t>Codigo</t>
   </si>
@@ -2075,6 +2075,27 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7791866001197.png</t>
+  </si>
+  <si>
+    <t>7793046001416</t>
+  </si>
+  <si>
+    <t>Dulce</t>
+  </si>
+  <si>
+    <t>de batata</t>
+  </si>
+  <si>
+    <t>a la vainilla</t>
+  </si>
+  <si>
+    <t>Dulcor</t>
+  </si>
+  <si>
+    <t>Dulces</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7793046001416.png</t>
   </si>
 </sst>
 </file>
@@ -2426,8 +2447,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABADBA17-6C44-418D-9C36-1A9520D58FD3}">
-  <dimension ref="A1:R128"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F2548CD-4639-4365-8D52-C9367429DA92}">
+  <dimension ref="A1:R129"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -6652,34 +6673,34 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="B76" t="s">
-        <v>584</v>
+        <v>683</v>
       </c>
       <c r="C76" t="s">
-        <v>585</v>
+        <v>684</v>
       </c>
       <c r="D76" t="s">
-        <v>541</v>
+        <v>685</v>
       </c>
       <c r="E76" t="s">
-        <v>586</v>
+        <v>686</v>
       </c>
       <c r="F76" t="s">
-        <v>517</v>
+        <v>687</v>
       </c>
       <c r="G76">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="H76" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I76" t="s">
-        <v>490</v>
+        <v>96</v>
       </c>
       <c r="J76" t="s">
-        <v>587</v>
+        <v>688</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
@@ -6694,7 +6715,7 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>588</v>
+        <v>689</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -6708,37 +6729,37 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B77" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C77" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="D77" t="s">
-        <v>591</v>
+        <v>541</v>
       </c>
       <c r="E77" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="F77" t="s">
-        <v>593</v>
+        <v>517</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H77" t="s">
         <v>20</v>
       </c>
       <c r="I77" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="J77" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="K77" t="s">
-        <v>595</v>
+        <v>23</v>
       </c>
       <c r="L77">
         <v>12</v>
@@ -6747,10 +6768,10 @@
         <v>0</v>
       </c>
       <c r="N77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6764,49 +6785,49 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B78" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="C78" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="D78" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="E78" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="F78" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="G78">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H78" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I78" t="s">
         <v>53</v>
       </c>
       <c r="J78" t="s">
-        <v>76</v>
+        <v>594</v>
       </c>
       <c r="K78" t="s">
-        <v>23</v>
+        <v>595</v>
       </c>
       <c r="L78">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
       </c>
       <c r="N78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O78" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6820,49 +6841,49 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B79" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="C79" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="D79" t="s">
-        <v>172</v>
+        <v>598</v>
       </c>
       <c r="E79" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="F79" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="H79" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I79" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J79" t="s">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
       </c>
       <c r="N79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6871,27 +6892,27 @@
         <v>1</v>
       </c>
       <c r="R79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B80" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C80" t="s">
-        <v>607</v>
+        <v>195</v>
       </c>
       <c r="D80" t="s">
-        <v>608</v>
+        <v>172</v>
       </c>
       <c r="E80" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="F80" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -6900,16 +6921,16 @@
         <v>20</v>
       </c>
       <c r="I80" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J80" t="s">
-        <v>611</v>
+        <v>243</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
@@ -6918,7 +6939,7 @@
         <v>0</v>
       </c>
       <c r="O80" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6927,39 +6948,39 @@
         <v>1</v>
       </c>
       <c r="R80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B81" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="C81" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="D81" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="E81" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="F81" t="s">
-        <v>111</v>
+        <v>610</v>
       </c>
       <c r="G81">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H81" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I81" t="s">
         <v>490</v>
       </c>
       <c r="J81" t="s">
-        <v>576</v>
+        <v>611</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
@@ -6971,10 +6992,10 @@
         <v>0</v>
       </c>
       <c r="N81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O81" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6988,25 +7009,25 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B82" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C82" t="s">
-        <v>174</v>
+        <v>614</v>
       </c>
       <c r="D82" t="s">
-        <v>175</v>
+        <v>615</v>
       </c>
       <c r="E82" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="F82" t="s">
-        <v>620</v>
+        <v>111</v>
       </c>
       <c r="G82">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H82" t="s">
         <v>42</v>
@@ -7015,13 +7036,13 @@
         <v>490</v>
       </c>
       <c r="J82" t="s">
-        <v>177</v>
+        <v>576</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
       </c>
       <c r="L82">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
@@ -7030,7 +7051,7 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -7044,40 +7065,40 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="B83" t="s">
-        <v>373</v>
+        <v>618</v>
       </c>
       <c r="C83" t="s">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="D83" t="s">
-        <v>89</v>
+        <v>175</v>
       </c>
       <c r="E83" t="s">
-        <v>90</v>
+        <v>619</v>
       </c>
       <c r="F83" t="s">
-        <v>91</v>
+        <v>620</v>
       </c>
       <c r="G83">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="H83" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I83" t="s">
-        <v>36</v>
+        <v>490</v>
       </c>
       <c r="J83" t="s">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
       </c>
       <c r="L83">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
@@ -7086,13 +7107,13 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>265</v>
+        <v>621</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
       </c>
       <c r="Q83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" t="b">
         <v>1</v>
@@ -7100,40 +7121,40 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C84" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D84" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E84" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F84" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G84">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H84" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I84" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J84" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
       </c>
       <c r="L84">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
@@ -7142,7 +7163,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -7156,41 +7177,41 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B85" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C85" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D85" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E85" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F85" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H85" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I85" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J85" t="s">
+        <v>66</v>
+      </c>
+      <c r="K85" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85">
         <v>30</v>
       </c>
-      <c r="K85" t="s">
-        <v>23</v>
-      </c>
-      <c r="L85">
-        <v>12</v>
-      </c>
       <c r="M85" t="b">
         <v>0</v>
       </c>
@@ -7198,13 +7219,13 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
       </c>
       <c r="Q85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" t="b">
         <v>1</v>
@@ -7212,55 +7233,55 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
+        <v>29</v>
+      </c>
+      <c r="B86" t="s">
+        <v>375</v>
+      </c>
+      <c r="C86" t="s">
+        <v>24</v>
+      </c>
+      <c r="D86" t="s">
+        <v>54</v>
+      </c>
+      <c r="E86" t="s">
+        <v>55</v>
+      </c>
+      <c r="F86" t="s">
+        <v>61</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+      <c r="H86" t="s">
+        <v>28</v>
+      </c>
+      <c r="I86" t="s">
+        <v>96</v>
+      </c>
+      <c r="J86" t="s">
         <v>30</v>
       </c>
-      <c r="B86" t="s">
-        <v>376</v>
-      </c>
-      <c r="C86" t="s">
-        <v>97</v>
-      </c>
-      <c r="D86" t="s">
-        <v>98</v>
-      </c>
-      <c r="E86" t="s">
-        <v>99</v>
-      </c>
-      <c r="F86" t="s">
-        <v>100</v>
-      </c>
-      <c r="G86">
-        <v>100</v>
-      </c>
-      <c r="H86" t="s">
-        <v>20</v>
-      </c>
-      <c r="I86" t="s">
-        <v>101</v>
-      </c>
-      <c r="J86" t="s">
-        <v>102</v>
-      </c>
       <c r="K86" t="s">
         <v>23</v>
       </c>
       <c r="L86">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
       </c>
       <c r="N86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
       </c>
       <c r="Q86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" t="b">
         <v>1</v>
@@ -7268,49 +7289,49 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B87" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C87" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D87" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E87" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F87" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G87">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H87" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I87" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J87" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
       </c>
       <c r="L87">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
       </c>
       <c r="N87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O87" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -7324,22 +7345,22 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B88" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C88" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D88" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E88" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F88" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G88">
         <v>500</v>
@@ -7351,13 +7372,13 @@
         <v>107</v>
       </c>
       <c r="J88" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
@@ -7366,7 +7387,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -7380,40 +7401,40 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B89" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C89" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D89" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E89" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F89" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G89">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H89" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I89" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J89" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
@@ -7422,13 +7443,13 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
       </c>
       <c r="Q89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R89" t="b">
         <v>1</v>
@@ -7436,40 +7457,40 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B90" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C90" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D90" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E90" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F90" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G90">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H90" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I90" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J90" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
       </c>
       <c r="L90">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -7478,13 +7499,13 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
       </c>
       <c r="Q90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" t="b">
         <v>1</v>
@@ -7492,40 +7513,40 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
+        <v>34</v>
+      </c>
+      <c r="B91" t="s">
+        <v>380</v>
+      </c>
+      <c r="C91" t="s">
+        <v>112</v>
+      </c>
+      <c r="D91" t="s">
+        <v>113</v>
+      </c>
+      <c r="E91" t="s">
+        <v>114</v>
+      </c>
+      <c r="F91" t="s">
+        <v>115</v>
+      </c>
+      <c r="G91">
+        <v>300</v>
+      </c>
+      <c r="H91" t="s">
         <v>35</v>
       </c>
-      <c r="B91" t="s">
-        <v>381</v>
-      </c>
-      <c r="C91" t="s">
-        <v>117</v>
-      </c>
-      <c r="D91" t="s">
-        <v>118</v>
-      </c>
-      <c r="E91" t="s">
-        <v>119</v>
-      </c>
-      <c r="F91" t="s">
-        <v>120</v>
-      </c>
-      <c r="G91">
-        <v>500</v>
-      </c>
-      <c r="H91" t="s">
-        <v>42</v>
-      </c>
       <c r="I91" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J91" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -7534,7 +7555,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -7548,40 +7569,40 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B92" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C92" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D92" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E92" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F92" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G92">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H92" t="s">
         <v>42</v>
       </c>
       <c r="I92" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J92" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
       </c>
       <c r="L92">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -7590,13 +7611,13 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
       </c>
       <c r="Q92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="b">
         <v>1</v>
@@ -7604,40 +7625,40 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B93" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C93" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D93" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E93" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F93" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G93">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H93" t="s">
         <v>42</v>
       </c>
       <c r="I93" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J93" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
       </c>
       <c r="L93">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -7646,13 +7667,13 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
       </c>
       <c r="Q93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
@@ -7660,34 +7681,34 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B94" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C94" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D94" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E94" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F94" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G94">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H94" t="s">
         <v>42</v>
       </c>
       <c r="I94" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J94" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
@@ -7702,13 +7723,13 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
       </c>
       <c r="Q94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R94" t="b">
         <v>1</v>
@@ -7716,40 +7737,40 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B95" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C95" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D95" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E95" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F95" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G95">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H95" t="s">
         <v>42</v>
       </c>
       <c r="I95" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J95" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
       </c>
       <c r="L95">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
@@ -7758,7 +7779,7 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
@@ -7772,40 +7793,40 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B96" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C96" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D96" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E96" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F96" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G96">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H96" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I96" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J96" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
       </c>
       <c r="L96">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
@@ -7814,7 +7835,7 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
@@ -7828,55 +7849,55 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B97" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C97" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D97" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E97" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F97" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G97">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H97" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I97" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J97" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K97" t="s">
         <v>23</v>
       </c>
       <c r="L97">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
       </c>
       <c r="Q97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" t="b">
         <v>1</v>
@@ -7884,10 +7905,10 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B98" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C98" t="s">
         <v>138</v>
@@ -7896,10 +7917,10 @@
         <v>139</v>
       </c>
       <c r="E98" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F98" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G98">
         <v>1000</v>
@@ -7923,10 +7944,10 @@
         <v>1</v>
       </c>
       <c r="N98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O98" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
@@ -7940,22 +7961,22 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B99" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C99" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D99" t="s">
         <v>139</v>
       </c>
       <c r="E99" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F99" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G99">
         <v>1000</v>
@@ -7967,7 +7988,7 @@
         <v>142</v>
       </c>
       <c r="J99" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K99" t="s">
         <v>23</v>
@@ -7982,7 +8003,7 @@
         <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
@@ -7996,55 +8017,55 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B100" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C100" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D100" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E100" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F100" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G100">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H100" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I100" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J100" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K100" t="s">
         <v>23</v>
       </c>
       <c r="L100">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
       </c>
       <c r="Q100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R100" t="b">
         <v>1</v>
@@ -8052,55 +8073,55 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B101" t="s">
-        <v>645</v>
+        <v>390</v>
       </c>
       <c r="C101" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D101" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E101" t="s">
-        <v>646</v>
+        <v>151</v>
       </c>
       <c r="F101" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G101">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H101" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I101" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="J101" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="K101" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="L101">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M101" t="b">
         <v>0</v>
       </c>
       <c r="N101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>647</v>
+        <v>282</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
       </c>
       <c r="Q101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" t="b">
         <v>1</v>
@@ -8108,55 +8129,55 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B102" t="s">
-        <v>391</v>
+        <v>645</v>
       </c>
       <c r="C102" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D102" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E102" t="s">
-        <v>163</v>
+        <v>646</v>
       </c>
       <c r="F102" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G102">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H102" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I102" t="s">
-        <v>29</v>
+        <v>158</v>
       </c>
       <c r="J102" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K102" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="L102">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M102" t="b">
         <v>0</v>
       </c>
       <c r="N102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O102" t="s">
-        <v>283</v>
+        <v>647</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
       </c>
       <c r="Q102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R102" t="b">
         <v>1</v>
@@ -8164,34 +8185,34 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B103" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C103" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D103" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E103" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F103" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G103">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H103" t="s">
         <v>42</v>
       </c>
       <c r="I103" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J103" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="K103" t="s">
         <v>23</v>
@@ -8206,7 +8227,7 @@
         <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
@@ -8220,22 +8241,22 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B104" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C104" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D104" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E104" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F104" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="G104">
         <v>500</v>
@@ -8247,7 +8268,7 @@
         <v>21</v>
       </c>
       <c r="J104" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K104" t="s">
         <v>23</v>
@@ -8262,7 +8283,7 @@
         <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
@@ -8276,34 +8297,34 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B105" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C105" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D105" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E105" t="s">
-        <v>622</v>
+        <v>172</v>
       </c>
       <c r="F105" t="s">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="G105">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H105" t="s">
         <v>42</v>
       </c>
       <c r="I105" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J105" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="K105" t="s">
         <v>23</v>
@@ -8318,7 +8339,7 @@
         <v>1</v>
       </c>
       <c r="O105" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
@@ -8332,37 +8353,37 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
+        <v>49</v>
+      </c>
+      <c r="B106" t="s">
+        <v>394</v>
+      </c>
+      <c r="C106" t="s">
+        <v>174</v>
+      </c>
+      <c r="D106" t="s">
+        <v>175</v>
+      </c>
+      <c r="E106" t="s">
+        <v>622</v>
+      </c>
+      <c r="F106" t="s">
+        <v>176</v>
+      </c>
+      <c r="G106">
         <v>50</v>
       </c>
-      <c r="B106" t="s">
-        <v>395</v>
-      </c>
-      <c r="C106" t="s">
-        <v>178</v>
-      </c>
-      <c r="D106" t="s">
-        <v>179</v>
-      </c>
-      <c r="E106" t="s">
-        <v>180</v>
-      </c>
-      <c r="F106" t="s">
-        <v>181</v>
-      </c>
-      <c r="G106">
-        <v>12</v>
-      </c>
       <c r="H106" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I106" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="J106" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="K106" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="L106">
         <v>12</v>
@@ -8374,7 +8395,7 @@
         <v>1</v>
       </c>
       <c r="O106" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
@@ -8388,40 +8409,40 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B107" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C107" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D107" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E107" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F107" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G107">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H107" t="s">
-        <v>188</v>
+        <v>20</v>
       </c>
       <c r="I107" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="J107" t="s">
-        <v>552</v>
+        <v>182</v>
       </c>
       <c r="K107" t="s">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="L107">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M107" t="b">
         <v>0</v>
@@ -8430,7 +8451,7 @@
         <v>1</v>
       </c>
       <c r="O107" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
@@ -8444,40 +8465,40 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B108" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C108" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D108" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E108" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F108" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="G108">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H108" t="s">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="I108" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
       <c r="J108" t="s">
-        <v>182</v>
+        <v>552</v>
       </c>
       <c r="K108" t="s">
         <v>23</v>
       </c>
       <c r="L108">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M108" t="b">
         <v>0</v>
@@ -8486,7 +8507,7 @@
         <v>1</v>
       </c>
       <c r="O108" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P108" t="b">
         <v>1</v>
@@ -8500,40 +8521,40 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
+        <v>52</v>
+      </c>
+      <c r="B109" t="s">
+        <v>397</v>
+      </c>
+      <c r="C109" t="s">
+        <v>191</v>
+      </c>
+      <c r="D109" t="s">
+        <v>179</v>
+      </c>
+      <c r="E109" t="s">
+        <v>180</v>
+      </c>
+      <c r="F109" t="s">
+        <v>181</v>
+      </c>
+      <c r="G109">
+        <v>24</v>
+      </c>
+      <c r="H109" t="s">
+        <v>20</v>
+      </c>
+      <c r="I109" t="s">
         <v>53</v>
       </c>
-      <c r="B109" t="s">
-        <v>398</v>
-      </c>
-      <c r="C109" t="s">
-        <v>31</v>
-      </c>
-      <c r="D109" t="s">
-        <v>192</v>
-      </c>
-      <c r="E109" t="s">
-        <v>193</v>
-      </c>
-      <c r="F109" t="s">
-        <v>194</v>
-      </c>
-      <c r="G109">
-        <v>1.5</v>
-      </c>
-      <c r="H109" t="s">
-        <v>28</v>
-      </c>
-      <c r="I109" t="s">
-        <v>36</v>
-      </c>
       <c r="J109" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="K109" t="s">
         <v>23</v>
       </c>
       <c r="L109">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M109" t="b">
         <v>0</v>
@@ -8542,7 +8563,7 @@
         <v>1</v>
       </c>
       <c r="O109" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P109" t="b">
         <v>1</v>
@@ -8556,52 +8577,52 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C110" t="s">
-        <v>195</v>
+        <v>31</v>
       </c>
       <c r="D110" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E110" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F110" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G110">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H110" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I110" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J110" t="s">
-        <v>199</v>
+        <v>37</v>
       </c>
       <c r="K110" t="s">
         <v>23</v>
       </c>
       <c r="L110">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M110" t="b">
         <v>0</v>
       </c>
       <c r="N110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O110" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q110" t="b">
         <v>1</v>
@@ -8612,55 +8633,55 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B111" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C111" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="D111" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E111" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F111" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G111">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H111" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I111" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="J111" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="K111" t="s">
         <v>23</v>
       </c>
       <c r="L111">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M111" t="b">
         <v>0</v>
       </c>
       <c r="N111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O111" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R111" t="b">
         <v>1</v>
@@ -8668,40 +8689,40 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B112" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C112" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="D112" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E112" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F112" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G112">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H112" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I112" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="J112" t="s">
-        <v>66</v>
+        <v>190</v>
       </c>
       <c r="K112" t="s">
         <v>23</v>
       </c>
       <c r="L112">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M112" t="b">
         <v>0</v>
@@ -8710,7 +8731,7 @@
         <v>1</v>
       </c>
       <c r="O112" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P112" t="b">
         <v>1</v>
@@ -8724,19 +8745,19 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B113" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C113" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D113" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E113" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F113" t="s">
         <v>206</v>
@@ -8766,7 +8787,7 @@
         <v>1</v>
       </c>
       <c r="O113" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P113" t="b">
         <v>1</v>
@@ -8780,19 +8801,19 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B114" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C114" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D114" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E114" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F114" t="s">
         <v>206</v>
@@ -8813,7 +8834,7 @@
         <v>23</v>
       </c>
       <c r="L114">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M114" t="b">
         <v>0</v>
@@ -8822,7 +8843,7 @@
         <v>1</v>
       </c>
       <c r="O114" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P114" t="b">
         <v>1</v>
@@ -8836,34 +8857,34 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B115" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C115" t="s">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="D115" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E115" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F115" t="s">
-        <v>56</v>
+        <v>206</v>
       </c>
       <c r="G115">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H115" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I115" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="J115" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K115" t="s">
         <v>23</v>
@@ -8878,13 +8899,13 @@
         <v>1</v>
       </c>
       <c r="O115" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P115" t="b">
         <v>1</v>
       </c>
       <c r="Q115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R115" t="b">
         <v>1</v>
@@ -8892,34 +8913,34 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B116" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C116" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D116" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="E116" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="F116" t="s">
-        <v>214</v>
+        <v>56</v>
       </c>
       <c r="G116">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H116" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I116" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J116" t="s">
-        <v>553</v>
+        <v>148</v>
       </c>
       <c r="K116" t="s">
         <v>23</v>
@@ -8934,7 +8955,7 @@
         <v>1</v>
       </c>
       <c r="O116" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P116" t="b">
         <v>1</v>
@@ -8948,49 +8969,49 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B117" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C117" t="s">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="D117" t="s">
-        <v>216</v>
+        <v>81</v>
       </c>
       <c r="E117" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="F117" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G117">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H117" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I117" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J117" t="s">
-        <v>215</v>
+        <v>553</v>
       </c>
       <c r="K117" t="s">
         <v>23</v>
       </c>
       <c r="L117">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M117" t="b">
         <v>0</v>
       </c>
       <c r="N117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O117" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P117" t="b">
         <v>1</v>
@@ -9004,22 +9025,22 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B118" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C118" t="s">
         <v>215</v>
       </c>
       <c r="D118" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E118" t="s">
         <v>217</v>
       </c>
       <c r="F118" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G118">
         <v>20</v>
@@ -9046,13 +9067,13 @@
         <v>0</v>
       </c>
       <c r="O118" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P118" t="b">
         <v>1</v>
       </c>
       <c r="Q118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R118" t="b">
         <v>1</v>
@@ -9060,49 +9081,49 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B119" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C119" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D119" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="E119" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F119" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="G119">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H119" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I119" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J119" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K119" t="s">
         <v>23</v>
       </c>
       <c r="L119">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M119" t="b">
         <v>0</v>
       </c>
       <c r="N119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O119" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P119" t="b">
         <v>1</v>
@@ -9116,34 +9137,34 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B120" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C120" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D120" t="s">
         <v>200</v>
       </c>
       <c r="E120" t="s">
-        <v>32</v>
+        <v>201</v>
       </c>
       <c r="F120" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="G120">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H120" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I120" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J120" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="K120" t="s">
         <v>23</v>
@@ -9158,7 +9179,7 @@
         <v>1</v>
       </c>
       <c r="O120" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P120" t="b">
         <v>1</v>
@@ -9172,40 +9193,40 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B121" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C121" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D121" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="E121" t="s">
-        <v>227</v>
+        <v>32</v>
       </c>
       <c r="F121" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G121">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H121" t="s">
         <v>42</v>
       </c>
       <c r="I121" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J121" t="s">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="K121" t="s">
         <v>23</v>
       </c>
       <c r="L121">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M121" t="b">
         <v>0</v>
@@ -9214,13 +9235,13 @@
         <v>1</v>
       </c>
       <c r="O121" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P121" t="b">
         <v>1</v>
       </c>
       <c r="Q121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R121" t="b">
         <v>1</v>
@@ -9228,40 +9249,40 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B122" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C122" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
       <c r="D122" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E122" t="s">
         <v>227</v>
       </c>
       <c r="F122" t="s">
-        <v>47</v>
+        <v>228</v>
       </c>
       <c r="G122">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H122" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I122" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J122" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K122" t="s">
         <v>23</v>
       </c>
       <c r="L122">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M122" t="b">
         <v>0</v>
@@ -9270,7 +9291,7 @@
         <v>1</v>
       </c>
       <c r="O122" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P122" t="b">
         <v>1</v>
@@ -9284,40 +9305,40 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B123" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C123" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D123" t="s">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="E123" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F123" t="s">
-        <v>194</v>
+        <v>47</v>
       </c>
       <c r="G123">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H123" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I123" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J123" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K123" t="s">
         <v>23</v>
       </c>
       <c r="L123">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M123" t="b">
         <v>0</v>
@@ -9326,13 +9347,13 @@
         <v>1</v>
       </c>
       <c r="O123" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P123" t="b">
         <v>1</v>
       </c>
       <c r="Q123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R123" t="b">
         <v>1</v>
@@ -9340,34 +9361,34 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B124" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C124" t="s">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="D124" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E124" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F124" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G124">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H124" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I124" t="s">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="J124" t="s">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="K124" t="s">
         <v>23</v>
@@ -9382,7 +9403,7 @@
         <v>1</v>
       </c>
       <c r="O124" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P124" t="b">
         <v>1</v>
@@ -9396,10 +9417,10 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B125" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C125" t="s">
         <v>184</v>
@@ -9408,13 +9429,13 @@
         <v>200</v>
       </c>
       <c r="E125" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F125" t="s">
         <v>202</v>
       </c>
       <c r="G125">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H125" t="s">
         <v>35</v>
@@ -9438,7 +9459,7 @@
         <v>1</v>
       </c>
       <c r="O125" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P125" t="b">
         <v>1</v>
@@ -9452,10 +9473,10 @@
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B126" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C126" t="s">
         <v>184</v>
@@ -9470,7 +9491,7 @@
         <v>202</v>
       </c>
       <c r="G126">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H126" t="s">
         <v>35</v>
@@ -9494,7 +9515,7 @@
         <v>1</v>
       </c>
       <c r="O126" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P126" t="b">
         <v>1</v>
@@ -9508,41 +9529,41 @@
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B127" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C127" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="D127" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="E127" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F127" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="G127">
+        <v>250</v>
+      </c>
+      <c r="H127" t="s">
+        <v>35</v>
+      </c>
+      <c r="I127" t="s">
+        <v>189</v>
+      </c>
+      <c r="J127" t="s">
+        <v>190</v>
+      </c>
+      <c r="K127" t="s">
+        <v>23</v>
+      </c>
+      <c r="L127">
         <v>6</v>
       </c>
-      <c r="H127" t="s">
-        <v>20</v>
-      </c>
-      <c r="I127" t="s">
-        <v>237</v>
-      </c>
-      <c r="J127" t="s">
-        <v>233</v>
-      </c>
-      <c r="K127" t="s">
-        <v>23</v>
-      </c>
-      <c r="L127">
-        <v>1</v>
-      </c>
       <c r="M127" t="b">
         <v>0</v>
       </c>
@@ -9550,13 +9571,13 @@
         <v>1</v>
       </c>
       <c r="O127" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R127" t="b">
         <v>1</v>
@@ -9564,57 +9585,113 @@
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B128" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C128" t="s">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="D128" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="E128" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="F128" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G128">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H128" t="s">
         <v>20</v>
       </c>
       <c r="I128" t="s">
+        <v>237</v>
+      </c>
+      <c r="J128" t="s">
+        <v>233</v>
+      </c>
+      <c r="K128" t="s">
+        <v>23</v>
+      </c>
+      <c r="L128">
+        <v>1</v>
+      </c>
+      <c r="M128" t="b">
+        <v>0</v>
+      </c>
+      <c r="N128" t="b">
+        <v>1</v>
+      </c>
+      <c r="O128" t="s">
+        <v>308</v>
+      </c>
+      <c r="P128" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="b">
+        <v>1</v>
+      </c>
+      <c r="R128" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>72</v>
+      </c>
+      <c r="B129" t="s">
+        <v>417</v>
+      </c>
+      <c r="C129" t="s">
+        <v>195</v>
+      </c>
+      <c r="D129" t="s">
+        <v>196</v>
+      </c>
+      <c r="E129" t="s">
+        <v>197</v>
+      </c>
+      <c r="F129" t="s">
+        <v>238</v>
+      </c>
+      <c r="G129">
+        <v>4</v>
+      </c>
+      <c r="H129" t="s">
+        <v>20</v>
+      </c>
+      <c r="I129" t="s">
         <v>21</v>
       </c>
-      <c r="J128" t="s">
+      <c r="J129" t="s">
         <v>199</v>
       </c>
-      <c r="K128" t="s">
-        <v>23</v>
-      </c>
-      <c r="L128">
+      <c r="K129" t="s">
+        <v>23</v>
+      </c>
+      <c r="L129">
         <v>10</v>
       </c>
-      <c r="M128" t="b">
-        <v>0</v>
-      </c>
-      <c r="N128" t="b">
-        <v>0</v>
-      </c>
-      <c r="O128" t="s">
+      <c r="M129" t="b">
+        <v>0</v>
+      </c>
+      <c r="N129" t="b">
+        <v>0</v>
+      </c>
+      <c r="O129" t="s">
         <v>309</v>
       </c>
-      <c r="P128" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q128" t="b">
-        <v>1</v>
-      </c>
-      <c r="R128" t="b">
+      <c r="P129" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q129" t="b">
+        <v>1</v>
+      </c>
+      <c r="R129" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF20BF0-25D1-42AA-883A-2044FFE73076}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B90666-B566-4502-B1ED-0FEEFCA64A55}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="77" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="78" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="698">
   <si>
     <t>Codigo</t>
   </si>
@@ -2096,6 +2096,30 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7793046001416.png</t>
+  </si>
+  <si>
+    <t>047400179240</t>
+  </si>
+  <si>
+    <t>Repuesto</t>
+  </si>
+  <si>
+    <t>para máquina de afeitar</t>
+  </si>
+  <si>
+    <t>match 3</t>
+  </si>
+  <si>
+    <t>Gillette</t>
+  </si>
+  <si>
+    <t>blister</t>
+  </si>
+  <si>
+    <t>Perfumería</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\047400179240.png</t>
   </si>
 </sst>
 </file>
@@ -2447,8 +2471,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F2548CD-4639-4365-8D52-C9367429DA92}">
-  <dimension ref="A1:R129"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9C8F266-7FA3-4121-AAFA-09564096B23A}">
+  <dimension ref="A1:R130"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -6729,22 +6753,22 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="B77" t="s">
-        <v>584</v>
+        <v>690</v>
       </c>
       <c r="C77" t="s">
-        <v>585</v>
+        <v>691</v>
       </c>
       <c r="D77" t="s">
-        <v>541</v>
+        <v>692</v>
       </c>
       <c r="E77" t="s">
-        <v>586</v>
+        <v>693</v>
       </c>
       <c r="F77" t="s">
-        <v>517</v>
+        <v>694</v>
       </c>
       <c r="G77">
         <v>2</v>
@@ -6753,69 +6777,69 @@
         <v>20</v>
       </c>
       <c r="I77" t="s">
-        <v>490</v>
+        <v>695</v>
       </c>
       <c r="J77" t="s">
-        <v>587</v>
+        <v>696</v>
       </c>
       <c r="K77" t="s">
-        <v>23</v>
+        <v>595</v>
       </c>
       <c r="L77">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
       </c>
       <c r="N77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="s">
-        <v>588</v>
+        <v>697</v>
       </c>
       <c r="P77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="b">
         <v>1</v>
       </c>
       <c r="R77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B78" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C78" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="D78" t="s">
-        <v>591</v>
+        <v>541</v>
       </c>
       <c r="E78" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="F78" t="s">
-        <v>593</v>
+        <v>517</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" t="s">
         <v>20</v>
       </c>
       <c r="I78" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="J78" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="K78" t="s">
-        <v>595</v>
+        <v>23</v>
       </c>
       <c r="L78">
         <v>12</v>
@@ -6824,10 +6848,10 @@
         <v>0</v>
       </c>
       <c r="N78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6841,49 +6865,49 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B79" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="C79" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="D79" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="E79" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="F79" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="G79">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H79" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I79" t="s">
         <v>53</v>
       </c>
       <c r="J79" t="s">
-        <v>76</v>
+        <v>594</v>
       </c>
       <c r="K79" t="s">
-        <v>23</v>
+        <v>595</v>
       </c>
       <c r="L79">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
       </c>
       <c r="N79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O79" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6897,49 +6921,49 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B80" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="C80" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="D80" t="s">
-        <v>172</v>
+        <v>598</v>
       </c>
       <c r="E80" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="F80" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="H80" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I80" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J80" t="s">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
       </c>
       <c r="N80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6948,27 +6972,27 @@
         <v>1</v>
       </c>
       <c r="R80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B81" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C81" t="s">
-        <v>607</v>
+        <v>195</v>
       </c>
       <c r="D81" t="s">
-        <v>608</v>
+        <v>172</v>
       </c>
       <c r="E81" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="F81" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -6977,16 +7001,16 @@
         <v>20</v>
       </c>
       <c r="I81" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J81" t="s">
-        <v>611</v>
+        <v>243</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
@@ -6995,7 +7019,7 @@
         <v>0</v>
       </c>
       <c r="O81" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -7004,39 +7028,39 @@
         <v>1</v>
       </c>
       <c r="R81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B82" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="C82" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="D82" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="E82" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="F82" t="s">
-        <v>111</v>
+        <v>610</v>
       </c>
       <c r="G82">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H82" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I82" t="s">
         <v>490</v>
       </c>
       <c r="J82" t="s">
-        <v>576</v>
+        <v>611</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
@@ -7048,10 +7072,10 @@
         <v>0</v>
       </c>
       <c r="N82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O82" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -7065,25 +7089,25 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B83" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C83" t="s">
-        <v>174</v>
+        <v>614</v>
       </c>
       <c r="D83" t="s">
-        <v>175</v>
+        <v>615</v>
       </c>
       <c r="E83" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="F83" t="s">
-        <v>620</v>
+        <v>111</v>
       </c>
       <c r="G83">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H83" t="s">
         <v>42</v>
@@ -7092,13 +7116,13 @@
         <v>490</v>
       </c>
       <c r="J83" t="s">
-        <v>177</v>
+        <v>576</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
       </c>
       <c r="L83">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
@@ -7107,7 +7131,7 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -7121,40 +7145,40 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="B84" t="s">
-        <v>373</v>
+        <v>618</v>
       </c>
       <c r="C84" t="s">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="D84" t="s">
-        <v>89</v>
+        <v>175</v>
       </c>
       <c r="E84" t="s">
-        <v>90</v>
+        <v>619</v>
       </c>
       <c r="F84" t="s">
-        <v>91</v>
+        <v>620</v>
       </c>
       <c r="G84">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="H84" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I84" t="s">
-        <v>36</v>
+        <v>490</v>
       </c>
       <c r="J84" t="s">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
       </c>
       <c r="L84">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
@@ -7163,13 +7187,13 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>265</v>
+        <v>621</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
       </c>
       <c r="Q84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" t="b">
         <v>1</v>
@@ -7177,40 +7201,40 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C85" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D85" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E85" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F85" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G85">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H85" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I85" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J85" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
       </c>
       <c r="L85">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
@@ -7219,7 +7243,7 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -7233,41 +7257,41 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B86" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C86" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D86" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E86" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F86" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G86">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H86" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I86" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J86" t="s">
+        <v>66</v>
+      </c>
+      <c r="K86" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86">
         <v>30</v>
       </c>
-      <c r="K86" t="s">
-        <v>23</v>
-      </c>
-      <c r="L86">
-        <v>12</v>
-      </c>
       <c r="M86" t="b">
         <v>0</v>
       </c>
@@ -7275,13 +7299,13 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
       </c>
       <c r="Q86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R86" t="b">
         <v>1</v>
@@ -7289,55 +7313,55 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
+        <v>29</v>
+      </c>
+      <c r="B87" t="s">
+        <v>375</v>
+      </c>
+      <c r="C87" t="s">
+        <v>24</v>
+      </c>
+      <c r="D87" t="s">
+        <v>54</v>
+      </c>
+      <c r="E87" t="s">
+        <v>55</v>
+      </c>
+      <c r="F87" t="s">
+        <v>61</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+      <c r="H87" t="s">
+        <v>28</v>
+      </c>
+      <c r="I87" t="s">
+        <v>96</v>
+      </c>
+      <c r="J87" t="s">
         <v>30</v>
       </c>
-      <c r="B87" t="s">
-        <v>376</v>
-      </c>
-      <c r="C87" t="s">
-        <v>97</v>
-      </c>
-      <c r="D87" t="s">
-        <v>98</v>
-      </c>
-      <c r="E87" t="s">
-        <v>99</v>
-      </c>
-      <c r="F87" t="s">
-        <v>100</v>
-      </c>
-      <c r="G87">
-        <v>100</v>
-      </c>
-      <c r="H87" t="s">
-        <v>20</v>
-      </c>
-      <c r="I87" t="s">
-        <v>101</v>
-      </c>
-      <c r="J87" t="s">
-        <v>102</v>
-      </c>
       <c r="K87" t="s">
         <v>23</v>
       </c>
       <c r="L87">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
       </c>
       <c r="N87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
       </c>
       <c r="Q87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87" t="b">
         <v>1</v>
@@ -7345,49 +7369,49 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B88" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C88" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D88" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E88" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F88" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G88">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H88" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I88" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J88" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
       </c>
       <c r="N88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -7401,22 +7425,22 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B89" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C89" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D89" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E89" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F89" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G89">
         <v>500</v>
@@ -7428,13 +7452,13 @@
         <v>107</v>
       </c>
       <c r="J89" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
@@ -7443,7 +7467,7 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -7457,40 +7481,40 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B90" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C90" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D90" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E90" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F90" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H90" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I90" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J90" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
       </c>
       <c r="L90">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -7499,13 +7523,13 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
       </c>
       <c r="Q90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="b">
         <v>1</v>
@@ -7513,40 +7537,40 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B91" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C91" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D91" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E91" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F91" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G91">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H91" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I91" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J91" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -7555,13 +7579,13 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
       </c>
       <c r="Q91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" t="b">
         <v>1</v>
@@ -7569,40 +7593,40 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
+        <v>34</v>
+      </c>
+      <c r="B92" t="s">
+        <v>380</v>
+      </c>
+      <c r="C92" t="s">
+        <v>112</v>
+      </c>
+      <c r="D92" t="s">
+        <v>113</v>
+      </c>
+      <c r="E92" t="s">
+        <v>114</v>
+      </c>
+      <c r="F92" t="s">
+        <v>115</v>
+      </c>
+      <c r="G92">
+        <v>300</v>
+      </c>
+      <c r="H92" t="s">
         <v>35</v>
       </c>
-      <c r="B92" t="s">
-        <v>381</v>
-      </c>
-      <c r="C92" t="s">
-        <v>117</v>
-      </c>
-      <c r="D92" t="s">
-        <v>118</v>
-      </c>
-      <c r="E92" t="s">
-        <v>119</v>
-      </c>
-      <c r="F92" t="s">
-        <v>120</v>
-      </c>
-      <c r="G92">
-        <v>500</v>
-      </c>
-      <c r="H92" t="s">
-        <v>42</v>
-      </c>
       <c r="I92" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J92" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
       </c>
       <c r="L92">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -7611,7 +7635,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -7625,40 +7649,40 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B93" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C93" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D93" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E93" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F93" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G93">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H93" t="s">
         <v>42</v>
       </c>
       <c r="I93" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J93" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
       </c>
       <c r="L93">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -7667,13 +7691,13 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
       </c>
       <c r="Q93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
@@ -7681,40 +7705,40 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B94" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C94" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D94" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E94" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F94" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G94">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H94" t="s">
         <v>42</v>
       </c>
       <c r="I94" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J94" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
       </c>
       <c r="L94">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -7723,13 +7747,13 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
       </c>
       <c r="Q94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94" t="b">
         <v>1</v>
@@ -7737,34 +7761,34 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B95" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C95" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D95" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E95" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F95" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G95">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H95" t="s">
         <v>42</v>
       </c>
       <c r="I95" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J95" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
@@ -7779,13 +7803,13 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
       </c>
       <c r="Q95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R95" t="b">
         <v>1</v>
@@ -7793,40 +7817,40 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B96" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C96" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D96" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E96" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F96" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G96">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H96" t="s">
         <v>42</v>
       </c>
       <c r="I96" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J96" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
       </c>
       <c r="L96">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
@@ -7835,7 +7859,7 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
@@ -7849,40 +7873,40 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B97" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C97" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D97" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E97" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F97" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G97">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H97" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I97" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J97" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K97" t="s">
         <v>23</v>
       </c>
       <c r="L97">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
@@ -7891,7 +7915,7 @@
         <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
@@ -7905,55 +7929,55 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B98" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C98" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D98" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E98" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F98" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G98">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H98" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I98" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J98" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K98" t="s">
         <v>23</v>
       </c>
       <c r="L98">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
       </c>
       <c r="Q98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" t="b">
         <v>1</v>
@@ -7961,10 +7985,10 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B99" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C99" t="s">
         <v>138</v>
@@ -7973,10 +7997,10 @@
         <v>139</v>
       </c>
       <c r="E99" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F99" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G99">
         <v>1000</v>
@@ -8000,10 +8024,10 @@
         <v>1</v>
       </c>
       <c r="N99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O99" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
@@ -8017,22 +8041,22 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B100" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C100" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D100" t="s">
         <v>139</v>
       </c>
       <c r="E100" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F100" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G100">
         <v>1000</v>
@@ -8044,7 +8068,7 @@
         <v>142</v>
       </c>
       <c r="J100" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K100" t="s">
         <v>23</v>
@@ -8059,7 +8083,7 @@
         <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
@@ -8073,55 +8097,55 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B101" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C101" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D101" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E101" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F101" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G101">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H101" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I101" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J101" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K101" t="s">
         <v>23</v>
       </c>
       <c r="L101">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
       </c>
       <c r="Q101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R101" t="b">
         <v>1</v>
@@ -8129,55 +8153,55 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B102" t="s">
-        <v>645</v>
+        <v>390</v>
       </c>
       <c r="C102" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D102" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E102" t="s">
-        <v>646</v>
+        <v>151</v>
       </c>
       <c r="F102" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G102">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H102" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I102" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="J102" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="K102" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="L102">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M102" t="b">
         <v>0</v>
       </c>
       <c r="N102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>647</v>
+        <v>282</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
       </c>
       <c r="Q102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R102" t="b">
         <v>1</v>
@@ -8185,55 +8209,55 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B103" t="s">
-        <v>391</v>
+        <v>645</v>
       </c>
       <c r="C103" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D103" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E103" t="s">
-        <v>163</v>
+        <v>646</v>
       </c>
       <c r="F103" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G103">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H103" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I103" t="s">
-        <v>29</v>
+        <v>158</v>
       </c>
       <c r="J103" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K103" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="L103">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M103" t="b">
         <v>0</v>
       </c>
       <c r="N103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O103" t="s">
-        <v>283</v>
+        <v>647</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
       </c>
       <c r="Q103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R103" t="b">
         <v>1</v>
@@ -8241,34 +8265,34 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B104" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C104" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D104" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E104" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F104" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G104">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H104" t="s">
         <v>42</v>
       </c>
       <c r="I104" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J104" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="K104" t="s">
         <v>23</v>
@@ -8283,7 +8307,7 @@
         <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
@@ -8297,22 +8321,22 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B105" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C105" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D105" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E105" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F105" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="G105">
         <v>500</v>
@@ -8324,7 +8348,7 @@
         <v>21</v>
       </c>
       <c r="J105" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K105" t="s">
         <v>23</v>
@@ -8339,7 +8363,7 @@
         <v>1</v>
       </c>
       <c r="O105" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
@@ -8353,34 +8377,34 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B106" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C106" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D106" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E106" t="s">
-        <v>622</v>
+        <v>172</v>
       </c>
       <c r="F106" t="s">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="G106">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H106" t="s">
         <v>42</v>
       </c>
       <c r="I106" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J106" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="K106" t="s">
         <v>23</v>
@@ -8395,7 +8419,7 @@
         <v>1</v>
       </c>
       <c r="O106" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
@@ -8409,37 +8433,37 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
+        <v>49</v>
+      </c>
+      <c r="B107" t="s">
+        <v>394</v>
+      </c>
+      <c r="C107" t="s">
+        <v>174</v>
+      </c>
+      <c r="D107" t="s">
+        <v>175</v>
+      </c>
+      <c r="E107" t="s">
+        <v>622</v>
+      </c>
+      <c r="F107" t="s">
+        <v>176</v>
+      </c>
+      <c r="G107">
         <v>50</v>
       </c>
-      <c r="B107" t="s">
-        <v>395</v>
-      </c>
-      <c r="C107" t="s">
-        <v>178</v>
-      </c>
-      <c r="D107" t="s">
-        <v>179</v>
-      </c>
-      <c r="E107" t="s">
-        <v>180</v>
-      </c>
-      <c r="F107" t="s">
-        <v>181</v>
-      </c>
-      <c r="G107">
-        <v>12</v>
-      </c>
       <c r="H107" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I107" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="J107" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="K107" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="L107">
         <v>12</v>
@@ -8451,7 +8475,7 @@
         <v>1</v>
       </c>
       <c r="O107" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
@@ -8465,40 +8489,40 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B108" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C108" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D108" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E108" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F108" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G108">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H108" t="s">
-        <v>188</v>
+        <v>20</v>
       </c>
       <c r="I108" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="J108" t="s">
-        <v>552</v>
+        <v>182</v>
       </c>
       <c r="K108" t="s">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="L108">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M108" t="b">
         <v>0</v>
@@ -8507,7 +8531,7 @@
         <v>1</v>
       </c>
       <c r="O108" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P108" t="b">
         <v>1</v>
@@ -8521,40 +8545,40 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B109" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C109" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D109" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E109" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F109" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="G109">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H109" t="s">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="I109" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
       <c r="J109" t="s">
-        <v>182</v>
+        <v>552</v>
       </c>
       <c r="K109" t="s">
         <v>23</v>
       </c>
       <c r="L109">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M109" t="b">
         <v>0</v>
@@ -8563,7 +8587,7 @@
         <v>1</v>
       </c>
       <c r="O109" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P109" t="b">
         <v>1</v>
@@ -8577,40 +8601,40 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
+        <v>52</v>
+      </c>
+      <c r="B110" t="s">
+        <v>397</v>
+      </c>
+      <c r="C110" t="s">
+        <v>191</v>
+      </c>
+      <c r="D110" t="s">
+        <v>179</v>
+      </c>
+      <c r="E110" t="s">
+        <v>180</v>
+      </c>
+      <c r="F110" t="s">
+        <v>181</v>
+      </c>
+      <c r="G110">
+        <v>24</v>
+      </c>
+      <c r="H110" t="s">
+        <v>20</v>
+      </c>
+      <c r="I110" t="s">
         <v>53</v>
       </c>
-      <c r="B110" t="s">
-        <v>398</v>
-      </c>
-      <c r="C110" t="s">
-        <v>31</v>
-      </c>
-      <c r="D110" t="s">
-        <v>192</v>
-      </c>
-      <c r="E110" t="s">
-        <v>193</v>
-      </c>
-      <c r="F110" t="s">
-        <v>194</v>
-      </c>
-      <c r="G110">
-        <v>1.5</v>
-      </c>
-      <c r="H110" t="s">
-        <v>28</v>
-      </c>
-      <c r="I110" t="s">
-        <v>36</v>
-      </c>
       <c r="J110" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="K110" t="s">
         <v>23</v>
       </c>
       <c r="L110">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M110" t="b">
         <v>0</v>
@@ -8619,7 +8643,7 @@
         <v>1</v>
       </c>
       <c r="O110" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P110" t="b">
         <v>1</v>
@@ -8633,52 +8657,52 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C111" t="s">
-        <v>195</v>
+        <v>31</v>
       </c>
       <c r="D111" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E111" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F111" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G111">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H111" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I111" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J111" t="s">
-        <v>199</v>
+        <v>37</v>
       </c>
       <c r="K111" t="s">
         <v>23</v>
       </c>
       <c r="L111">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M111" t="b">
         <v>0</v>
       </c>
       <c r="N111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q111" t="b">
         <v>1</v>
@@ -8689,55 +8713,55 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B112" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C112" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="D112" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E112" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F112" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G112">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H112" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I112" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="J112" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="K112" t="s">
         <v>23</v>
       </c>
       <c r="L112">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M112" t="b">
         <v>0</v>
       </c>
       <c r="N112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O112" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R112" t="b">
         <v>1</v>
@@ -8745,40 +8769,40 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B113" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C113" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="D113" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E113" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F113" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G113">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H113" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I113" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="J113" t="s">
-        <v>66</v>
+        <v>190</v>
       </c>
       <c r="K113" t="s">
         <v>23</v>
       </c>
       <c r="L113">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M113" t="b">
         <v>0</v>
@@ -8787,7 +8811,7 @@
         <v>1</v>
       </c>
       <c r="O113" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P113" t="b">
         <v>1</v>
@@ -8801,19 +8825,19 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B114" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C114" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D114" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E114" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F114" t="s">
         <v>206</v>
@@ -8843,7 +8867,7 @@
         <v>1</v>
       </c>
       <c r="O114" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P114" t="b">
         <v>1</v>
@@ -8857,19 +8881,19 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B115" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C115" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D115" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E115" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F115" t="s">
         <v>206</v>
@@ -8890,7 +8914,7 @@
         <v>23</v>
       </c>
       <c r="L115">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M115" t="b">
         <v>0</v>
@@ -8899,7 +8923,7 @@
         <v>1</v>
       </c>
       <c r="O115" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P115" t="b">
         <v>1</v>
@@ -8913,34 +8937,34 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B116" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C116" t="s">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="D116" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E116" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F116" t="s">
-        <v>56</v>
+        <v>206</v>
       </c>
       <c r="G116">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H116" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I116" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="J116" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K116" t="s">
         <v>23</v>
@@ -8955,13 +8979,13 @@
         <v>1</v>
       </c>
       <c r="O116" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P116" t="b">
         <v>1</v>
       </c>
       <c r="Q116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R116" t="b">
         <v>1</v>
@@ -8969,34 +8993,34 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B117" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C117" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D117" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="E117" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="F117" t="s">
-        <v>214</v>
+        <v>56</v>
       </c>
       <c r="G117">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H117" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I117" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J117" t="s">
-        <v>553</v>
+        <v>148</v>
       </c>
       <c r="K117" t="s">
         <v>23</v>
@@ -9011,7 +9035,7 @@
         <v>1</v>
       </c>
       <c r="O117" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P117" t="b">
         <v>1</v>
@@ -9025,49 +9049,49 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B118" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C118" t="s">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="D118" t="s">
-        <v>216</v>
+        <v>81</v>
       </c>
       <c r="E118" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="F118" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G118">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H118" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I118" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J118" t="s">
-        <v>215</v>
+        <v>553</v>
       </c>
       <c r="K118" t="s">
         <v>23</v>
       </c>
       <c r="L118">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M118" t="b">
         <v>0</v>
       </c>
       <c r="N118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O118" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P118" t="b">
         <v>1</v>
@@ -9081,22 +9105,22 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B119" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C119" t="s">
         <v>215</v>
       </c>
       <c r="D119" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E119" t="s">
         <v>217</v>
       </c>
       <c r="F119" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G119">
         <v>20</v>
@@ -9123,13 +9147,13 @@
         <v>0</v>
       </c>
       <c r="O119" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P119" t="b">
         <v>1</v>
       </c>
       <c r="Q119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R119" t="b">
         <v>1</v>
@@ -9137,49 +9161,49 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B120" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C120" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D120" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="E120" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F120" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="G120">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H120" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I120" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J120" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K120" t="s">
         <v>23</v>
       </c>
       <c r="L120">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M120" t="b">
         <v>0</v>
       </c>
       <c r="N120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O120" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P120" t="b">
         <v>1</v>
@@ -9193,34 +9217,34 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B121" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C121" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D121" t="s">
         <v>200</v>
       </c>
       <c r="E121" t="s">
-        <v>32</v>
+        <v>201</v>
       </c>
       <c r="F121" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="G121">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H121" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I121" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J121" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="K121" t="s">
         <v>23</v>
@@ -9235,7 +9259,7 @@
         <v>1</v>
       </c>
       <c r="O121" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P121" t="b">
         <v>1</v>
@@ -9249,40 +9273,40 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B122" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C122" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D122" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="E122" t="s">
-        <v>227</v>
+        <v>32</v>
       </c>
       <c r="F122" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G122">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H122" t="s">
         <v>42</v>
       </c>
       <c r="I122" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J122" t="s">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="K122" t="s">
         <v>23</v>
       </c>
       <c r="L122">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M122" t="b">
         <v>0</v>
@@ -9291,13 +9315,13 @@
         <v>1</v>
       </c>
       <c r="O122" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P122" t="b">
         <v>1</v>
       </c>
       <c r="Q122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R122" t="b">
         <v>1</v>
@@ -9305,40 +9329,40 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B123" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C123" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
       <c r="D123" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E123" t="s">
         <v>227</v>
       </c>
       <c r="F123" t="s">
-        <v>47</v>
+        <v>228</v>
       </c>
       <c r="G123">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H123" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I123" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J123" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K123" t="s">
         <v>23</v>
       </c>
       <c r="L123">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M123" t="b">
         <v>0</v>
@@ -9347,7 +9371,7 @@
         <v>1</v>
       </c>
       <c r="O123" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P123" t="b">
         <v>1</v>
@@ -9361,40 +9385,40 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B124" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C124" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D124" t="s">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="E124" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F124" t="s">
-        <v>194</v>
+        <v>47</v>
       </c>
       <c r="G124">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H124" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I124" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J124" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K124" t="s">
         <v>23</v>
       </c>
       <c r="L124">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M124" t="b">
         <v>0</v>
@@ -9403,13 +9427,13 @@
         <v>1</v>
       </c>
       <c r="O124" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P124" t="b">
         <v>1</v>
       </c>
       <c r="Q124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R124" t="b">
         <v>1</v>
@@ -9417,34 +9441,34 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B125" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C125" t="s">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="D125" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E125" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F125" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G125">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H125" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I125" t="s">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="J125" t="s">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="K125" t="s">
         <v>23</v>
@@ -9459,7 +9483,7 @@
         <v>1</v>
       </c>
       <c r="O125" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P125" t="b">
         <v>1</v>
@@ -9473,10 +9497,10 @@
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B126" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C126" t="s">
         <v>184</v>
@@ -9485,13 +9509,13 @@
         <v>200</v>
       </c>
       <c r="E126" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F126" t="s">
         <v>202</v>
       </c>
       <c r="G126">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H126" t="s">
         <v>35</v>
@@ -9515,7 +9539,7 @@
         <v>1</v>
       </c>
       <c r="O126" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P126" t="b">
         <v>1</v>
@@ -9529,10 +9553,10 @@
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B127" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C127" t="s">
         <v>184</v>
@@ -9547,7 +9571,7 @@
         <v>202</v>
       </c>
       <c r="G127">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H127" t="s">
         <v>35</v>
@@ -9571,7 +9595,7 @@
         <v>1</v>
       </c>
       <c r="O127" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P127" t="b">
         <v>1</v>
@@ -9585,41 +9609,41 @@
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B128" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C128" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="D128" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="E128" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F128" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="G128">
+        <v>250</v>
+      </c>
+      <c r="H128" t="s">
+        <v>35</v>
+      </c>
+      <c r="I128" t="s">
+        <v>189</v>
+      </c>
+      <c r="J128" t="s">
+        <v>190</v>
+      </c>
+      <c r="K128" t="s">
+        <v>23</v>
+      </c>
+      <c r="L128">
         <v>6</v>
       </c>
-      <c r="H128" t="s">
-        <v>20</v>
-      </c>
-      <c r="I128" t="s">
-        <v>237</v>
-      </c>
-      <c r="J128" t="s">
-        <v>233</v>
-      </c>
-      <c r="K128" t="s">
-        <v>23</v>
-      </c>
-      <c r="L128">
-        <v>1</v>
-      </c>
       <c r="M128" t="b">
         <v>0</v>
       </c>
@@ -9627,13 +9651,13 @@
         <v>1</v>
       </c>
       <c r="O128" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R128" t="b">
         <v>1</v>
@@ -9641,57 +9665,113 @@
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B129" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C129" t="s">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="D129" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="E129" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="F129" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G129">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H129" t="s">
         <v>20</v>
       </c>
       <c r="I129" t="s">
+        <v>237</v>
+      </c>
+      <c r="J129" t="s">
+        <v>233</v>
+      </c>
+      <c r="K129" t="s">
+        <v>23</v>
+      </c>
+      <c r="L129">
+        <v>1</v>
+      </c>
+      <c r="M129" t="b">
+        <v>0</v>
+      </c>
+      <c r="N129" t="b">
+        <v>1</v>
+      </c>
+      <c r="O129" t="s">
+        <v>308</v>
+      </c>
+      <c r="P129" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="b">
+        <v>1</v>
+      </c>
+      <c r="R129" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>72</v>
+      </c>
+      <c r="B130" t="s">
+        <v>417</v>
+      </c>
+      <c r="C130" t="s">
+        <v>195</v>
+      </c>
+      <c r="D130" t="s">
+        <v>196</v>
+      </c>
+      <c r="E130" t="s">
+        <v>197</v>
+      </c>
+      <c r="F130" t="s">
+        <v>238</v>
+      </c>
+      <c r="G130">
+        <v>4</v>
+      </c>
+      <c r="H130" t="s">
+        <v>20</v>
+      </c>
+      <c r="I130" t="s">
         <v>21</v>
       </c>
-      <c r="J129" t="s">
+      <c r="J130" t="s">
         <v>199</v>
       </c>
-      <c r="K129" t="s">
-        <v>23</v>
-      </c>
-      <c r="L129">
+      <c r="K130" t="s">
+        <v>23</v>
+      </c>
+      <c r="L130">
         <v>10</v>
       </c>
-      <c r="M129" t="b">
-        <v>0</v>
-      </c>
-      <c r="N129" t="b">
-        <v>0</v>
-      </c>
-      <c r="O129" t="s">
+      <c r="M130" t="b">
+        <v>0</v>
+      </c>
+      <c r="N130" t="b">
+        <v>0</v>
+      </c>
+      <c r="O130" t="s">
         <v>309</v>
       </c>
-      <c r="P129" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q129" t="b">
-        <v>1</v>
-      </c>
-      <c r="R129" t="b">
+      <c r="P130" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q130" t="b">
+        <v>1</v>
+      </c>
+      <c r="R130" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B90666-B566-4502-B1ED-0FEEFCA64A55}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869219E5-BB2C-4E79-9D00-C103200C82BE}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="78" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="79" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="706">
   <si>
     <t>Codigo</t>
   </si>
@@ -2120,6 +2120,30 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\047400179240.png</t>
+  </si>
+  <si>
+    <t>039800013613</t>
+  </si>
+  <si>
+    <t>Batería</t>
+  </si>
+  <si>
+    <t>9 voltios</t>
+  </si>
+  <si>
+    <t>alcalina</t>
+  </si>
+  <si>
+    <t>Energizer</t>
+  </si>
+  <si>
+    <t>Pilas</t>
+  </si>
+  <si>
+    <t>Malasia</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\039800013613.png</t>
   </si>
 </sst>
 </file>
@@ -2471,8 +2495,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9C8F266-7FA3-4121-AAFA-09564096B23A}">
-  <dimension ref="A1:R130"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F8846C-9FAF-40B1-8447-0F855A47D92E}">
+  <dimension ref="A1:R131"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -6809,40 +6833,40 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B78" t="s">
-        <v>584</v>
+        <v>698</v>
       </c>
       <c r="C78" t="s">
-        <v>585</v>
+        <v>699</v>
       </c>
       <c r="D78" t="s">
-        <v>541</v>
+        <v>700</v>
       </c>
       <c r="E78" t="s">
-        <v>586</v>
+        <v>701</v>
       </c>
       <c r="F78" t="s">
-        <v>517</v>
+        <v>702</v>
       </c>
       <c r="G78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" t="s">
         <v>20</v>
       </c>
       <c r="I78" t="s">
-        <v>490</v>
+        <v>695</v>
       </c>
       <c r="J78" t="s">
-        <v>587</v>
+        <v>703</v>
       </c>
       <c r="K78" t="s">
-        <v>23</v>
+        <v>704</v>
       </c>
       <c r="L78">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -6851,7 +6875,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>588</v>
+        <v>705</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6865,37 +6889,37 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B79" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C79" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="D79" t="s">
-        <v>591</v>
+        <v>541</v>
       </c>
       <c r="E79" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="F79" t="s">
-        <v>593</v>
+        <v>517</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H79" t="s">
         <v>20</v>
       </c>
       <c r="I79" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="J79" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="K79" t="s">
-        <v>595</v>
+        <v>23</v>
       </c>
       <c r="L79">
         <v>12</v>
@@ -6904,10 +6928,10 @@
         <v>0</v>
       </c>
       <c r="N79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6921,49 +6945,49 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B80" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="C80" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="D80" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="E80" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="F80" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="G80">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H80" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I80" t="s">
         <v>53</v>
       </c>
       <c r="J80" t="s">
-        <v>76</v>
+        <v>594</v>
       </c>
       <c r="K80" t="s">
-        <v>23</v>
+        <v>595</v>
       </c>
       <c r="L80">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
       </c>
       <c r="N80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6977,49 +7001,49 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B81" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="C81" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="D81" t="s">
-        <v>172</v>
+        <v>598</v>
       </c>
       <c r="E81" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="F81" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="H81" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I81" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J81" t="s">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
       </c>
       <c r="N81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -7028,27 +7052,27 @@
         <v>1</v>
       </c>
       <c r="R81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B82" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C82" t="s">
-        <v>607</v>
+        <v>195</v>
       </c>
       <c r="D82" t="s">
-        <v>608</v>
+        <v>172</v>
       </c>
       <c r="E82" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="F82" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -7057,16 +7081,16 @@
         <v>20</v>
       </c>
       <c r="I82" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J82" t="s">
-        <v>611</v>
+        <v>243</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
       </c>
       <c r="L82">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
@@ -7075,7 +7099,7 @@
         <v>0</v>
       </c>
       <c r="O82" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -7084,39 +7108,39 @@
         <v>1</v>
       </c>
       <c r="R82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B83" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="C83" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="D83" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="E83" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="F83" t="s">
-        <v>111</v>
+        <v>610</v>
       </c>
       <c r="G83">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H83" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I83" t="s">
         <v>490</v>
       </c>
       <c r="J83" t="s">
-        <v>576</v>
+        <v>611</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
@@ -7128,10 +7152,10 @@
         <v>0</v>
       </c>
       <c r="N83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O83" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -7145,25 +7169,25 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B84" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C84" t="s">
-        <v>174</v>
+        <v>614</v>
       </c>
       <c r="D84" t="s">
-        <v>175</v>
+        <v>615</v>
       </c>
       <c r="E84" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="F84" t="s">
-        <v>620</v>
+        <v>111</v>
       </c>
       <c r="G84">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H84" t="s">
         <v>42</v>
@@ -7172,13 +7196,13 @@
         <v>490</v>
       </c>
       <c r="J84" t="s">
-        <v>177</v>
+        <v>576</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
       </c>
       <c r="L84">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
@@ -7187,7 +7211,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -7201,40 +7225,40 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="B85" t="s">
-        <v>373</v>
+        <v>618</v>
       </c>
       <c r="C85" t="s">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="D85" t="s">
-        <v>89</v>
+        <v>175</v>
       </c>
       <c r="E85" t="s">
-        <v>90</v>
+        <v>619</v>
       </c>
       <c r="F85" t="s">
-        <v>91</v>
+        <v>620</v>
       </c>
       <c r="G85">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="H85" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I85" t="s">
-        <v>36</v>
+        <v>490</v>
       </c>
       <c r="J85" t="s">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
       </c>
       <c r="L85">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
@@ -7243,13 +7267,13 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>265</v>
+        <v>621</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
       </c>
       <c r="Q85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" t="b">
         <v>1</v>
@@ -7257,40 +7281,40 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B86" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C86" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D86" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E86" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F86" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G86">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H86" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I86" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J86" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
       </c>
       <c r="L86">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
@@ -7299,7 +7323,7 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -7313,41 +7337,41 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B87" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C87" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D87" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E87" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F87" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G87">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H87" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I87" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J87" t="s">
+        <v>66</v>
+      </c>
+      <c r="K87" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87">
         <v>30</v>
       </c>
-      <c r="K87" t="s">
-        <v>23</v>
-      </c>
-      <c r="L87">
-        <v>12</v>
-      </c>
       <c r="M87" t="b">
         <v>0</v>
       </c>
@@ -7355,13 +7379,13 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
       </c>
       <c r="Q87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" t="b">
         <v>1</v>
@@ -7369,55 +7393,55 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
+        <v>29</v>
+      </c>
+      <c r="B88" t="s">
+        <v>375</v>
+      </c>
+      <c r="C88" t="s">
+        <v>24</v>
+      </c>
+      <c r="D88" t="s">
+        <v>54</v>
+      </c>
+      <c r="E88" t="s">
+        <v>55</v>
+      </c>
+      <c r="F88" t="s">
+        <v>61</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88" t="s">
+        <v>28</v>
+      </c>
+      <c r="I88" t="s">
+        <v>96</v>
+      </c>
+      <c r="J88" t="s">
         <v>30</v>
       </c>
-      <c r="B88" t="s">
-        <v>376</v>
-      </c>
-      <c r="C88" t="s">
-        <v>97</v>
-      </c>
-      <c r="D88" t="s">
-        <v>98</v>
-      </c>
-      <c r="E88" t="s">
-        <v>99</v>
-      </c>
-      <c r="F88" t="s">
-        <v>100</v>
-      </c>
-      <c r="G88">
-        <v>100</v>
-      </c>
-      <c r="H88" t="s">
-        <v>20</v>
-      </c>
-      <c r="I88" t="s">
-        <v>101</v>
-      </c>
-      <c r="J88" t="s">
-        <v>102</v>
-      </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
       </c>
       <c r="N88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
       </c>
       <c r="Q88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" t="b">
         <v>1</v>
@@ -7425,49 +7449,49 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B89" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C89" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D89" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E89" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F89" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G89">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H89" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I89" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J89" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
       </c>
       <c r="N89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -7481,22 +7505,22 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B90" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C90" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D90" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E90" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F90" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G90">
         <v>500</v>
@@ -7508,13 +7532,13 @@
         <v>107</v>
       </c>
       <c r="J90" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
       </c>
       <c r="L90">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -7523,7 +7547,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -7537,40 +7561,40 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B91" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C91" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D91" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E91" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F91" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G91">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H91" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I91" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J91" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -7579,13 +7603,13 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
       </c>
       <c r="Q91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R91" t="b">
         <v>1</v>
@@ -7593,40 +7617,40 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B92" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C92" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D92" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E92" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F92" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G92">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H92" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I92" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J92" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
       </c>
       <c r="L92">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -7635,13 +7659,13 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
       </c>
       <c r="Q92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" t="b">
         <v>1</v>
@@ -7649,40 +7673,40 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
+        <v>34</v>
+      </c>
+      <c r="B93" t="s">
+        <v>380</v>
+      </c>
+      <c r="C93" t="s">
+        <v>112</v>
+      </c>
+      <c r="D93" t="s">
+        <v>113</v>
+      </c>
+      <c r="E93" t="s">
+        <v>114</v>
+      </c>
+      <c r="F93" t="s">
+        <v>115</v>
+      </c>
+      <c r="G93">
+        <v>300</v>
+      </c>
+      <c r="H93" t="s">
         <v>35</v>
       </c>
-      <c r="B93" t="s">
-        <v>381</v>
-      </c>
-      <c r="C93" t="s">
-        <v>117</v>
-      </c>
-      <c r="D93" t="s">
-        <v>118</v>
-      </c>
-      <c r="E93" t="s">
-        <v>119</v>
-      </c>
-      <c r="F93" t="s">
-        <v>120</v>
-      </c>
-      <c r="G93">
-        <v>500</v>
-      </c>
-      <c r="H93" t="s">
-        <v>42</v>
-      </c>
       <c r="I93" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J93" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
       </c>
       <c r="L93">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -7691,7 +7715,7 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
@@ -7705,40 +7729,40 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B94" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C94" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D94" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E94" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F94" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G94">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H94" t="s">
         <v>42</v>
       </c>
       <c r="I94" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J94" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
       </c>
       <c r="L94">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -7747,13 +7771,13 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
       </c>
       <c r="Q94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R94" t="b">
         <v>1</v>
@@ -7761,40 +7785,40 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B95" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C95" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D95" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E95" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F95" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G95">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H95" t="s">
         <v>42</v>
       </c>
       <c r="I95" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J95" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
       </c>
       <c r="L95">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
@@ -7803,13 +7827,13 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
       </c>
       <c r="Q95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R95" t="b">
         <v>1</v>
@@ -7817,34 +7841,34 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B96" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C96" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D96" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E96" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F96" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G96">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H96" t="s">
         <v>42</v>
       </c>
       <c r="I96" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J96" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
@@ -7859,13 +7883,13 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
       </c>
       <c r="Q96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" t="b">
         <v>1</v>
@@ -7873,40 +7897,40 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B97" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C97" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D97" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E97" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F97" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G97">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H97" t="s">
         <v>42</v>
       </c>
       <c r="I97" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J97" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K97" t="s">
         <v>23</v>
       </c>
       <c r="L97">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
@@ -7915,7 +7939,7 @@
         <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
@@ -7929,40 +7953,40 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B98" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C98" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D98" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E98" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F98" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G98">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H98" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I98" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J98" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K98" t="s">
         <v>23</v>
       </c>
       <c r="L98">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M98" t="b">
         <v>0</v>
@@ -7971,7 +7995,7 @@
         <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
@@ -7985,55 +8009,55 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B99" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C99" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D99" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E99" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F99" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G99">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H99" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I99" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J99" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K99" t="s">
         <v>23</v>
       </c>
       <c r="L99">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
       </c>
       <c r="Q99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R99" t="b">
         <v>1</v>
@@ -8041,10 +8065,10 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B100" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C100" t="s">
         <v>138</v>
@@ -8053,10 +8077,10 @@
         <v>139</v>
       </c>
       <c r="E100" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F100" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G100">
         <v>1000</v>
@@ -8080,10 +8104,10 @@
         <v>1</v>
       </c>
       <c r="N100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
@@ -8097,22 +8121,22 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B101" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C101" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D101" t="s">
         <v>139</v>
       </c>
       <c r="E101" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F101" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G101">
         <v>1000</v>
@@ -8124,7 +8148,7 @@
         <v>142</v>
       </c>
       <c r="J101" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K101" t="s">
         <v>23</v>
@@ -8139,7 +8163,7 @@
         <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
@@ -8153,55 +8177,55 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B102" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C102" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D102" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E102" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F102" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G102">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H102" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I102" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J102" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K102" t="s">
         <v>23</v>
       </c>
       <c r="L102">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
       </c>
       <c r="Q102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R102" t="b">
         <v>1</v>
@@ -8209,55 +8233,55 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B103" t="s">
-        <v>645</v>
+        <v>390</v>
       </c>
       <c r="C103" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D103" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E103" t="s">
-        <v>646</v>
+        <v>151</v>
       </c>
       <c r="F103" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G103">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H103" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I103" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="J103" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="K103" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="L103">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M103" t="b">
         <v>0</v>
       </c>
       <c r="N103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>647</v>
+        <v>282</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
       </c>
       <c r="Q103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R103" t="b">
         <v>1</v>
@@ -8265,55 +8289,55 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B104" t="s">
-        <v>391</v>
+        <v>645</v>
       </c>
       <c r="C104" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D104" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E104" t="s">
-        <v>163</v>
+        <v>646</v>
       </c>
       <c r="F104" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G104">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H104" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I104" t="s">
-        <v>29</v>
+        <v>158</v>
       </c>
       <c r="J104" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K104" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="L104">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M104" t="b">
         <v>0</v>
       </c>
       <c r="N104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O104" t="s">
-        <v>283</v>
+        <v>647</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
       </c>
       <c r="Q104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R104" t="b">
         <v>1</v>
@@ -8321,34 +8345,34 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B105" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C105" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D105" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E105" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F105" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G105">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H105" t="s">
         <v>42</v>
       </c>
       <c r="I105" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J105" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="K105" t="s">
         <v>23</v>
@@ -8363,7 +8387,7 @@
         <v>1</v>
       </c>
       <c r="O105" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
@@ -8377,22 +8401,22 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B106" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C106" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D106" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E106" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F106" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="G106">
         <v>500</v>
@@ -8404,7 +8428,7 @@
         <v>21</v>
       </c>
       <c r="J106" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K106" t="s">
         <v>23</v>
@@ -8419,7 +8443,7 @@
         <v>1</v>
       </c>
       <c r="O106" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
@@ -8433,34 +8457,34 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B107" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C107" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D107" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E107" t="s">
-        <v>622</v>
+        <v>172</v>
       </c>
       <c r="F107" t="s">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="G107">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H107" t="s">
         <v>42</v>
       </c>
       <c r="I107" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J107" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="K107" t="s">
         <v>23</v>
@@ -8475,7 +8499,7 @@
         <v>1</v>
       </c>
       <c r="O107" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
@@ -8489,37 +8513,37 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
+        <v>49</v>
+      </c>
+      <c r="B108" t="s">
+        <v>394</v>
+      </c>
+      <c r="C108" t="s">
+        <v>174</v>
+      </c>
+      <c r="D108" t="s">
+        <v>175</v>
+      </c>
+      <c r="E108" t="s">
+        <v>622</v>
+      </c>
+      <c r="F108" t="s">
+        <v>176</v>
+      </c>
+      <c r="G108">
         <v>50</v>
       </c>
-      <c r="B108" t="s">
-        <v>395</v>
-      </c>
-      <c r="C108" t="s">
-        <v>178</v>
-      </c>
-      <c r="D108" t="s">
-        <v>179</v>
-      </c>
-      <c r="E108" t="s">
-        <v>180</v>
-      </c>
-      <c r="F108" t="s">
-        <v>181</v>
-      </c>
-      <c r="G108">
-        <v>12</v>
-      </c>
       <c r="H108" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I108" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="J108" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="K108" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="L108">
         <v>12</v>
@@ -8531,7 +8555,7 @@
         <v>1</v>
       </c>
       <c r="O108" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P108" t="b">
         <v>1</v>
@@ -8545,40 +8569,40 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B109" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C109" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D109" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E109" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F109" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G109">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H109" t="s">
-        <v>188</v>
+        <v>20</v>
       </c>
       <c r="I109" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="J109" t="s">
-        <v>552</v>
+        <v>182</v>
       </c>
       <c r="K109" t="s">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="L109">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M109" t="b">
         <v>0</v>
@@ -8587,7 +8611,7 @@
         <v>1</v>
       </c>
       <c r="O109" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P109" t="b">
         <v>1</v>
@@ -8601,40 +8625,40 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B110" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C110" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D110" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E110" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F110" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="G110">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H110" t="s">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="I110" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
       <c r="J110" t="s">
-        <v>182</v>
+        <v>552</v>
       </c>
       <c r="K110" t="s">
         <v>23</v>
       </c>
       <c r="L110">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M110" t="b">
         <v>0</v>
@@ -8643,7 +8667,7 @@
         <v>1</v>
       </c>
       <c r="O110" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P110" t="b">
         <v>1</v>
@@ -8657,40 +8681,40 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
+        <v>52</v>
+      </c>
+      <c r="B111" t="s">
+        <v>397</v>
+      </c>
+      <c r="C111" t="s">
+        <v>191</v>
+      </c>
+      <c r="D111" t="s">
+        <v>179</v>
+      </c>
+      <c r="E111" t="s">
+        <v>180</v>
+      </c>
+      <c r="F111" t="s">
+        <v>181</v>
+      </c>
+      <c r="G111">
+        <v>24</v>
+      </c>
+      <c r="H111" t="s">
+        <v>20</v>
+      </c>
+      <c r="I111" t="s">
         <v>53</v>
       </c>
-      <c r="B111" t="s">
-        <v>398</v>
-      </c>
-      <c r="C111" t="s">
-        <v>31</v>
-      </c>
-      <c r="D111" t="s">
-        <v>192</v>
-      </c>
-      <c r="E111" t="s">
-        <v>193</v>
-      </c>
-      <c r="F111" t="s">
-        <v>194</v>
-      </c>
-      <c r="G111">
-        <v>1.5</v>
-      </c>
-      <c r="H111" t="s">
-        <v>28</v>
-      </c>
-      <c r="I111" t="s">
-        <v>36</v>
-      </c>
       <c r="J111" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="K111" t="s">
         <v>23</v>
       </c>
       <c r="L111">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M111" t="b">
         <v>0</v>
@@ -8699,7 +8723,7 @@
         <v>1</v>
       </c>
       <c r="O111" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P111" t="b">
         <v>1</v>
@@ -8713,52 +8737,52 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C112" t="s">
-        <v>195</v>
+        <v>31</v>
       </c>
       <c r="D112" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E112" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F112" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G112">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H112" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I112" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J112" t="s">
-        <v>199</v>
+        <v>37</v>
       </c>
       <c r="K112" t="s">
         <v>23</v>
       </c>
       <c r="L112">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M112" t="b">
         <v>0</v>
       </c>
       <c r="N112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q112" t="b">
         <v>1</v>
@@ -8769,55 +8793,55 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B113" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C113" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="D113" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E113" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F113" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G113">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H113" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I113" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="J113" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="K113" t="s">
         <v>23</v>
       </c>
       <c r="L113">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M113" t="b">
         <v>0</v>
       </c>
       <c r="N113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O113" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" t="b">
         <v>1</v>
@@ -8825,40 +8849,40 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B114" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C114" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="D114" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E114" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F114" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G114">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H114" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I114" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="J114" t="s">
-        <v>66</v>
+        <v>190</v>
       </c>
       <c r="K114" t="s">
         <v>23</v>
       </c>
       <c r="L114">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M114" t="b">
         <v>0</v>
@@ -8867,7 +8891,7 @@
         <v>1</v>
       </c>
       <c r="O114" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P114" t="b">
         <v>1</v>
@@ -8881,19 +8905,19 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B115" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C115" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D115" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E115" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F115" t="s">
         <v>206</v>
@@ -8923,7 +8947,7 @@
         <v>1</v>
       </c>
       <c r="O115" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P115" t="b">
         <v>1</v>
@@ -8937,19 +8961,19 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B116" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C116" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D116" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E116" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F116" t="s">
         <v>206</v>
@@ -8970,7 +8994,7 @@
         <v>23</v>
       </c>
       <c r="L116">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M116" t="b">
         <v>0</v>
@@ -8979,7 +9003,7 @@
         <v>1</v>
       </c>
       <c r="O116" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P116" t="b">
         <v>1</v>
@@ -8993,34 +9017,34 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B117" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C117" t="s">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="D117" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E117" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F117" t="s">
-        <v>56</v>
+        <v>206</v>
       </c>
       <c r="G117">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H117" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I117" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="J117" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K117" t="s">
         <v>23</v>
@@ -9035,13 +9059,13 @@
         <v>1</v>
       </c>
       <c r="O117" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P117" t="b">
         <v>1</v>
       </c>
       <c r="Q117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R117" t="b">
         <v>1</v>
@@ -9049,34 +9073,34 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B118" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C118" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D118" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="E118" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="F118" t="s">
-        <v>214</v>
+        <v>56</v>
       </c>
       <c r="G118">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H118" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I118" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J118" t="s">
-        <v>553</v>
+        <v>148</v>
       </c>
       <c r="K118" t="s">
         <v>23</v>
@@ -9091,7 +9115,7 @@
         <v>1</v>
       </c>
       <c r="O118" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P118" t="b">
         <v>1</v>
@@ -9105,49 +9129,49 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B119" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C119" t="s">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="D119" t="s">
-        <v>216</v>
+        <v>81</v>
       </c>
       <c r="E119" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="F119" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G119">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H119" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I119" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J119" t="s">
-        <v>215</v>
+        <v>553</v>
       </c>
       <c r="K119" t="s">
         <v>23</v>
       </c>
       <c r="L119">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M119" t="b">
         <v>0</v>
       </c>
       <c r="N119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O119" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P119" t="b">
         <v>1</v>
@@ -9161,22 +9185,22 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B120" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C120" t="s">
         <v>215</v>
       </c>
       <c r="D120" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E120" t="s">
         <v>217</v>
       </c>
       <c r="F120" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G120">
         <v>20</v>
@@ -9203,13 +9227,13 @@
         <v>0</v>
       </c>
       <c r="O120" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P120" t="b">
         <v>1</v>
       </c>
       <c r="Q120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R120" t="b">
         <v>1</v>
@@ -9217,49 +9241,49 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B121" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C121" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D121" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="E121" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F121" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="G121">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H121" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I121" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J121" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K121" t="s">
         <v>23</v>
       </c>
       <c r="L121">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M121" t="b">
         <v>0</v>
       </c>
       <c r="N121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O121" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P121" t="b">
         <v>1</v>
@@ -9273,34 +9297,34 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B122" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C122" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D122" t="s">
         <v>200</v>
       </c>
       <c r="E122" t="s">
-        <v>32</v>
+        <v>201</v>
       </c>
       <c r="F122" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="G122">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H122" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I122" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J122" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="K122" t="s">
         <v>23</v>
@@ -9315,7 +9339,7 @@
         <v>1</v>
       </c>
       <c r="O122" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P122" t="b">
         <v>1</v>
@@ -9329,40 +9353,40 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B123" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C123" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D123" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="E123" t="s">
-        <v>227</v>
+        <v>32</v>
       </c>
       <c r="F123" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G123">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H123" t="s">
         <v>42</v>
       </c>
       <c r="I123" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J123" t="s">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="K123" t="s">
         <v>23</v>
       </c>
       <c r="L123">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M123" t="b">
         <v>0</v>
@@ -9371,13 +9395,13 @@
         <v>1</v>
       </c>
       <c r="O123" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P123" t="b">
         <v>1</v>
       </c>
       <c r="Q123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R123" t="b">
         <v>1</v>
@@ -9385,40 +9409,40 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B124" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C124" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
       <c r="D124" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E124" t="s">
         <v>227</v>
       </c>
       <c r="F124" t="s">
-        <v>47</v>
+        <v>228</v>
       </c>
       <c r="G124">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H124" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I124" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J124" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K124" t="s">
         <v>23</v>
       </c>
       <c r="L124">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M124" t="b">
         <v>0</v>
@@ -9427,7 +9451,7 @@
         <v>1</v>
       </c>
       <c r="O124" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P124" t="b">
         <v>1</v>
@@ -9441,40 +9465,40 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B125" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C125" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D125" t="s">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="E125" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F125" t="s">
-        <v>194</v>
+        <v>47</v>
       </c>
       <c r="G125">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H125" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I125" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J125" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K125" t="s">
         <v>23</v>
       </c>
       <c r="L125">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M125" t="b">
         <v>0</v>
@@ -9483,13 +9507,13 @@
         <v>1</v>
       </c>
       <c r="O125" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P125" t="b">
         <v>1</v>
       </c>
       <c r="Q125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R125" t="b">
         <v>1</v>
@@ -9497,34 +9521,34 @@
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B126" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C126" t="s">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="D126" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E126" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F126" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G126">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H126" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I126" t="s">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="J126" t="s">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="K126" t="s">
         <v>23</v>
@@ -9539,7 +9563,7 @@
         <v>1</v>
       </c>
       <c r="O126" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P126" t="b">
         <v>1</v>
@@ -9553,10 +9577,10 @@
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B127" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C127" t="s">
         <v>184</v>
@@ -9565,13 +9589,13 @@
         <v>200</v>
       </c>
       <c r="E127" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F127" t="s">
         <v>202</v>
       </c>
       <c r="G127">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H127" t="s">
         <v>35</v>
@@ -9595,7 +9619,7 @@
         <v>1</v>
       </c>
       <c r="O127" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P127" t="b">
         <v>1</v>
@@ -9609,10 +9633,10 @@
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B128" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C128" t="s">
         <v>184</v>
@@ -9627,7 +9651,7 @@
         <v>202</v>
       </c>
       <c r="G128">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H128" t="s">
         <v>35</v>
@@ -9651,7 +9675,7 @@
         <v>1</v>
       </c>
       <c r="O128" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P128" t="b">
         <v>1</v>
@@ -9665,41 +9689,41 @@
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B129" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C129" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="D129" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="E129" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F129" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="G129">
+        <v>250</v>
+      </c>
+      <c r="H129" t="s">
+        <v>35</v>
+      </c>
+      <c r="I129" t="s">
+        <v>189</v>
+      </c>
+      <c r="J129" t="s">
+        <v>190</v>
+      </c>
+      <c r="K129" t="s">
+        <v>23</v>
+      </c>
+      <c r="L129">
         <v>6</v>
       </c>
-      <c r="H129" t="s">
-        <v>20</v>
-      </c>
-      <c r="I129" t="s">
-        <v>237</v>
-      </c>
-      <c r="J129" t="s">
-        <v>233</v>
-      </c>
-      <c r="K129" t="s">
-        <v>23</v>
-      </c>
-      <c r="L129">
-        <v>1</v>
-      </c>
       <c r="M129" t="b">
         <v>0</v>
       </c>
@@ -9707,13 +9731,13 @@
         <v>1</v>
       </c>
       <c r="O129" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R129" t="b">
         <v>1</v>
@@ -9721,57 +9745,113 @@
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B130" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C130" t="s">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="D130" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="E130" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="F130" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G130">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H130" t="s">
         <v>20</v>
       </c>
       <c r="I130" t="s">
+        <v>237</v>
+      </c>
+      <c r="J130" t="s">
+        <v>233</v>
+      </c>
+      <c r="K130" t="s">
+        <v>23</v>
+      </c>
+      <c r="L130">
+        <v>1</v>
+      </c>
+      <c r="M130" t="b">
+        <v>0</v>
+      </c>
+      <c r="N130" t="b">
+        <v>1</v>
+      </c>
+      <c r="O130" t="s">
+        <v>308</v>
+      </c>
+      <c r="P130" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="b">
+        <v>1</v>
+      </c>
+      <c r="R130" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>72</v>
+      </c>
+      <c r="B131" t="s">
+        <v>417</v>
+      </c>
+      <c r="C131" t="s">
+        <v>195</v>
+      </c>
+      <c r="D131" t="s">
+        <v>196</v>
+      </c>
+      <c r="E131" t="s">
+        <v>197</v>
+      </c>
+      <c r="F131" t="s">
+        <v>238</v>
+      </c>
+      <c r="G131">
+        <v>4</v>
+      </c>
+      <c r="H131" t="s">
+        <v>20</v>
+      </c>
+      <c r="I131" t="s">
         <v>21</v>
       </c>
-      <c r="J130" t="s">
+      <c r="J131" t="s">
         <v>199</v>
       </c>
-      <c r="K130" t="s">
-        <v>23</v>
-      </c>
-      <c r="L130">
+      <c r="K131" t="s">
+        <v>23</v>
+      </c>
+      <c r="L131">
         <v>10</v>
       </c>
-      <c r="M130" t="b">
-        <v>0</v>
-      </c>
-      <c r="N130" t="b">
-        <v>0</v>
-      </c>
-      <c r="O130" t="s">
+      <c r="M131" t="b">
+        <v>0</v>
+      </c>
+      <c r="N131" t="b">
+        <v>0</v>
+      </c>
+      <c r="O131" t="s">
         <v>309</v>
       </c>
-      <c r="P130" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q130" t="b">
-        <v>1</v>
-      </c>
-      <c r="R130" t="b">
+      <c r="P131" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q131" t="b">
+        <v>1</v>
+      </c>
+      <c r="R131" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869219E5-BB2C-4E79-9D00-C103200C82BE}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9BAEABD-EEB8-4DD3-863B-D8DD11D61FA6}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="79" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="81" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="710">
   <si>
     <t>Codigo</t>
   </si>
@@ -2144,6 +2144,18 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\039800013613.png</t>
+  </si>
+  <si>
+    <t>7795293101338</t>
+  </si>
+  <si>
+    <t>Tapas para pascualina</t>
+  </si>
+  <si>
+    <t>Don Yeyo</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7795293101338.png</t>
   </si>
 </sst>
 </file>
@@ -2495,13 +2507,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F8846C-9FAF-40B1-8447-0F855A47D92E}">
-  <dimension ref="A1:R131"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C277221A-2691-4088-8341-2FC0D2ABE050}">
+  <dimension ref="A1:R132"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
@@ -7281,40 +7293,40 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="B86" t="s">
-        <v>373</v>
+        <v>706</v>
       </c>
       <c r="C86" t="s">
-        <v>88</v>
+        <v>707</v>
       </c>
       <c r="D86" t="s">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="E86" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="F86" t="s">
-        <v>91</v>
+        <v>708</v>
       </c>
       <c r="G86">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="H86" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I86" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J86" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
       </c>
       <c r="L86">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
@@ -7323,13 +7335,13 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>265</v>
+        <v>709</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
       </c>
       <c r="Q86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" t="b">
         <v>1</v>
@@ -7337,40 +7349,40 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B87" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C87" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D87" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E87" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F87" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G87">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H87" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I87" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J87" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
       </c>
       <c r="L87">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
@@ -7379,7 +7391,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -7393,41 +7405,41 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B88" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C88" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D88" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E88" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F88" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G88">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H88" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I88" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J88" t="s">
+        <v>66</v>
+      </c>
+      <c r="K88" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88">
         <v>30</v>
       </c>
-      <c r="K88" t="s">
-        <v>23</v>
-      </c>
-      <c r="L88">
-        <v>12</v>
-      </c>
       <c r="M88" t="b">
         <v>0</v>
       </c>
@@ -7435,13 +7447,13 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
       </c>
       <c r="Q88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R88" t="b">
         <v>1</v>
@@ -7449,55 +7461,55 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
+        <v>29</v>
+      </c>
+      <c r="B89" t="s">
+        <v>375</v>
+      </c>
+      <c r="C89" t="s">
+        <v>24</v>
+      </c>
+      <c r="D89" t="s">
+        <v>54</v>
+      </c>
+      <c r="E89" t="s">
+        <v>55</v>
+      </c>
+      <c r="F89" t="s">
+        <v>61</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89" t="s">
+        <v>28</v>
+      </c>
+      <c r="I89" t="s">
+        <v>96</v>
+      </c>
+      <c r="J89" t="s">
         <v>30</v>
       </c>
-      <c r="B89" t="s">
-        <v>376</v>
-      </c>
-      <c r="C89" t="s">
-        <v>97</v>
-      </c>
-      <c r="D89" t="s">
-        <v>98</v>
-      </c>
-      <c r="E89" t="s">
-        <v>99</v>
-      </c>
-      <c r="F89" t="s">
-        <v>100</v>
-      </c>
-      <c r="G89">
-        <v>100</v>
-      </c>
-      <c r="H89" t="s">
-        <v>20</v>
-      </c>
-      <c r="I89" t="s">
-        <v>101</v>
-      </c>
-      <c r="J89" t="s">
-        <v>102</v>
-      </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
       </c>
       <c r="N89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
       </c>
       <c r="Q89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" t="b">
         <v>1</v>
@@ -7505,49 +7517,49 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B90" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C90" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D90" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E90" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F90" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G90">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H90" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I90" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J90" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
       </c>
       <c r="L90">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
       </c>
       <c r="N90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O90" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -7561,22 +7573,22 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B91" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C91" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D91" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E91" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F91" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G91">
         <v>500</v>
@@ -7588,13 +7600,13 @@
         <v>107</v>
       </c>
       <c r="J91" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -7603,7 +7615,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -7617,40 +7629,40 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B92" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C92" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D92" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E92" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F92" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H92" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I92" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J92" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
       </c>
       <c r="L92">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -7659,13 +7671,13 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
       </c>
       <c r="Q92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="b">
         <v>1</v>
@@ -7673,40 +7685,40 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B93" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C93" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D93" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E93" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F93" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G93">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H93" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I93" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J93" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
       </c>
       <c r="L93">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -7715,13 +7727,13 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
       </c>
       <c r="Q93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
@@ -7729,40 +7741,40 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
+        <v>34</v>
+      </c>
+      <c r="B94" t="s">
+        <v>380</v>
+      </c>
+      <c r="C94" t="s">
+        <v>112</v>
+      </c>
+      <c r="D94" t="s">
+        <v>113</v>
+      </c>
+      <c r="E94" t="s">
+        <v>114</v>
+      </c>
+      <c r="F94" t="s">
+        <v>115</v>
+      </c>
+      <c r="G94">
+        <v>300</v>
+      </c>
+      <c r="H94" t="s">
         <v>35</v>
       </c>
-      <c r="B94" t="s">
-        <v>381</v>
-      </c>
-      <c r="C94" t="s">
-        <v>117</v>
-      </c>
-      <c r="D94" t="s">
-        <v>118</v>
-      </c>
-      <c r="E94" t="s">
-        <v>119</v>
-      </c>
-      <c r="F94" t="s">
-        <v>120</v>
-      </c>
-      <c r="G94">
-        <v>500</v>
-      </c>
-      <c r="H94" t="s">
-        <v>42</v>
-      </c>
       <c r="I94" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J94" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
       </c>
       <c r="L94">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -7771,7 +7783,7 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -7785,40 +7797,40 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B95" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C95" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D95" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E95" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F95" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G95">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H95" t="s">
         <v>42</v>
       </c>
       <c r="I95" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J95" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
       </c>
       <c r="L95">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
@@ -7827,13 +7839,13 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
       </c>
       <c r="Q95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R95" t="b">
         <v>1</v>
@@ -7841,40 +7853,40 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B96" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C96" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D96" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E96" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F96" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G96">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H96" t="s">
         <v>42</v>
       </c>
       <c r="I96" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J96" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
       </c>
       <c r="L96">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
@@ -7883,13 +7895,13 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
       </c>
       <c r="Q96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" t="b">
         <v>1</v>
@@ -7897,34 +7909,34 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B97" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C97" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D97" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E97" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F97" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G97">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H97" t="s">
         <v>42</v>
       </c>
       <c r="I97" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J97" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K97" t="s">
         <v>23</v>
@@ -7939,13 +7951,13 @@
         <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
       </c>
       <c r="Q97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" t="b">
         <v>1</v>
@@ -7953,40 +7965,40 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B98" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C98" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D98" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E98" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F98" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G98">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H98" t="s">
         <v>42</v>
       </c>
       <c r="I98" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J98" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K98" t="s">
         <v>23</v>
       </c>
       <c r="L98">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M98" t="b">
         <v>0</v>
@@ -7995,7 +8007,7 @@
         <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
@@ -8009,40 +8021,40 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B99" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C99" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D99" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E99" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F99" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G99">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H99" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I99" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J99" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K99" t="s">
         <v>23</v>
       </c>
       <c r="L99">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M99" t="b">
         <v>0</v>
@@ -8051,7 +8063,7 @@
         <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
@@ -8065,55 +8077,55 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B100" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C100" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D100" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E100" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F100" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G100">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H100" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I100" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J100" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K100" t="s">
         <v>23</v>
       </c>
       <c r="L100">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
       </c>
       <c r="Q100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R100" t="b">
         <v>1</v>
@@ -8121,10 +8133,10 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B101" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C101" t="s">
         <v>138</v>
@@ -8133,10 +8145,10 @@
         <v>139</v>
       </c>
       <c r="E101" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F101" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G101">
         <v>1000</v>
@@ -8160,10 +8172,10 @@
         <v>1</v>
       </c>
       <c r="N101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O101" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
@@ -8177,22 +8189,22 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B102" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C102" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D102" t="s">
         <v>139</v>
       </c>
       <c r="E102" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F102" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G102">
         <v>1000</v>
@@ -8204,7 +8216,7 @@
         <v>142</v>
       </c>
       <c r="J102" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K102" t="s">
         <v>23</v>
@@ -8219,7 +8231,7 @@
         <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
@@ -8233,55 +8245,55 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B103" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C103" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D103" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E103" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F103" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G103">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H103" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I103" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J103" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K103" t="s">
         <v>23</v>
       </c>
       <c r="L103">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N103" t="b">
         <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
       </c>
       <c r="Q103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R103" t="b">
         <v>1</v>
@@ -8289,55 +8301,55 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B104" t="s">
-        <v>645</v>
+        <v>390</v>
       </c>
       <c r="C104" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D104" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E104" t="s">
-        <v>646</v>
+        <v>151</v>
       </c>
       <c r="F104" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G104">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H104" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I104" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="J104" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="K104" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="L104">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M104" t="b">
         <v>0</v>
       </c>
       <c r="N104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>647</v>
+        <v>282</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
       </c>
       <c r="Q104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" t="b">
         <v>1</v>
@@ -8345,55 +8357,55 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B105" t="s">
-        <v>391</v>
+        <v>645</v>
       </c>
       <c r="C105" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D105" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E105" t="s">
-        <v>163</v>
+        <v>646</v>
       </c>
       <c r="F105" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G105">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H105" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I105" t="s">
-        <v>29</v>
+        <v>158</v>
       </c>
       <c r="J105" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K105" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="L105">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M105" t="b">
         <v>0</v>
       </c>
       <c r="N105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O105" t="s">
-        <v>283</v>
+        <v>647</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
       </c>
       <c r="Q105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R105" t="b">
         <v>1</v>
@@ -8401,34 +8413,34 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B106" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C106" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D106" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E106" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F106" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G106">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H106" t="s">
         <v>42</v>
       </c>
       <c r="I106" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J106" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="K106" t="s">
         <v>23</v>
@@ -8443,7 +8455,7 @@
         <v>1</v>
       </c>
       <c r="O106" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
@@ -8457,22 +8469,22 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B107" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C107" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D107" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E107" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F107" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="G107">
         <v>500</v>
@@ -8484,7 +8496,7 @@
         <v>21</v>
       </c>
       <c r="J107" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K107" t="s">
         <v>23</v>
@@ -8499,7 +8511,7 @@
         <v>1</v>
       </c>
       <c r="O107" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
@@ -8513,34 +8525,34 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B108" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C108" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D108" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E108" t="s">
-        <v>622</v>
+        <v>172</v>
       </c>
       <c r="F108" t="s">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="G108">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H108" t="s">
         <v>42</v>
       </c>
       <c r="I108" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J108" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="K108" t="s">
         <v>23</v>
@@ -8555,7 +8567,7 @@
         <v>1</v>
       </c>
       <c r="O108" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P108" t="b">
         <v>1</v>
@@ -8569,37 +8581,37 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
+        <v>49</v>
+      </c>
+      <c r="B109" t="s">
+        <v>394</v>
+      </c>
+      <c r="C109" t="s">
+        <v>174</v>
+      </c>
+      <c r="D109" t="s">
+        <v>175</v>
+      </c>
+      <c r="E109" t="s">
+        <v>622</v>
+      </c>
+      <c r="F109" t="s">
+        <v>176</v>
+      </c>
+      <c r="G109">
         <v>50</v>
       </c>
-      <c r="B109" t="s">
-        <v>395</v>
-      </c>
-      <c r="C109" t="s">
-        <v>178</v>
-      </c>
-      <c r="D109" t="s">
-        <v>179</v>
-      </c>
-      <c r="E109" t="s">
-        <v>180</v>
-      </c>
-      <c r="F109" t="s">
-        <v>181</v>
-      </c>
-      <c r="G109">
-        <v>12</v>
-      </c>
       <c r="H109" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I109" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="J109" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="K109" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="L109">
         <v>12</v>
@@ -8611,7 +8623,7 @@
         <v>1</v>
       </c>
       <c r="O109" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P109" t="b">
         <v>1</v>
@@ -8625,40 +8637,40 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B110" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C110" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D110" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E110" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F110" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G110">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H110" t="s">
-        <v>188</v>
+        <v>20</v>
       </c>
       <c r="I110" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="J110" t="s">
-        <v>552</v>
+        <v>182</v>
       </c>
       <c r="K110" t="s">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="L110">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M110" t="b">
         <v>0</v>
@@ -8667,7 +8679,7 @@
         <v>1</v>
       </c>
       <c r="O110" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P110" t="b">
         <v>1</v>
@@ -8681,40 +8693,40 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B111" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C111" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D111" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E111" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F111" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="G111">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H111" t="s">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="I111" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
       <c r="J111" t="s">
-        <v>182</v>
+        <v>552</v>
       </c>
       <c r="K111" t="s">
         <v>23</v>
       </c>
       <c r="L111">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M111" t="b">
         <v>0</v>
@@ -8723,7 +8735,7 @@
         <v>1</v>
       </c>
       <c r="O111" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P111" t="b">
         <v>1</v>
@@ -8737,40 +8749,40 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
+        <v>52</v>
+      </c>
+      <c r="B112" t="s">
+        <v>397</v>
+      </c>
+      <c r="C112" t="s">
+        <v>191</v>
+      </c>
+      <c r="D112" t="s">
+        <v>179</v>
+      </c>
+      <c r="E112" t="s">
+        <v>180</v>
+      </c>
+      <c r="F112" t="s">
+        <v>181</v>
+      </c>
+      <c r="G112">
+        <v>24</v>
+      </c>
+      <c r="H112" t="s">
+        <v>20</v>
+      </c>
+      <c r="I112" t="s">
         <v>53</v>
       </c>
-      <c r="B112" t="s">
-        <v>398</v>
-      </c>
-      <c r="C112" t="s">
-        <v>31</v>
-      </c>
-      <c r="D112" t="s">
-        <v>192</v>
-      </c>
-      <c r="E112" t="s">
-        <v>193</v>
-      </c>
-      <c r="F112" t="s">
-        <v>194</v>
-      </c>
-      <c r="G112">
-        <v>1.5</v>
-      </c>
-      <c r="H112" t="s">
-        <v>28</v>
-      </c>
-      <c r="I112" t="s">
-        <v>36</v>
-      </c>
       <c r="J112" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="K112" t="s">
         <v>23</v>
       </c>
       <c r="L112">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M112" t="b">
         <v>0</v>
@@ -8779,7 +8791,7 @@
         <v>1</v>
       </c>
       <c r="O112" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P112" t="b">
         <v>1</v>
@@ -8793,52 +8805,52 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C113" t="s">
-        <v>195</v>
+        <v>31</v>
       </c>
       <c r="D113" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E113" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F113" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G113">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H113" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I113" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J113" t="s">
-        <v>199</v>
+        <v>37</v>
       </c>
       <c r="K113" t="s">
         <v>23</v>
       </c>
       <c r="L113">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M113" t="b">
         <v>0</v>
       </c>
       <c r="N113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O113" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q113" t="b">
         <v>1</v>
@@ -8849,55 +8861,55 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B114" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C114" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="D114" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E114" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F114" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G114">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H114" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I114" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="J114" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="K114" t="s">
         <v>23</v>
       </c>
       <c r="L114">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M114" t="b">
         <v>0</v>
       </c>
       <c r="N114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O114" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R114" t="b">
         <v>1</v>
@@ -8905,40 +8917,40 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B115" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C115" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="D115" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E115" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F115" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G115">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H115" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I115" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="J115" t="s">
-        <v>66</v>
+        <v>190</v>
       </c>
       <c r="K115" t="s">
         <v>23</v>
       </c>
       <c r="L115">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M115" t="b">
         <v>0</v>
@@ -8947,7 +8959,7 @@
         <v>1</v>
       </c>
       <c r="O115" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P115" t="b">
         <v>1</v>
@@ -8961,19 +8973,19 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B116" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C116" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D116" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E116" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F116" t="s">
         <v>206</v>
@@ -9003,7 +9015,7 @@
         <v>1</v>
       </c>
       <c r="O116" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P116" t="b">
         <v>1</v>
@@ -9017,19 +9029,19 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B117" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C117" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D117" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E117" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F117" t="s">
         <v>206</v>
@@ -9050,7 +9062,7 @@
         <v>23</v>
       </c>
       <c r="L117">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M117" t="b">
         <v>0</v>
@@ -9059,7 +9071,7 @@
         <v>1</v>
       </c>
       <c r="O117" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P117" t="b">
         <v>1</v>
@@ -9073,34 +9085,34 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B118" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C118" t="s">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="D118" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E118" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F118" t="s">
-        <v>56</v>
+        <v>206</v>
       </c>
       <c r="G118">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H118" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I118" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="J118" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K118" t="s">
         <v>23</v>
@@ -9115,13 +9127,13 @@
         <v>1</v>
       </c>
       <c r="O118" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P118" t="b">
         <v>1</v>
       </c>
       <c r="Q118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R118" t="b">
         <v>1</v>
@@ -9129,34 +9141,34 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B119" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C119" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D119" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="E119" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="F119" t="s">
-        <v>214</v>
+        <v>56</v>
       </c>
       <c r="G119">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H119" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I119" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J119" t="s">
-        <v>553</v>
+        <v>148</v>
       </c>
       <c r="K119" t="s">
         <v>23</v>
@@ -9171,7 +9183,7 @@
         <v>1</v>
       </c>
       <c r="O119" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P119" t="b">
         <v>1</v>
@@ -9185,49 +9197,49 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B120" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C120" t="s">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="D120" t="s">
-        <v>216</v>
+        <v>81</v>
       </c>
       <c r="E120" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="F120" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G120">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H120" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I120" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J120" t="s">
-        <v>215</v>
+        <v>553</v>
       </c>
       <c r="K120" t="s">
         <v>23</v>
       </c>
       <c r="L120">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M120" t="b">
         <v>0</v>
       </c>
       <c r="N120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O120" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P120" t="b">
         <v>1</v>
@@ -9241,22 +9253,22 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B121" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C121" t="s">
         <v>215</v>
       </c>
       <c r="D121" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E121" t="s">
         <v>217</v>
       </c>
       <c r="F121" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G121">
         <v>20</v>
@@ -9283,13 +9295,13 @@
         <v>0</v>
       </c>
       <c r="O121" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P121" t="b">
         <v>1</v>
       </c>
       <c r="Q121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R121" t="b">
         <v>1</v>
@@ -9297,49 +9309,49 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B122" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C122" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D122" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="E122" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F122" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="G122">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H122" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I122" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J122" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K122" t="s">
         <v>23</v>
       </c>
       <c r="L122">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M122" t="b">
         <v>0</v>
       </c>
       <c r="N122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O122" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P122" t="b">
         <v>1</v>
@@ -9353,34 +9365,34 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B123" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C123" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D123" t="s">
         <v>200</v>
       </c>
       <c r="E123" t="s">
-        <v>32</v>
+        <v>201</v>
       </c>
       <c r="F123" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="G123">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H123" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I123" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J123" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="K123" t="s">
         <v>23</v>
@@ -9395,7 +9407,7 @@
         <v>1</v>
       </c>
       <c r="O123" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P123" t="b">
         <v>1</v>
@@ -9409,40 +9421,40 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B124" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C124" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D124" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="E124" t="s">
-        <v>227</v>
+        <v>32</v>
       </c>
       <c r="F124" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G124">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H124" t="s">
         <v>42</v>
       </c>
       <c r="I124" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J124" t="s">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="K124" t="s">
         <v>23</v>
       </c>
       <c r="L124">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M124" t="b">
         <v>0</v>
@@ -9451,13 +9463,13 @@
         <v>1</v>
       </c>
       <c r="O124" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P124" t="b">
         <v>1</v>
       </c>
       <c r="Q124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R124" t="b">
         <v>1</v>
@@ -9465,40 +9477,40 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B125" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C125" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
       <c r="D125" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E125" t="s">
         <v>227</v>
       </c>
       <c r="F125" t="s">
-        <v>47</v>
+        <v>228</v>
       </c>
       <c r="G125">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H125" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I125" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J125" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K125" t="s">
         <v>23</v>
       </c>
       <c r="L125">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M125" t="b">
         <v>0</v>
@@ -9507,7 +9519,7 @@
         <v>1</v>
       </c>
       <c r="O125" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P125" t="b">
         <v>1</v>
@@ -9521,40 +9533,40 @@
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B126" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C126" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D126" t="s">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="E126" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F126" t="s">
-        <v>194</v>
+        <v>47</v>
       </c>
       <c r="G126">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H126" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I126" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J126" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K126" t="s">
         <v>23</v>
       </c>
       <c r="L126">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M126" t="b">
         <v>0</v>
@@ -9563,13 +9575,13 @@
         <v>1</v>
       </c>
       <c r="O126" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P126" t="b">
         <v>1</v>
       </c>
       <c r="Q126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R126" t="b">
         <v>1</v>
@@ -9577,34 +9589,34 @@
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B127" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C127" t="s">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="D127" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E127" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F127" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G127">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H127" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I127" t="s">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="J127" t="s">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="K127" t="s">
         <v>23</v>
@@ -9619,7 +9631,7 @@
         <v>1</v>
       </c>
       <c r="O127" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P127" t="b">
         <v>1</v>
@@ -9633,10 +9645,10 @@
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B128" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C128" t="s">
         <v>184</v>
@@ -9645,13 +9657,13 @@
         <v>200</v>
       </c>
       <c r="E128" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F128" t="s">
         <v>202</v>
       </c>
       <c r="G128">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H128" t="s">
         <v>35</v>
@@ -9675,7 +9687,7 @@
         <v>1</v>
       </c>
       <c r="O128" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P128" t="b">
         <v>1</v>
@@ -9689,10 +9701,10 @@
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B129" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C129" t="s">
         <v>184</v>
@@ -9707,7 +9719,7 @@
         <v>202</v>
       </c>
       <c r="G129">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H129" t="s">
         <v>35</v>
@@ -9731,7 +9743,7 @@
         <v>1</v>
       </c>
       <c r="O129" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P129" t="b">
         <v>1</v>
@@ -9745,41 +9757,41 @@
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B130" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C130" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="D130" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="E130" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F130" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="G130">
+        <v>250</v>
+      </c>
+      <c r="H130" t="s">
+        <v>35</v>
+      </c>
+      <c r="I130" t="s">
+        <v>189</v>
+      </c>
+      <c r="J130" t="s">
+        <v>190</v>
+      </c>
+      <c r="K130" t="s">
+        <v>23</v>
+      </c>
+      <c r="L130">
         <v>6</v>
       </c>
-      <c r="H130" t="s">
-        <v>20</v>
-      </c>
-      <c r="I130" t="s">
-        <v>237</v>
-      </c>
-      <c r="J130" t="s">
-        <v>233</v>
-      </c>
-      <c r="K130" t="s">
-        <v>23</v>
-      </c>
-      <c r="L130">
-        <v>1</v>
-      </c>
       <c r="M130" t="b">
         <v>0</v>
       </c>
@@ -9787,13 +9799,13 @@
         <v>1</v>
       </c>
       <c r="O130" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R130" t="b">
         <v>1</v>
@@ -9801,57 +9813,113 @@
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B131" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C131" t="s">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="D131" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="E131" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="F131" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G131">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H131" t="s">
         <v>20</v>
       </c>
       <c r="I131" t="s">
+        <v>237</v>
+      </c>
+      <c r="J131" t="s">
+        <v>233</v>
+      </c>
+      <c r="K131" t="s">
+        <v>23</v>
+      </c>
+      <c r="L131">
+        <v>1</v>
+      </c>
+      <c r="M131" t="b">
+        <v>0</v>
+      </c>
+      <c r="N131" t="b">
+        <v>1</v>
+      </c>
+      <c r="O131" t="s">
+        <v>308</v>
+      </c>
+      <c r="P131" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="b">
+        <v>1</v>
+      </c>
+      <c r="R131" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>72</v>
+      </c>
+      <c r="B132" t="s">
+        <v>417</v>
+      </c>
+      <c r="C132" t="s">
+        <v>195</v>
+      </c>
+      <c r="D132" t="s">
+        <v>196</v>
+      </c>
+      <c r="E132" t="s">
+        <v>197</v>
+      </c>
+      <c r="F132" t="s">
+        <v>238</v>
+      </c>
+      <c r="G132">
+        <v>4</v>
+      </c>
+      <c r="H132" t="s">
+        <v>20</v>
+      </c>
+      <c r="I132" t="s">
         <v>21</v>
       </c>
-      <c r="J131" t="s">
+      <c r="J132" t="s">
         <v>199</v>
       </c>
-      <c r="K131" t="s">
-        <v>23</v>
-      </c>
-      <c r="L131">
+      <c r="K132" t="s">
+        <v>23</v>
+      </c>
+      <c r="L132">
         <v>10</v>
       </c>
-      <c r="M131" t="b">
-        <v>0</v>
-      </c>
-      <c r="N131" t="b">
-        <v>0</v>
-      </c>
-      <c r="O131" t="s">
+      <c r="M132" t="b">
+        <v>0</v>
+      </c>
+      <c r="N132" t="b">
+        <v>0</v>
+      </c>
+      <c r="O132" t="s">
         <v>309</v>
       </c>
-      <c r="P131" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q131" t="b">
-        <v>1</v>
-      </c>
-      <c r="R131" t="b">
+      <c r="P132" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q132" t="b">
+        <v>1</v>
+      </c>
+      <c r="R132" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9BAEABD-EEB8-4DD3-863B-D8DD11D61FA6}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128C7E77-C3AB-4DAE-9E77-C59D871EFBFB}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="81" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="82" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="715">
   <si>
     <t>Codigo</t>
   </si>
@@ -2156,6 +2156,21 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7795293101338.png</t>
+  </si>
+  <si>
+    <t>7798338290486</t>
+  </si>
+  <si>
+    <t>parcialmente descremada</t>
+  </si>
+  <si>
+    <t>2%</t>
+  </si>
+  <si>
+    <t>Angelita</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7798338290486.png</t>
   </si>
 </sst>
 </file>
@@ -2507,8 +2522,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C277221A-2691-4088-8341-2FC0D2ABE050}">
-  <dimension ref="A1:R132"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B822734-5BC3-4524-8D81-F1CCF9AB835B}">
+  <dimension ref="A1:R133"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -4358,7 +4373,7 @@
         <v>23</v>
       </c>
       <c r="L33">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M33" t="b">
         <v>0</v>
@@ -5310,7 +5325,7 @@
         <v>23</v>
       </c>
       <c r="L50">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M50" t="b">
         <v>0</v>
@@ -7349,34 +7364,34 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="B87" t="s">
-        <v>373</v>
+        <v>710</v>
       </c>
       <c r="C87" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="D87" t="s">
-        <v>89</v>
+        <v>711</v>
       </c>
       <c r="E87" t="s">
-        <v>90</v>
+        <v>712</v>
       </c>
       <c r="F87" t="s">
-        <v>91</v>
+        <v>713</v>
       </c>
       <c r="G87">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H87" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I87" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J87" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
@@ -7391,13 +7406,13 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>265</v>
+        <v>714</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
       </c>
       <c r="Q87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87" t="b">
         <v>1</v>
@@ -7405,40 +7420,40 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C88" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D88" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E88" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F88" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G88">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H88" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I88" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J88" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
@@ -7447,7 +7462,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -7461,41 +7476,41 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B89" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C89" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D89" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E89" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F89" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G89">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H89" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I89" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J89" t="s">
+        <v>66</v>
+      </c>
+      <c r="K89" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89">
         <v>30</v>
       </c>
-      <c r="K89" t="s">
-        <v>23</v>
-      </c>
-      <c r="L89">
-        <v>12</v>
-      </c>
       <c r="M89" t="b">
         <v>0</v>
       </c>
@@ -7503,13 +7518,13 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
       </c>
       <c r="Q89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R89" t="b">
         <v>1</v>
@@ -7517,34 +7532,34 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
+        <v>29</v>
+      </c>
+      <c r="B90" t="s">
+        <v>375</v>
+      </c>
+      <c r="C90" t="s">
+        <v>24</v>
+      </c>
+      <c r="D90" t="s">
+        <v>54</v>
+      </c>
+      <c r="E90" t="s">
+        <v>55</v>
+      </c>
+      <c r="F90" t="s">
+        <v>61</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+      <c r="H90" t="s">
+        <v>28</v>
+      </c>
+      <c r="I90" t="s">
+        <v>96</v>
+      </c>
+      <c r="J90" t="s">
         <v>30</v>
-      </c>
-      <c r="B90" t="s">
-        <v>376</v>
-      </c>
-      <c r="C90" t="s">
-        <v>97</v>
-      </c>
-      <c r="D90" t="s">
-        <v>98</v>
-      </c>
-      <c r="E90" t="s">
-        <v>99</v>
-      </c>
-      <c r="F90" t="s">
-        <v>100</v>
-      </c>
-      <c r="G90">
-        <v>100</v>
-      </c>
-      <c r="H90" t="s">
-        <v>20</v>
-      </c>
-      <c r="I90" t="s">
-        <v>101</v>
-      </c>
-      <c r="J90" t="s">
-        <v>102</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
@@ -7556,16 +7571,16 @@
         <v>0</v>
       </c>
       <c r="N90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
       </c>
       <c r="Q90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" t="b">
         <v>1</v>
@@ -7573,49 +7588,49 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B91" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C91" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D91" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E91" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F91" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G91">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H91" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I91" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J91" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
       </c>
       <c r="N91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O91" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -7629,22 +7644,22 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B92" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C92" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D92" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E92" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F92" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G92">
         <v>500</v>
@@ -7656,13 +7671,13 @@
         <v>107</v>
       </c>
       <c r="J92" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
       </c>
       <c r="L92">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -7671,7 +7686,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -7685,40 +7700,40 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B93" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C93" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D93" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E93" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F93" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G93">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H93" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I93" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J93" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
       </c>
       <c r="L93">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -7727,13 +7742,13 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
       </c>
       <c r="Q93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
@@ -7741,40 +7756,40 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B94" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C94" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D94" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E94" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F94" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G94">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H94" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I94" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J94" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
       </c>
       <c r="L94">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -7783,13 +7798,13 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
       </c>
       <c r="Q94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94" t="b">
         <v>1</v>
@@ -7797,40 +7812,40 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
+        <v>34</v>
+      </c>
+      <c r="B95" t="s">
+        <v>380</v>
+      </c>
+      <c r="C95" t="s">
+        <v>112</v>
+      </c>
+      <c r="D95" t="s">
+        <v>113</v>
+      </c>
+      <c r="E95" t="s">
+        <v>114</v>
+      </c>
+      <c r="F95" t="s">
+        <v>115</v>
+      </c>
+      <c r="G95">
+        <v>300</v>
+      </c>
+      <c r="H95" t="s">
         <v>35</v>
       </c>
-      <c r="B95" t="s">
-        <v>381</v>
-      </c>
-      <c r="C95" t="s">
-        <v>117</v>
-      </c>
-      <c r="D95" t="s">
-        <v>118</v>
-      </c>
-      <c r="E95" t="s">
-        <v>119</v>
-      </c>
-      <c r="F95" t="s">
-        <v>120</v>
-      </c>
-      <c r="G95">
-        <v>500</v>
-      </c>
-      <c r="H95" t="s">
-        <v>42</v>
-      </c>
       <c r="I95" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J95" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
       </c>
       <c r="L95">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
@@ -7839,7 +7854,7 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
@@ -7853,40 +7868,40 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B96" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C96" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D96" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E96" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F96" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G96">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H96" t="s">
         <v>42</v>
       </c>
       <c r="I96" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J96" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
       </c>
       <c r="L96">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
@@ -7895,13 +7910,13 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
       </c>
       <c r="Q96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" t="b">
         <v>1</v>
@@ -7909,40 +7924,40 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B97" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C97" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D97" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E97" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F97" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G97">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H97" t="s">
         <v>42</v>
       </c>
       <c r="I97" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J97" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K97" t="s">
         <v>23</v>
       </c>
       <c r="L97">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
@@ -7951,13 +7966,13 @@
         <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
       </c>
       <c r="Q97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" t="b">
         <v>1</v>
@@ -7965,34 +7980,34 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B98" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C98" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D98" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E98" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F98" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G98">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H98" t="s">
         <v>42</v>
       </c>
       <c r="I98" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J98" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K98" t="s">
         <v>23</v>
@@ -8007,13 +8022,13 @@
         <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
       </c>
       <c r="Q98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="b">
         <v>1</v>
@@ -8021,40 +8036,40 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B99" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C99" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D99" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E99" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F99" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G99">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H99" t="s">
         <v>42</v>
       </c>
       <c r="I99" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J99" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K99" t="s">
         <v>23</v>
       </c>
       <c r="L99">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M99" t="b">
         <v>0</v>
@@ -8063,7 +8078,7 @@
         <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
@@ -8077,40 +8092,40 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B100" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C100" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D100" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E100" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F100" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H100" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I100" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J100" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K100" t="s">
         <v>23</v>
       </c>
       <c r="L100">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M100" t="b">
         <v>0</v>
@@ -8119,7 +8134,7 @@
         <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
@@ -8133,55 +8148,55 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B101" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C101" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D101" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E101" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F101" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G101">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H101" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I101" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J101" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K101" t="s">
         <v>23</v>
       </c>
       <c r="L101">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
       </c>
       <c r="Q101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" t="b">
         <v>1</v>
@@ -8189,10 +8204,10 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B102" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C102" t="s">
         <v>138</v>
@@ -8201,10 +8216,10 @@
         <v>139</v>
       </c>
       <c r="E102" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F102" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G102">
         <v>1000</v>
@@ -8228,10 +8243,10 @@
         <v>1</v>
       </c>
       <c r="N102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O102" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
@@ -8245,22 +8260,22 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B103" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C103" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D103" t="s">
         <v>139</v>
       </c>
       <c r="E103" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F103" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G103">
         <v>1000</v>
@@ -8272,7 +8287,7 @@
         <v>142</v>
       </c>
       <c r="J103" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K103" t="s">
         <v>23</v>
@@ -8287,7 +8302,7 @@
         <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
@@ -8301,55 +8316,55 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B104" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C104" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D104" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E104" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F104" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G104">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H104" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I104" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J104" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K104" t="s">
         <v>23</v>
       </c>
       <c r="L104">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
       </c>
       <c r="Q104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R104" t="b">
         <v>1</v>
@@ -8357,55 +8372,55 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B105" t="s">
-        <v>645</v>
+        <v>390</v>
       </c>
       <c r="C105" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D105" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E105" t="s">
-        <v>646</v>
+        <v>151</v>
       </c>
       <c r="F105" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G105">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H105" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I105" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="J105" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="K105" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="L105">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M105" t="b">
         <v>0</v>
       </c>
       <c r="N105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O105" t="s">
-        <v>647</v>
+        <v>282</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
       </c>
       <c r="Q105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105" t="b">
         <v>1</v>
@@ -8413,55 +8428,55 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B106" t="s">
-        <v>391</v>
+        <v>645</v>
       </c>
       <c r="C106" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D106" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E106" t="s">
-        <v>163</v>
+        <v>646</v>
       </c>
       <c r="F106" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G106">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H106" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I106" t="s">
-        <v>29</v>
+        <v>158</v>
       </c>
       <c r="J106" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K106" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="L106">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M106" t="b">
         <v>0</v>
       </c>
       <c r="N106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O106" t="s">
-        <v>283</v>
+        <v>647</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
       </c>
       <c r="Q106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R106" t="b">
         <v>1</v>
@@ -8469,34 +8484,34 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B107" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C107" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D107" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E107" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F107" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G107">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H107" t="s">
         <v>42</v>
       </c>
       <c r="I107" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J107" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="K107" t="s">
         <v>23</v>
@@ -8511,7 +8526,7 @@
         <v>1</v>
       </c>
       <c r="O107" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
@@ -8525,22 +8540,22 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B108" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C108" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D108" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E108" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F108" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="G108">
         <v>500</v>
@@ -8552,7 +8567,7 @@
         <v>21</v>
       </c>
       <c r="J108" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K108" t="s">
         <v>23</v>
@@ -8567,7 +8582,7 @@
         <v>1</v>
       </c>
       <c r="O108" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P108" t="b">
         <v>1</v>
@@ -8581,34 +8596,34 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B109" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C109" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D109" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E109" t="s">
-        <v>622</v>
+        <v>172</v>
       </c>
       <c r="F109" t="s">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="G109">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H109" t="s">
         <v>42</v>
       </c>
       <c r="I109" t="s">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="J109" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="K109" t="s">
         <v>23</v>
@@ -8623,7 +8638,7 @@
         <v>1</v>
       </c>
       <c r="O109" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P109" t="b">
         <v>1</v>
@@ -8637,37 +8652,37 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
+        <v>49</v>
+      </c>
+      <c r="B110" t="s">
+        <v>394</v>
+      </c>
+      <c r="C110" t="s">
+        <v>174</v>
+      </c>
+      <c r="D110" t="s">
+        <v>175</v>
+      </c>
+      <c r="E110" t="s">
+        <v>622</v>
+      </c>
+      <c r="F110" t="s">
+        <v>176</v>
+      </c>
+      <c r="G110">
         <v>50</v>
       </c>
-      <c r="B110" t="s">
-        <v>395</v>
-      </c>
-      <c r="C110" t="s">
-        <v>178</v>
-      </c>
-      <c r="D110" t="s">
-        <v>179</v>
-      </c>
-      <c r="E110" t="s">
-        <v>180</v>
-      </c>
-      <c r="F110" t="s">
-        <v>181</v>
-      </c>
-      <c r="G110">
-        <v>12</v>
-      </c>
       <c r="H110" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I110" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="J110" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="K110" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="L110">
         <v>12</v>
@@ -8679,7 +8694,7 @@
         <v>1</v>
       </c>
       <c r="O110" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P110" t="b">
         <v>1</v>
@@ -8693,40 +8708,40 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B111" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C111" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D111" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E111" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F111" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G111">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H111" t="s">
-        <v>188</v>
+        <v>20</v>
       </c>
       <c r="I111" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="J111" t="s">
-        <v>552</v>
+        <v>182</v>
       </c>
       <c r="K111" t="s">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="L111">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M111" t="b">
         <v>0</v>
@@ -8735,7 +8750,7 @@
         <v>1</v>
       </c>
       <c r="O111" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P111" t="b">
         <v>1</v>
@@ -8749,40 +8764,40 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B112" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C112" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D112" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E112" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F112" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="G112">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H112" t="s">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="I112" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
       <c r="J112" t="s">
-        <v>182</v>
+        <v>552</v>
       </c>
       <c r="K112" t="s">
         <v>23</v>
       </c>
       <c r="L112">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M112" t="b">
         <v>0</v>
@@ -8791,7 +8806,7 @@
         <v>1</v>
       </c>
       <c r="O112" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P112" t="b">
         <v>1</v>
@@ -8805,40 +8820,40 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
+        <v>52</v>
+      </c>
+      <c r="B113" t="s">
+        <v>397</v>
+      </c>
+      <c r="C113" t="s">
+        <v>191</v>
+      </c>
+      <c r="D113" t="s">
+        <v>179</v>
+      </c>
+      <c r="E113" t="s">
+        <v>180</v>
+      </c>
+      <c r="F113" t="s">
+        <v>181</v>
+      </c>
+      <c r="G113">
+        <v>24</v>
+      </c>
+      <c r="H113" t="s">
+        <v>20</v>
+      </c>
+      <c r="I113" t="s">
         <v>53</v>
       </c>
-      <c r="B113" t="s">
-        <v>398</v>
-      </c>
-      <c r="C113" t="s">
-        <v>31</v>
-      </c>
-      <c r="D113" t="s">
-        <v>192</v>
-      </c>
-      <c r="E113" t="s">
-        <v>193</v>
-      </c>
-      <c r="F113" t="s">
-        <v>194</v>
-      </c>
-      <c r="G113">
-        <v>1.5</v>
-      </c>
-      <c r="H113" t="s">
-        <v>28</v>
-      </c>
-      <c r="I113" t="s">
-        <v>36</v>
-      </c>
       <c r="J113" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="K113" t="s">
         <v>23</v>
       </c>
       <c r="L113">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M113" t="b">
         <v>0</v>
@@ -8847,7 +8862,7 @@
         <v>1</v>
       </c>
       <c r="O113" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P113" t="b">
         <v>1</v>
@@ -8861,52 +8876,52 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C114" t="s">
-        <v>195</v>
+        <v>31</v>
       </c>
       <c r="D114" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E114" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F114" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G114">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H114" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I114" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J114" t="s">
-        <v>199</v>
+        <v>37</v>
       </c>
       <c r="K114" t="s">
         <v>23</v>
       </c>
       <c r="L114">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M114" t="b">
         <v>0</v>
       </c>
       <c r="N114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O114" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q114" t="b">
         <v>1</v>
@@ -8917,55 +8932,55 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C115" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="D115" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E115" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F115" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G115">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H115" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I115" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="J115" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="K115" t="s">
         <v>23</v>
       </c>
       <c r="L115">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M115" t="b">
         <v>0</v>
       </c>
       <c r="N115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O115" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R115" t="b">
         <v>1</v>
@@ -8973,40 +8988,40 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B116" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C116" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="D116" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E116" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F116" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G116">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H116" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I116" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="J116" t="s">
-        <v>66</v>
+        <v>190</v>
       </c>
       <c r="K116" t="s">
         <v>23</v>
       </c>
       <c r="L116">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M116" t="b">
         <v>0</v>
@@ -9015,7 +9030,7 @@
         <v>1</v>
       </c>
       <c r="O116" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P116" t="b">
         <v>1</v>
@@ -9029,19 +9044,19 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B117" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C117" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D117" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E117" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F117" t="s">
         <v>206</v>
@@ -9071,7 +9086,7 @@
         <v>1</v>
       </c>
       <c r="O117" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P117" t="b">
         <v>1</v>
@@ -9085,19 +9100,19 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B118" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C118" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D118" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E118" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F118" t="s">
         <v>206</v>
@@ -9118,7 +9133,7 @@
         <v>23</v>
       </c>
       <c r="L118">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M118" t="b">
         <v>0</v>
@@ -9127,7 +9142,7 @@
         <v>1</v>
       </c>
       <c r="O118" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P118" t="b">
         <v>1</v>
@@ -9141,34 +9156,34 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B119" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C119" t="s">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="D119" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E119" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F119" t="s">
-        <v>56</v>
+        <v>206</v>
       </c>
       <c r="G119">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H119" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I119" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="J119" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K119" t="s">
         <v>23</v>
@@ -9183,13 +9198,13 @@
         <v>1</v>
       </c>
       <c r="O119" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P119" t="b">
         <v>1</v>
       </c>
       <c r="Q119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R119" t="b">
         <v>1</v>
@@ -9197,34 +9212,34 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B120" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C120" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D120" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="E120" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="F120" t="s">
-        <v>214</v>
+        <v>56</v>
       </c>
       <c r="G120">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H120" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I120" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J120" t="s">
-        <v>553</v>
+        <v>148</v>
       </c>
       <c r="K120" t="s">
         <v>23</v>
@@ -9239,7 +9254,7 @@
         <v>1</v>
       </c>
       <c r="O120" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P120" t="b">
         <v>1</v>
@@ -9253,49 +9268,49 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B121" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C121" t="s">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="D121" t="s">
-        <v>216</v>
+        <v>81</v>
       </c>
       <c r="E121" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="F121" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G121">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H121" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I121" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J121" t="s">
-        <v>215</v>
+        <v>553</v>
       </c>
       <c r="K121" t="s">
         <v>23</v>
       </c>
       <c r="L121">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M121" t="b">
         <v>0</v>
       </c>
       <c r="N121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O121" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P121" t="b">
         <v>1</v>
@@ -9309,22 +9324,22 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B122" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C122" t="s">
         <v>215</v>
       </c>
       <c r="D122" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E122" t="s">
         <v>217</v>
       </c>
       <c r="F122" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G122">
         <v>20</v>
@@ -9351,13 +9366,13 @@
         <v>0</v>
       </c>
       <c r="O122" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P122" t="b">
         <v>1</v>
       </c>
       <c r="Q122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R122" t="b">
         <v>1</v>
@@ -9365,49 +9380,49 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B123" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C123" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D123" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="E123" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F123" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="G123">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H123" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I123" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J123" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K123" t="s">
         <v>23</v>
       </c>
       <c r="L123">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M123" t="b">
         <v>0</v>
       </c>
       <c r="N123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O123" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P123" t="b">
         <v>1</v>
@@ -9421,34 +9436,34 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B124" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C124" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D124" t="s">
         <v>200</v>
       </c>
       <c r="E124" t="s">
-        <v>32</v>
+        <v>201</v>
       </c>
       <c r="F124" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="G124">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H124" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I124" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J124" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="K124" t="s">
         <v>23</v>
@@ -9463,7 +9478,7 @@
         <v>1</v>
       </c>
       <c r="O124" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P124" t="b">
         <v>1</v>
@@ -9477,40 +9492,40 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B125" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C125" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D125" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="E125" t="s">
-        <v>227</v>
+        <v>32</v>
       </c>
       <c r="F125" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G125">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H125" t="s">
         <v>42</v>
       </c>
       <c r="I125" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J125" t="s">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="K125" t="s">
         <v>23</v>
       </c>
       <c r="L125">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M125" t="b">
         <v>0</v>
@@ -9519,13 +9534,13 @@
         <v>1</v>
       </c>
       <c r="O125" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P125" t="b">
         <v>1</v>
       </c>
       <c r="Q125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R125" t="b">
         <v>1</v>
@@ -9533,40 +9548,40 @@
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B126" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C126" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
       <c r="D126" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E126" t="s">
         <v>227</v>
       </c>
       <c r="F126" t="s">
-        <v>47</v>
+        <v>228</v>
       </c>
       <c r="G126">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H126" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I126" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J126" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K126" t="s">
         <v>23</v>
       </c>
       <c r="L126">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M126" t="b">
         <v>0</v>
@@ -9575,7 +9590,7 @@
         <v>1</v>
       </c>
       <c r="O126" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P126" t="b">
         <v>1</v>
@@ -9589,40 +9604,40 @@
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B127" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C127" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D127" t="s">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="E127" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F127" t="s">
-        <v>194</v>
+        <v>47</v>
       </c>
       <c r="G127">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H127" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I127" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J127" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K127" t="s">
         <v>23</v>
       </c>
       <c r="L127">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M127" t="b">
         <v>0</v>
@@ -9631,13 +9646,13 @@
         <v>1</v>
       </c>
       <c r="O127" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P127" t="b">
         <v>1</v>
       </c>
       <c r="Q127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R127" t="b">
         <v>1</v>
@@ -9645,34 +9660,34 @@
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B128" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C128" t="s">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="D128" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E128" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F128" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G128">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H128" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I128" t="s">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="J128" t="s">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="K128" t="s">
         <v>23</v>
@@ -9687,7 +9702,7 @@
         <v>1</v>
       </c>
       <c r="O128" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P128" t="b">
         <v>1</v>
@@ -9701,10 +9716,10 @@
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B129" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C129" t="s">
         <v>184</v>
@@ -9713,13 +9728,13 @@
         <v>200</v>
       </c>
       <c r="E129" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F129" t="s">
         <v>202</v>
       </c>
       <c r="G129">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H129" t="s">
         <v>35</v>
@@ -9743,7 +9758,7 @@
         <v>1</v>
       </c>
       <c r="O129" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P129" t="b">
         <v>1</v>
@@ -9757,10 +9772,10 @@
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B130" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C130" t="s">
         <v>184</v>
@@ -9775,7 +9790,7 @@
         <v>202</v>
       </c>
       <c r="G130">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H130" t="s">
         <v>35</v>
@@ -9799,7 +9814,7 @@
         <v>1</v>
       </c>
       <c r="O130" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P130" t="b">
         <v>1</v>
@@ -9813,41 +9828,41 @@
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B131" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C131" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="D131" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="E131" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F131" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="G131">
+        <v>250</v>
+      </c>
+      <c r="H131" t="s">
+        <v>35</v>
+      </c>
+      <c r="I131" t="s">
+        <v>189</v>
+      </c>
+      <c r="J131" t="s">
+        <v>190</v>
+      </c>
+      <c r="K131" t="s">
+        <v>23</v>
+      </c>
+      <c r="L131">
         <v>6</v>
       </c>
-      <c r="H131" t="s">
-        <v>20</v>
-      </c>
-      <c r="I131" t="s">
-        <v>237</v>
-      </c>
-      <c r="J131" t="s">
-        <v>233</v>
-      </c>
-      <c r="K131" t="s">
-        <v>23</v>
-      </c>
-      <c r="L131">
-        <v>1</v>
-      </c>
       <c r="M131" t="b">
         <v>0</v>
       </c>
@@ -9855,13 +9870,13 @@
         <v>1</v>
       </c>
       <c r="O131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R131" t="b">
         <v>1</v>
@@ -9869,57 +9884,113 @@
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B132" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C132" t="s">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="D132" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="E132" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="F132" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G132">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H132" t="s">
         <v>20</v>
       </c>
       <c r="I132" t="s">
+        <v>237</v>
+      </c>
+      <c r="J132" t="s">
+        <v>233</v>
+      </c>
+      <c r="K132" t="s">
+        <v>23</v>
+      </c>
+      <c r="L132">
+        <v>1</v>
+      </c>
+      <c r="M132" t="b">
+        <v>0</v>
+      </c>
+      <c r="N132" t="b">
+        <v>1</v>
+      </c>
+      <c r="O132" t="s">
+        <v>308</v>
+      </c>
+      <c r="P132" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="b">
+        <v>1</v>
+      </c>
+      <c r="R132" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <v>72</v>
+      </c>
+      <c r="B133" t="s">
+        <v>417</v>
+      </c>
+      <c r="C133" t="s">
+        <v>195</v>
+      </c>
+      <c r="D133" t="s">
+        <v>196</v>
+      </c>
+      <c r="E133" t="s">
+        <v>197</v>
+      </c>
+      <c r="F133" t="s">
+        <v>238</v>
+      </c>
+      <c r="G133">
+        <v>4</v>
+      </c>
+      <c r="H133" t="s">
+        <v>20</v>
+      </c>
+      <c r="I133" t="s">
         <v>21</v>
       </c>
-      <c r="J132" t="s">
+      <c r="J133" t="s">
         <v>199</v>
       </c>
-      <c r="K132" t="s">
-        <v>23</v>
-      </c>
-      <c r="L132">
+      <c r="K133" t="s">
+        <v>23</v>
+      </c>
+      <c r="L133">
         <v>10</v>
       </c>
-      <c r="M132" t="b">
-        <v>0</v>
-      </c>
-      <c r="N132" t="b">
-        <v>0</v>
-      </c>
-      <c r="O132" t="s">
+      <c r="M133" t="b">
+        <v>0</v>
+      </c>
+      <c r="N133" t="b">
+        <v>0</v>
+      </c>
+      <c r="O133" t="s">
         <v>309</v>
       </c>
-      <c r="P132" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q132" t="b">
-        <v>1</v>
-      </c>
-      <c r="R132" t="b">
+      <c r="P133" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q133" t="b">
+        <v>1</v>
+      </c>
+      <c r="R133" t="b">
         <v>1</v>
       </c>
     </row>
